--- a/ESD2026.xlsx
+++ b/ESD2026.xlsx
@@ -12,7 +12,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="24450" windowHeight="7560"/>
   </bookViews>
   <sheets>
-    <sheet name="Evolove April 15 - 19" sheetId="1" r:id="rId1"/>
+    <sheet name="Evolve April 15 - 19" sheetId="1" r:id="rId1"/>
     <sheet name="Plie Prep April 29 - May 3" sheetId="2" r:id="rId2"/>
     <sheet name="Red Deer May 8 -10" sheetId="4" r:id="rId3"/>
     <sheet name="Abstract May 21-24" sheetId="3" r:id="rId4"/>

--- a/ESD2026.xlsx
+++ b/ESD2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17640" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17640" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Evolve April 15 - 19" sheetId="1" r:id="rId1"/>
@@ -1112,9 +1112,6 @@
     <t>Town Square Celebration</t>
   </si>
   <si>
-    <t>Eloise Baker, Annabella Beeroo,Charlotte Fedechko, Kenna Fowler,Ava Jagusch, Madison Jones, StellaKnowler, Quincy Knowler, MelodyLefebvre, Aurora O'Connor, MariaSushko, Philippa Tam, EmmyThomson, Annika Vidal, Ellery Watts,Brixton Wright</t>
-  </si>
-  <si>
     <t>Classical Ballet Extended Line age 13-14 Division 4</t>
   </si>
   <si>
@@ -1160,9 +1157,6 @@
     <t>It's Party Time</t>
   </si>
   <si>
-    <t>Eloise Baker, Annabella Beeroo, Ava Jagusch, Eniafe Jaji, Madison Jones, Stella Knowler, Quincy Knowler, Melody Lefebvre, Keira McCurdy, Aurora O'Connor, Claire Stretch, EmmyThomson, Ellery Watts, Brixton Wright</t>
-  </si>
-  <si>
     <t>Jazz Small Group age 13-14 Division 3</t>
   </si>
   <si>
@@ -1202,9 +1196,6 @@
     <t>Carry You</t>
   </si>
   <si>
-    <t>Eloise Baker, Annabella Beeroo, Ava Jagusch, Madison Jones, Stella Knowler, Quincy Knowler, Melody Lefebvre, Keira McCurdy, Aurora O'Connor, Claire Stretch, Maria Sushko, Philippa Tam, EmmyThomson, Ellery Watts, Brixton Wright</t>
-  </si>
-  <si>
     <t>Musical Theatre Solo age 11-12 Division 2</t>
   </si>
   <si>
@@ -1833,6 +1824,15 @@
   </si>
   <si>
     <t>April 29 - May 3</t>
+  </si>
+  <si>
+    <t>Eloise Baker, Annabella Beeroo,Charlotte Fedechko, Kenna Fowler,Ava Jagusch, Madison Jones, Stella Knowler, Quincy Knowler, Melody Lefebvre, Aurora O'Connor, Maria Sushko, Philippa Tam, Emmy Thomson, Annika Vidal, Ellery Watts, Brixton Wright</t>
+  </si>
+  <si>
+    <t>Eloise Baker, Annabella Beeroo, Ava Jagusch, Eniafe Jaji, Madison Jones, Stella Knowler, Quincy Knowler, Melody Lefebvre, Keira McCurdy, Aurora O'Connor, Claire Stretch, Emmy Thomson, Ellery Watts, Brixton Wright</t>
+  </si>
+  <si>
+    <t>Eloise Baker, Annabella Beeroo, Ava Jagusch, Madison Jones, Stella Knowler, Quincy Knowler, Melody Lefebvre, Keira McCurdy, Aurora O'Connor, Claire Stretch, Maria Sushko, Philippa Tam, Emmy Thomson, Ellery Watts, Brixton Wright</t>
   </si>
 </sst>
 </file>
@@ -3255,7 +3255,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>6</v>
@@ -5067,7 +5067,7 @@
         <v>216</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="C2" s="79"/>
       <c r="D2" s="80"/>
@@ -5084,7 +5084,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E3" s="82" t="s">
         <v>6</v>
@@ -7036,7 +7036,7 @@
         <v>355</v>
       </c>
       <c r="E128" s="75" t="s">
-        <v>356</v>
+        <v>594</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
@@ -7047,13 +7047,13 @@
         <v>0.60763888888888895</v>
       </c>
       <c r="C129" s="76" t="s">
+        <v>356</v>
+      </c>
+      <c r="D129" s="99" t="s">
         <v>357</v>
       </c>
-      <c r="D129" s="99" t="s">
+      <c r="E129" s="75" t="s">
         <v>358</v>
-      </c>
-      <c r="E129" s="75" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -7077,13 +7077,13 @@
         <v>0.70138888888888884</v>
       </c>
       <c r="C131" s="76" t="s">
+        <v>359</v>
+      </c>
+      <c r="D131" s="100" t="s">
         <v>360</v>
       </c>
-      <c r="D131" s="100" t="s">
+      <c r="E131" s="75" t="s">
         <v>361</v>
-      </c>
-      <c r="E131" s="75" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
@@ -7094,13 +7094,13 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="C132" s="76" t="s">
+        <v>362</v>
+      </c>
+      <c r="D132" s="100" t="s">
         <v>363</v>
       </c>
-      <c r="D132" s="100" t="s">
+      <c r="E132" s="75" t="s">
         <v>364</v>
-      </c>
-      <c r="E132" s="75" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -7124,7 +7124,7 @@
         <v>0.76736111111111116</v>
       </c>
       <c r="C134" s="47" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D134" s="94" t="s">
         <v>206</v>
@@ -7154,13 +7154,13 @@
         <v>0.78819444444444453</v>
       </c>
       <c r="C136" s="47" t="s">
+        <v>366</v>
+      </c>
+      <c r="D136" s="94" t="s">
         <v>367</v>
       </c>
-      <c r="D136" s="94" t="s">
+      <c r="E136" s="72" t="s">
         <v>368</v>
-      </c>
-      <c r="E136" s="72" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -7184,13 +7184,13 @@
         <v>0.81597222222222221</v>
       </c>
       <c r="C138" s="76" t="s">
+        <v>369</v>
+      </c>
+      <c r="D138" s="100" t="s">
         <v>370</v>
       </c>
-      <c r="D138" s="100" t="s">
-        <v>371</v>
-      </c>
       <c r="E138" s="75" t="s">
-        <v>372</v>
+        <v>595</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
@@ -7201,13 +7201,13 @@
         <v>0.82638888888888884</v>
       </c>
       <c r="C139" s="76" t="s">
+        <v>371</v>
+      </c>
+      <c r="D139" s="99" t="s">
+        <v>372</v>
+      </c>
+      <c r="E139" s="75" t="s">
         <v>373</v>
-      </c>
-      <c r="D139" s="99" t="s">
-        <v>374</v>
-      </c>
-      <c r="E139" s="75" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -7231,13 +7231,13 @@
         <v>0.85069444444444453</v>
       </c>
       <c r="C141" s="76" t="s">
+        <v>374</v>
+      </c>
+      <c r="D141" s="99" t="s">
+        <v>375</v>
+      </c>
+      <c r="E141" s="75" t="s">
         <v>376</v>
-      </c>
-      <c r="D141" s="99" t="s">
-        <v>377</v>
-      </c>
-      <c r="E141" s="75" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -7261,7 +7261,7 @@
         <v>0.88194444444444453</v>
       </c>
       <c r="C143" s="47" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D143" s="94" t="s">
         <v>84</v>
@@ -7291,7 +7291,7 @@
         <v>0.90972222222222221</v>
       </c>
       <c r="C145" s="47" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D145" s="94" t="s">
         <v>27</v>
@@ -7315,7 +7315,7 @@
     </row>
     <row r="147" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A147" s="91" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B147" s="92"/>
       <c r="C147" s="73"/>
@@ -7330,13 +7330,13 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="C148" s="76" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D148" s="101" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E148" s="75" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -7360,13 +7360,13 @@
         <v>0.61111111111111105</v>
       </c>
       <c r="C150" s="76" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D150" s="101" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E150" s="75" t="s">
-        <v>386</v>
+        <v>596</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -7390,7 +7390,7 @@
         <v>0.63888888888888895</v>
       </c>
       <c r="C152" s="47" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D152" s="89" t="s">
         <v>75</v>
@@ -7420,7 +7420,7 @@
         <v>0.69444444444444453</v>
       </c>
       <c r="C154" s="47" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D154" s="89" t="s">
         <v>115</v>
@@ -7444,24 +7444,24 @@
     </row>
     <row r="156" spans="1:5" ht="64.5" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A156" s="103" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B156" s="104">
         <v>0.70833333333333337</v>
       </c>
       <c r="C156" s="105" t="s">
+        <v>356</v>
+      </c>
+      <c r="D156" s="105" t="s">
         <v>357</v>
       </c>
-      <c r="D156" s="105" t="s">
-        <v>358</v>
-      </c>
       <c r="E156" s="75" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A157" s="22" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B157" s="106"/>
       <c r="C157" s="22"/>
@@ -7488,7 +7488,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="122" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B1" s="107"/>
       <c r="C1" s="5"/>
@@ -7497,10 +7497,10 @@
     </row>
     <row r="2" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B2" s="78" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
@@ -7517,7 +7517,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>6</v>
@@ -7525,7 +7525,7 @@
     </row>
     <row r="4" spans="1:5" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="124" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B4" s="84"/>
       <c r="C4" s="84"/>
@@ -7540,7 +7540,7 @@
         <v>0.49027777777777781</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D5" s="89" t="s">
         <v>126</v>
@@ -7557,7 +7557,7 @@
         <v>0.49444444444444446</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D6" s="125" t="s">
         <v>20</v>
@@ -7574,7 +7574,7 @@
         <v>0.50763888888888886</v>
       </c>
       <c r="C7" s="74" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D7" s="128" t="s">
         <v>142</v>
@@ -7591,10 +7591,10 @@
         <v>0.62291666666666667</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="D8" s="125" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="E8" s="108" t="s">
         <v>161</v>
@@ -7608,7 +7608,7 @@
         <v>0.625</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D9" s="125" t="s">
         <v>154</v>
@@ -7625,7 +7625,7 @@
         <v>0.62847222222222221</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="D10" s="125" t="s">
         <v>294</v>
@@ -7642,7 +7642,7 @@
         <v>0.64444444444444449</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D11" s="131" t="s">
         <v>50</v>
@@ -7659,7 +7659,7 @@
         <v>0.67361111111111116</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D12" s="77" t="s">
         <v>100</v>
@@ -7676,7 +7676,7 @@
         <v>0.76527777777777783</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D13" s="132" t="s">
         <v>129</v>
@@ -7693,7 +7693,7 @@
         <v>0.78680555555555554</v>
       </c>
       <c r="C14" s="109" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D14" s="135" t="s">
         <v>315</v>
@@ -7710,7 +7710,7 @@
         <v>0.7895833333333333</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D15" s="89" t="s">
         <v>318</v>
@@ -7727,7 +7727,7 @@
         <v>0.8354166666666667</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D16" s="125" t="s">
         <v>60</v>
@@ -7744,7 +7744,7 @@
         <v>0.84166666666666667</v>
       </c>
       <c r="C17" s="47" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D17" s="131" t="s">
         <v>175</v>
@@ -7761,7 +7761,7 @@
         <v>0.84305555555555556</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D18" s="131" t="s">
         <v>59</v>
@@ -7778,7 +7778,7 @@
         <v>0.85833333333333339</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D19" s="77" t="s">
         <v>321</v>
@@ -7789,7 +7789,7 @@
     </row>
     <row r="20" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="140" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B20" s="92"/>
       <c r="C20" s="92"/>
@@ -7804,7 +7804,7 @@
         <v>0.3888888888888889</v>
       </c>
       <c r="C21" s="76" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D21" s="141" t="s">
         <v>339</v>
@@ -7821,13 +7821,13 @@
         <v>0.39097222222222222</v>
       </c>
       <c r="C22" s="109" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D22" s="100" t="s">
         <v>355</v>
       </c>
       <c r="E22" s="75" t="s">
-        <v>356</v>
+        <v>594</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.25">
@@ -7838,7 +7838,7 @@
         <v>0.3923611111111111</v>
       </c>
       <c r="C23" s="109" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D23" s="135" t="s">
         <v>345</v>
@@ -7855,7 +7855,7 @@
         <v>0.40277777777777773</v>
       </c>
       <c r="C24" s="109" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D24" s="135" t="s">
         <v>342</v>
@@ -7866,30 +7866,30 @@
     </row>
     <row r="25" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="144" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B25" s="20">
         <v>0.4069444444444445</v>
       </c>
       <c r="C25" s="47" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D25" s="131" t="s">
         <v>94</v>
       </c>
       <c r="E25" s="108" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="144" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B26" s="20">
         <v>0.40972222222222227</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D26" s="89" t="s">
         <v>157</v>
@@ -7906,7 +7906,7 @@
         <v>0.41805555555555557</v>
       </c>
       <c r="C27" s="109" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D27" s="125" t="s">
         <v>292</v>
@@ -7917,7 +7917,7 @@
     </row>
     <row r="28" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A28" s="146" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B28" s="129"/>
       <c r="C28" s="110"/>
@@ -7932,18 +7932,18 @@
         <v>0.4201388888888889</v>
       </c>
       <c r="C29" s="76" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D29" s="141" t="s">
+        <v>357</v>
+      </c>
+      <c r="E29" s="75" t="s">
         <v>358</v>
-      </c>
-      <c r="E29" s="75" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="147" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B30" s="142"/>
       <c r="C30" s="112"/>
@@ -7958,7 +7958,7 @@
         <v>0.4680555555555555</v>
       </c>
       <c r="C31" s="109" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D31" s="125" t="s">
         <v>27</v>
@@ -7969,7 +7969,7 @@
     </row>
     <row r="32" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A32" s="146" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B32" s="129"/>
       <c r="C32" s="110"/>
@@ -7984,18 +7984,18 @@
         <v>0.47361111111111115</v>
       </c>
       <c r="C33" s="76" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D33" s="141" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E33" s="75" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="147" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B34" s="149"/>
       <c r="C34" s="112"/>
@@ -8010,7 +8010,7 @@
         <v>0.55069444444444449</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D35" s="89" t="s">
         <v>255</v>
@@ -8027,7 +8027,7 @@
         <v>0.56180555555555556</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D36" s="125" t="s">
         <v>137</v>
@@ -8038,13 +8038,13 @@
     </row>
     <row r="37" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="144" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B37" s="139">
         <v>0.58333333333333337</v>
       </c>
       <c r="C37" s="47" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D37" s="125" t="s">
         <v>210</v>
@@ -8061,13 +8061,13 @@
         <v>0.60486111111111118</v>
       </c>
       <c r="C38" s="47" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D38" s="131" t="s">
         <v>183</v>
       </c>
       <c r="E38" s="108" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8078,7 +8078,7 @@
         <v>0.6069444444444444</v>
       </c>
       <c r="C39" s="47" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D39" s="125" t="s">
         <v>186</v>
@@ -8095,7 +8095,7 @@
         <v>0.61041666666666672</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D40" s="125" t="s">
         <v>78</v>
@@ -8112,7 +8112,7 @@
         <v>0.62152777777777779</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D41" s="125" t="s">
         <v>193</v>
@@ -8123,13 +8123,13 @@
     </row>
     <row r="42" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="144" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B42" s="139">
         <v>0.62569444444444444</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D42" s="125" t="s">
         <v>190</v>
@@ -8146,7 +8146,7 @@
         <v>0.62708333333333333</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D43" s="125" t="s">
         <v>44</v>
@@ -8163,7 +8163,7 @@
         <v>0.62916666666666665</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="D44" s="132" t="s">
         <v>17</v>
@@ -8180,7 +8180,7 @@
         <v>0.64027777777777783</v>
       </c>
       <c r="C45" s="109" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D45" s="135" t="s">
         <v>333</v>
@@ -8197,7 +8197,7 @@
         <v>0.64652777777777781</v>
       </c>
       <c r="C46" s="109" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D46" s="101" t="s">
         <v>336</v>
@@ -8214,10 +8214,10 @@
         <v>0.65347222222222223</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D47" s="131" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E47" s="111" t="s">
         <v>37</v>
@@ -8231,7 +8231,7 @@
         <v>0.65555555555555556</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D48" s="131" t="s">
         <v>227</v>
@@ -8248,7 +8248,7 @@
         <v>0.70208333333333339</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D49" s="125" t="s">
         <v>297</v>
@@ -8265,24 +8265,24 @@
         <v>0.77500000000000002</v>
       </c>
       <c r="C50" s="76" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D50" s="141" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E50" s="75" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="144" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B51" s="139">
         <v>0.79513888888888884</v>
       </c>
       <c r="C51" s="47" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D51" s="125" t="s">
         <v>172</v>
@@ -8299,7 +8299,7 @@
         <v>0.84375</v>
       </c>
       <c r="C52" s="47" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D52" s="132" t="s">
         <v>177</v>
@@ -8316,7 +8316,7 @@
         <v>0.85625000000000007</v>
       </c>
       <c r="C53" s="47" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D53" s="125" t="s">
         <v>279</v>
@@ -8333,7 +8333,7 @@
         <v>0.85763888888888884</v>
       </c>
       <c r="C54" s="47" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D54" s="125" t="s">
         <v>176</v>
@@ -8344,7 +8344,7 @@
     </row>
     <row r="55" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="140" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B55" s="92"/>
       <c r="C55" s="34"/>
@@ -8359,13 +8359,13 @@
         <v>0.37916666666666665</v>
       </c>
       <c r="C56" s="115" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="D56" s="135" t="s">
+        <v>360</v>
+      </c>
+      <c r="E56" s="75" t="s">
         <v>361</v>
-      </c>
-      <c r="E56" s="75" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
@@ -8376,13 +8376,13 @@
         <v>0.38958333333333334</v>
       </c>
       <c r="C57" s="115" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="D57" s="141" t="s">
+        <v>363</v>
+      </c>
+      <c r="E57" s="75" t="s">
         <v>364</v>
-      </c>
-      <c r="E57" s="75" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8393,7 +8393,7 @@
         <v>0.41250000000000003</v>
       </c>
       <c r="C58" s="114" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D58" s="125" t="s">
         <v>202</v>
@@ -8410,7 +8410,7 @@
         <v>0.4145833333333333</v>
       </c>
       <c r="C59" s="115" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D59" s="158" t="s">
         <v>196</v>
@@ -8427,7 +8427,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="C60" s="115" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D60" s="125" t="s">
         <v>301</v>
@@ -8444,7 +8444,7 @@
         <v>0.41875000000000001</v>
       </c>
       <c r="C61" s="115" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D61" s="125" t="s">
         <v>22</v>
@@ -8461,7 +8461,7 @@
         <v>0.42083333333333334</v>
       </c>
       <c r="C62" s="114" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D62" s="77" t="s">
         <v>103</v>
@@ -8478,7 +8478,7 @@
         <v>0.42499999999999999</v>
       </c>
       <c r="C63" s="115" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D63" s="141" t="s">
         <v>309</v>
@@ -8495,7 +8495,7 @@
         <v>0.43611111111111112</v>
       </c>
       <c r="C64" s="115" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D64" s="135" t="s">
         <v>312</v>
@@ -8512,24 +8512,24 @@
         <v>0.4381944444444445</v>
       </c>
       <c r="C65" s="117" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="D65" s="141" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E65" s="75" t="s">
-        <v>372</v>
+        <v>595</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A66" s="157" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B66" s="139">
         <v>0.47569444444444442</v>
       </c>
       <c r="C66" s="119" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D66" s="125" t="s">
         <v>81</v>
@@ -8546,7 +8546,7 @@
         <v>0.4777777777777778</v>
       </c>
       <c r="C67" s="117" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="D67" s="131" t="s">
         <v>72</v>
@@ -8557,7 +8557,7 @@
     </row>
     <row r="68" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A68" s="157" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B68" s="150"/>
       <c r="C68" s="118"/>
@@ -8572,7 +8572,7 @@
         <v>0.48749999999999999</v>
       </c>
       <c r="C69" s="119" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D69" s="125" t="s">
         <v>84</v>
@@ -8589,13 +8589,13 @@
         <v>0.49374999999999997</v>
       </c>
       <c r="C70" s="117" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D70" s="141" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E70" s="75" t="s">
-        <v>386</v>
+        <v>596</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
@@ -8606,7 +8606,7 @@
         <v>0.52708333333333335</v>
       </c>
       <c r="C71" s="117" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D71" s="141" t="s">
         <v>257</v>
@@ -8623,13 +8623,13 @@
         <v>0.60138888888888886</v>
       </c>
       <c r="C72" s="119" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D72" s="89" t="s">
+        <v>367</v>
+      </c>
+      <c r="E72" s="72" t="s">
         <v>368</v>
-      </c>
-      <c r="E72" s="72" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -8640,7 +8640,7 @@
         <v>0.64166666666666672</v>
       </c>
       <c r="C73" s="119" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D73" s="87" t="s">
         <v>252</v>
@@ -8657,7 +8657,7 @@
         <v>0.6791666666666667</v>
       </c>
       <c r="C74" s="119" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D74" s="131" t="s">
         <v>115</v>
@@ -8674,7 +8674,7 @@
         <v>0.68888888888888899</v>
       </c>
       <c r="C75" s="119" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D75" s="132" t="s">
         <v>69</v>
@@ -8691,7 +8691,7 @@
         <v>0.79513888888888884</v>
       </c>
       <c r="C76" s="120" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="D76" s="125" t="s">
         <v>199</v>
@@ -8708,7 +8708,7 @@
         <v>0.80486111111111114</v>
       </c>
       <c r="C77" s="119" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D77" s="125" t="s">
         <v>206</v>
@@ -8725,7 +8725,7 @@
         <v>0.80694444444444446</v>
       </c>
       <c r="C78" s="119" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D78" s="125" t="s">
         <v>75</v>
@@ -8742,7 +8742,7 @@
         <v>0.86249999999999993</v>
       </c>
       <c r="C79" s="117" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D79" s="141" t="s">
         <v>348</v>
@@ -8753,7 +8753,7 @@
     </row>
     <row r="80" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A80" s="140" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B80" s="92"/>
       <c r="C80" s="34"/>
@@ -8768,7 +8768,7 @@
         <v>0.3840277777777778</v>
       </c>
       <c r="C81" s="21" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="D81" s="132" t="s">
         <v>40</v>
@@ -8785,7 +8785,7 @@
         <v>0.38611111111111113</v>
       </c>
       <c r="C82" s="21" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="D82" s="131" t="s">
         <v>263</v>
@@ -8802,7 +8802,7 @@
         <v>0.41111111111111115</v>
       </c>
       <c r="C83" s="21" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D83" s="132" t="s">
         <v>244</v>
@@ -8819,7 +8819,7 @@
         <v>0.42499999999999999</v>
       </c>
       <c r="C84" s="26" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D84" s="125" t="s">
         <v>327</v>
@@ -8836,7 +8836,7 @@
         <v>0.4284722222222222</v>
       </c>
       <c r="C85" s="21" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="D85" s="125" t="s">
         <v>66</v>
@@ -8853,7 +8853,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="C86" s="21" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D86" s="125" t="s">
         <v>109</v>
@@ -8870,7 +8870,7 @@
         <v>0.4597222222222222</v>
       </c>
       <c r="C87" s="21" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D87" s="125" t="s">
         <v>107</v>
@@ -8887,7 +8887,7 @@
         <v>0.46111111111111108</v>
       </c>
       <c r="C88" s="21" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D88" s="125" t="s">
         <v>47</v>
@@ -8904,7 +8904,7 @@
         <v>0.46319444444444446</v>
       </c>
       <c r="C89" s="21" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D89" s="131" t="s">
         <v>163</v>
@@ -8921,7 +8921,7 @@
         <v>0.46527777777777773</v>
       </c>
       <c r="C90" s="21" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D90" s="131" t="s">
         <v>233</v>
@@ -8938,7 +8938,7 @@
         <v>0.47222222222222227</v>
       </c>
       <c r="C91" s="109" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="D91" s="99" t="s">
         <v>151</v>
@@ -8955,13 +8955,13 @@
         <v>0.47569444444444442</v>
       </c>
       <c r="C92" s="21" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D92" s="132" t="s">
         <v>112</v>
       </c>
       <c r="E92" s="111" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8972,7 +8972,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="C93" s="74" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D93" s="125" t="s">
         <v>288</v>
@@ -8989,7 +8989,7 @@
         <v>0.48333333333333334</v>
       </c>
       <c r="C94" s="109" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D94" s="135" t="s">
         <v>9</v>
@@ -9006,7 +9006,7 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="C95" s="74" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D95" s="131" t="s">
         <v>135</v>
@@ -9023,7 +9023,7 @@
         <v>0.49305555555555558</v>
       </c>
       <c r="C96" s="21" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="D96" s="125" t="s">
         <v>97</v>
@@ -9040,7 +9040,7 @@
         <v>0.49652777777777773</v>
       </c>
       <c r="C97" s="26" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D97" s="125" t="s">
         <v>30</v>
@@ -9057,7 +9057,7 @@
         <v>0.5</v>
       </c>
       <c r="C98" s="21" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="D98" s="125" t="s">
         <v>353</v>
@@ -9074,7 +9074,7 @@
         <v>0.50208333333333333</v>
       </c>
       <c r="C99" s="26" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="D99" s="125" t="s">
         <v>122</v>
@@ -9091,7 +9091,7 @@
         <v>0.50624999999999998</v>
       </c>
       <c r="C100" s="21" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D100" s="125" t="s">
         <v>145</v>
@@ -9108,7 +9108,7 @@
         <v>0.51736111111111105</v>
       </c>
       <c r="C101" s="26" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D101" s="125" t="s">
         <v>174</v>
@@ -9125,7 +9125,7 @@
         <v>0.51944444444444449</v>
       </c>
       <c r="C102" s="21" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="D102" s="131" t="s">
         <v>25</v>
@@ -9142,7 +9142,7 @@
         <v>0.52361111111111114</v>
       </c>
       <c r="C103" s="26" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D103" s="125" t="s">
         <v>241</v>
@@ -9159,7 +9159,7 @@
         <v>0.58888888888888891</v>
       </c>
       <c r="C104" s="26" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D104" s="132" t="s">
         <v>56</v>
@@ -9176,7 +9176,7 @@
         <v>0.59166666666666667</v>
       </c>
       <c r="C105" s="47" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D105" s="125" t="s">
         <v>12</v>
@@ -9193,7 +9193,7 @@
         <v>0.59375</v>
       </c>
       <c r="C106" s="26" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D106" s="131" t="s">
         <v>54</v>
@@ -9204,7 +9204,7 @@
     </row>
     <row r="107" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A107" s="162" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B107" s="21"/>
       <c r="C107" s="21"/>
@@ -9231,10 +9231,10 @@
   <sheetData>
     <row r="1" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="176" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B1" s="177" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C1" s="164"/>
       <c r="D1" s="135"/>
@@ -9242,7 +9242,7 @@
     </row>
     <row r="2" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="178" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B2" s="179"/>
       <c r="C2" s="165"/>
@@ -9260,7 +9260,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="184" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>6</v>
@@ -9268,7 +9268,7 @@
     </row>
     <row r="4" spans="1:5" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A4" s="185" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B4" s="186"/>
       <c r="C4" s="186"/>
@@ -9283,10 +9283,10 @@
         <v>0.34583333333333338</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="D5" s="89" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="E5" s="108" t="s">
         <v>161</v>
@@ -9300,7 +9300,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="D6" s="89" t="s">
         <v>157</v>
@@ -9317,7 +9317,7 @@
         <v>0.35902777777777778</v>
       </c>
       <c r="C7" s="76" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D7" s="135" t="s">
         <v>342</v>
@@ -9341,7 +9341,7 @@
         <v>0.37847222222222227</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D9" s="89" t="s">
         <v>44</v>
@@ -9358,7 +9358,7 @@
         <v>0.38055555555555554</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D10" s="89" t="s">
         <v>190</v>
@@ -9375,7 +9375,7 @@
         <v>0.40625</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D11" s="89" t="s">
         <v>306</v>
@@ -9392,24 +9392,24 @@
         <v>0.4145833333333333</v>
       </c>
       <c r="C12" s="109" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="D12" s="141" t="s">
         <v>355</v>
       </c>
       <c r="E12" s="75" t="s">
-        <v>356</v>
+        <v>594</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="169" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B13" s="170">
         <v>0.41736111111111113</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D13" s="88"/>
       <c r="E13" s="166"/>
@@ -9422,7 +9422,7 @@
         <v>0.44722222222222219</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D14" s="89" t="s">
         <v>109</v>
@@ -9433,13 +9433,13 @@
     </row>
     <row r="15" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="160" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B15" s="167">
         <v>0.44930555555555557</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D15" s="89" t="s">
         <v>107</v>
@@ -9450,13 +9450,13 @@
     </row>
     <row r="16" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="160" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B16" s="167">
         <v>0.4513888888888889</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D16" s="89" t="s">
         <v>47</v>
@@ -9473,7 +9473,7 @@
         <v>0.47083333333333338</v>
       </c>
       <c r="C17" s="47" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D17" s="77" t="s">
         <v>244</v>
@@ -9490,7 +9490,7 @@
         <v>0.48541666666666666</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="D18" s="89" t="s">
         <v>75</v>
@@ -9507,7 +9507,7 @@
         <v>0.48749999999999999</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="D19" s="89" t="s">
         <v>206</v>
@@ -9524,13 +9524,13 @@
         <v>0.50694444444444442</v>
       </c>
       <c r="C20" s="109" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D20" s="141" t="s">
+        <v>363</v>
+      </c>
+      <c r="E20" s="75" t="s">
         <v>364</v>
-      </c>
-      <c r="E20" s="75" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -9541,7 +9541,7 @@
         <v>0.5180555555555556</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D21" s="89" t="s">
         <v>100</v>
@@ -9552,13 +9552,13 @@
     </row>
     <row r="22" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="169" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B22" s="170">
         <v>0.52569444444444446</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D22" s="171"/>
       <c r="E22" s="25"/>
@@ -9569,7 +9569,7 @@
         <v>0.54999999999999993</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D23" s="88"/>
       <c r="E23" s="166"/>
@@ -9582,7 +9582,7 @@
         <v>0.5854166666666667</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D24" s="89" t="s">
         <v>327</v>
@@ -9599,7 +9599,7 @@
         <v>0.60833333333333328</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D25" s="89" t="s">
         <v>22</v>
@@ -9616,7 +9616,7 @@
         <v>0.61041666666666672</v>
       </c>
       <c r="C26" s="47" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D26" s="94" t="s">
         <v>196</v>
@@ -9633,7 +9633,7 @@
         <v>0.62430555555555556</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D27" s="89" t="s">
         <v>174</v>
@@ -9644,13 +9644,13 @@
     </row>
     <row r="28" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="169" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B28" s="170">
         <v>0.65763888888888888</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D28" s="171"/>
       <c r="E28" s="166"/>
@@ -9663,7 +9663,7 @@
         <v>0.6875</v>
       </c>
       <c r="C29" s="47" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D29" s="87" t="s">
         <v>227</v>
@@ -9680,10 +9680,10 @@
         <v>0.69166666666666676</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D30" s="87" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E30" s="121" t="s">
         <v>37</v>
@@ -9697,7 +9697,7 @@
         <v>0.69374999999999998</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D31" s="87" t="s">
         <v>163</v>
@@ -9714,7 +9714,7 @@
         <v>0.6958333333333333</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="D32" s="87" t="s">
         <v>233</v>
@@ -9731,7 +9731,7 @@
         <v>0.71111111111111114</v>
       </c>
       <c r="C33" s="47" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D33" s="87" t="s">
         <v>72</v>
@@ -9748,7 +9748,7 @@
         <v>0.74791666666666667</v>
       </c>
       <c r="C34" s="47" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D34" s="87" t="s">
         <v>50</v>
@@ -9759,13 +9759,13 @@
     </row>
     <row r="35" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="169" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B35" s="170">
         <v>0.76874999999999993</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D35" s="88"/>
       <c r="E35" s="166"/>
@@ -9776,7 +9776,7 @@
         <v>0.79305555555555562</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D36" s="171"/>
       <c r="E36" s="25"/>
@@ -9789,31 +9789,31 @@
         <v>0.8222222222222223</v>
       </c>
       <c r="C37" s="109" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D37" s="141" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E37" s="75" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="169" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B38" s="170">
         <v>0.88611111111111107</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D38" s="171"/>
       <c r="E38" s="25"/>
     </row>
     <row r="39" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="173" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B39" s="174"/>
       <c r="C39" s="175"/>
@@ -9828,7 +9828,7 @@
         <v>0.34166666666666662</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="D40" s="89" t="s">
         <v>78</v>
@@ -9845,13 +9845,13 @@
         <v>0.35000000000000003</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D41" s="89" t="s">
+        <v>367</v>
+      </c>
+      <c r="E41" s="72" t="s">
         <v>368</v>
-      </c>
-      <c r="E41" s="72" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -9862,7 +9862,7 @@
         <v>0.36458333333333331</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D42" s="89" t="s">
         <v>66</v>
@@ -9879,7 +9879,7 @@
         <v>0.36874999999999997</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="D43" s="89" t="s">
         <v>154</v>
@@ -9896,7 +9896,7 @@
         <v>0.38194444444444442</v>
       </c>
       <c r="C44" s="76" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D44" s="135" t="s">
         <v>345</v>
@@ -9907,13 +9907,13 @@
     </row>
     <row r="45" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="169" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B45" s="170">
         <v>0.41597222222222219</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D45" s="88"/>
       <c r="E45" s="166"/>
@@ -9926,7 +9926,7 @@
         <v>0.44027777777777777</v>
       </c>
       <c r="C46" s="76" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="D46" s="135" t="s">
         <v>315</v>
@@ -9943,7 +9943,7 @@
         <v>0.4604166666666667</v>
       </c>
       <c r="C47" s="47" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="D47" s="89" t="s">
         <v>172</v>
@@ -9960,13 +9960,13 @@
         <v>0.47083333333333338</v>
       </c>
       <c r="C48" s="76" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D48" s="141" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E48" s="75" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -9977,7 +9977,7 @@
         <v>0.47361111111111115</v>
       </c>
       <c r="C49" s="47" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D49" s="77" t="s">
         <v>40</v>
@@ -9994,7 +9994,7 @@
         <v>0.4777777777777778</v>
       </c>
       <c r="C50" s="47" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D50" s="87" t="s">
         <v>263</v>
@@ -10011,7 +10011,7 @@
         <v>0.49236111111111108</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="D51" s="87" t="s">
         <v>115</v>
@@ -10028,7 +10028,7 @@
         <v>0.50486111111111109</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D52" s="87" t="s">
         <v>54</v>
@@ -10045,7 +10045,7 @@
         <v>0.50694444444444442</v>
       </c>
       <c r="C53" s="47" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D53" s="87" t="s">
         <v>25</v>
@@ -10062,7 +10062,7 @@
         <v>0.52013888888888882</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D54" s="89" t="s">
         <v>294</v>
@@ -10079,24 +10079,24 @@
         <v>0.52222222222222225</v>
       </c>
       <c r="C55" s="109" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D55" s="141" t="s">
+        <v>357</v>
+      </c>
+      <c r="E55" s="75" t="s">
         <v>358</v>
-      </c>
-      <c r="E55" s="75" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A56" s="169" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B56" s="170">
         <v>0.52500000000000002</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D56" s="88"/>
       <c r="E56" s="106"/>
@@ -10107,7 +10107,7 @@
         <v>0.5493055555555556</v>
       </c>
       <c r="C57" s="22" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D57" s="171"/>
       <c r="E57" s="25"/>
@@ -10120,7 +10120,7 @@
         <v>0.57013888888888886</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D58" s="89" t="s">
         <v>257</v>
@@ -10137,7 +10137,7 @@
         <v>0.57291666666666663</v>
       </c>
       <c r="C59" s="47" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D59" s="77" t="s">
         <v>69</v>
@@ -10154,7 +10154,7 @@
         <v>0.60138888888888886</v>
       </c>
       <c r="C60" s="109" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D60" s="141" t="s">
         <v>142</v>
@@ -10171,7 +10171,7 @@
         <v>0.61388888888888882</v>
       </c>
       <c r="C61" s="47" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D61" s="77" t="s">
         <v>312</v>
@@ -10188,7 +10188,7 @@
         <v>0.61875000000000002</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="D62" s="89" t="s">
         <v>12</v>
@@ -10205,7 +10205,7 @@
         <v>0.65069444444444446</v>
       </c>
       <c r="C63" s="47" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="D63" s="89" t="s">
         <v>20</v>
@@ -10216,13 +10216,13 @@
     </row>
     <row r="64" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A64" s="169" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B64" s="170">
         <v>0.65833333333333333</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D64" s="88"/>
       <c r="E64" s="106"/>
@@ -10235,7 +10235,7 @@
         <v>0.69166666666666676</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="D65" s="89" t="s">
         <v>103</v>
@@ -10252,7 +10252,7 @@
         <v>0.69930555555555562</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D66" s="89" t="s">
         <v>122</v>
@@ -10269,7 +10269,7 @@
         <v>0.70347222222222217</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D67" s="89" t="s">
         <v>353</v>
@@ -10286,7 +10286,7 @@
         <v>0.70486111111111116</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D68" s="89" t="s">
         <v>145</v>
@@ -10303,7 +10303,7 @@
         <v>0.72083333333333333</v>
       </c>
       <c r="C69" s="21" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D69" s="89" t="s">
         <v>97</v>
@@ -10314,13 +10314,13 @@
     </row>
     <row r="70" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A70" s="169" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B70" s="170">
         <v>0.76527777777777783</v>
       </c>
       <c r="C70" s="22" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D70" s="88"/>
       <c r="E70" s="106"/>
@@ -10331,7 +10331,7 @@
         <v>0.7895833333333333</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D71" s="88"/>
       <c r="E71" s="106"/>
@@ -10344,7 +10344,7 @@
         <v>0.84444444444444444</v>
       </c>
       <c r="C72" s="109" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D72" s="141" t="s">
         <v>348</v>
@@ -10361,31 +10361,31 @@
         <v>0.88263888888888886</v>
       </c>
       <c r="C73" s="109" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D73" s="141" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E73" s="75" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A74" s="169" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B74" s="170">
         <v>0.88541666666666663</v>
       </c>
       <c r="C74" s="22" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D74" s="171"/>
       <c r="E74" s="25"/>
     </row>
     <row r="75" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A75" s="173" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="B75" s="174"/>
       <c r="C75" s="175"/>
@@ -10400,7 +10400,7 @@
         <v>0.34583333333333338</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="D76" s="89" t="s">
         <v>81</v>
@@ -10417,7 +10417,7 @@
         <v>0.34791666666666665</v>
       </c>
       <c r="C77" s="21" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="D77" s="89" t="s">
         <v>186</v>
@@ -10434,7 +10434,7 @@
         <v>0.36041666666666666</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="D78" s="89" t="s">
         <v>301</v>
@@ -10451,7 +10451,7 @@
         <v>0.36249999999999999</v>
       </c>
       <c r="C79" s="21" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D79" s="89" t="s">
         <v>126</v>
@@ -10468,7 +10468,7 @@
         <v>0.37847222222222227</v>
       </c>
       <c r="C80" s="47" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="D80" s="77" t="s">
         <v>129</v>
@@ -10485,7 +10485,7 @@
         <v>0.38958333333333334</v>
       </c>
       <c r="C81" s="21" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D81" s="89" t="s">
         <v>330</v>
@@ -10502,7 +10502,7 @@
         <v>0.39513888888888887</v>
       </c>
       <c r="C82" s="109" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="D82" s="141" t="s">
         <v>339</v>
@@ -10513,13 +10513,13 @@
     </row>
     <row r="83" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A83" s="169" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B83" s="170">
         <v>0.41319444444444442</v>
       </c>
       <c r="C83" s="22" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D83" s="171"/>
       <c r="E83" s="25"/>
@@ -10532,7 +10532,7 @@
         <v>0.4916666666666667</v>
       </c>
       <c r="C84" s="21" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D84" s="89" t="s">
         <v>292</v>
@@ -10549,7 +10549,7 @@
         <v>0.99375000000000002</v>
       </c>
       <c r="C85" s="109" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="D85" s="141" t="s">
         <v>350</v>
@@ -10566,7 +10566,7 @@
         <v>0.50694444444444442</v>
       </c>
       <c r="C86" s="109" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="D86" s="135" t="s">
         <v>333</v>
@@ -10577,13 +10577,13 @@
     </row>
     <row r="87" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A87" s="169" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B87" s="170">
         <v>0.51736111111111105</v>
       </c>
       <c r="C87" s="22" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D87" s="88"/>
       <c r="E87" s="106"/>
@@ -10594,7 +10594,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C88" s="22" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D88" s="171"/>
       <c r="E88" s="25"/>
@@ -10607,7 +10607,7 @@
         <v>0.56666666666666665</v>
       </c>
       <c r="C89" s="47" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D89" s="77" t="s">
         <v>56</v>
@@ -10624,7 +10624,7 @@
         <v>0.56874999999999998</v>
       </c>
       <c r="C90" s="21" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D90" s="89" t="s">
         <v>241</v>
@@ -10641,7 +10641,7 @@
         <v>0.57291666666666663</v>
       </c>
       <c r="C91" s="21" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D91" s="89" t="s">
         <v>193</v>
@@ -10658,7 +10658,7 @@
         <v>0.57500000000000007</v>
       </c>
       <c r="C92" s="47" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D92" s="77" t="s">
         <v>17</v>
@@ -10675,7 +10675,7 @@
         <v>0.5805555555555556</v>
       </c>
       <c r="C93" s="21" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D93" s="89" t="s">
         <v>318</v>
@@ -10692,7 +10692,7 @@
         <v>0.58750000000000002</v>
       </c>
       <c r="C94" s="47" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="D94" s="77" t="s">
         <v>177</v>
@@ -10709,13 +10709,13 @@
         <v>0.6</v>
       </c>
       <c r="C95" s="109" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="D95" s="141" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E95" s="75" t="s">
-        <v>386</v>
+        <v>596</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="38.25" x14ac:dyDescent="0.15">
@@ -10726,24 +10726,24 @@
         <v>0.63680555555555551</v>
       </c>
       <c r="C96" s="109" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="D96" s="141" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E96" s="75" t="s">
-        <v>372</v>
+        <v>595</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A97" s="169" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B97" s="170">
         <v>0.63750000000000007</v>
       </c>
       <c r="C97" s="22" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D97" s="171"/>
       <c r="E97" s="25"/>
@@ -10756,7 +10756,7 @@
         <v>0.67152777777777783</v>
       </c>
       <c r="C98" s="21" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D98" s="89" t="s">
         <v>288</v>
@@ -10773,13 +10773,13 @@
         <v>0.6777777777777777</v>
       </c>
       <c r="C99" s="76" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="D99" s="135" t="s">
+        <v>360</v>
+      </c>
+      <c r="E99" s="75" t="s">
         <v>361</v>
-      </c>
-      <c r="E99" s="75" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
@@ -10790,7 +10790,7 @@
         <v>0.69374999999999998</v>
       </c>
       <c r="C100" s="21" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="D100" s="89" t="s">
         <v>275</v>
@@ -10807,7 +10807,7 @@
         <v>0.7055555555555556</v>
       </c>
       <c r="C101" s="21" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D101" s="89" t="s">
         <v>279</v>
@@ -10824,7 +10824,7 @@
         <v>0.70763888888888893</v>
       </c>
       <c r="C102" s="21" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D102" s="89" t="s">
         <v>176</v>
@@ -10841,7 +10841,7 @@
         <v>0.72361111111111109</v>
       </c>
       <c r="C103" s="21" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="D103" s="89" t="s">
         <v>297</v>
@@ -10858,7 +10858,7 @@
         <v>0.72569444444444453</v>
       </c>
       <c r="C104" s="21" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="D104" s="89" t="s">
         <v>202</v>
@@ -10875,7 +10875,7 @@
         <v>0.73541666666666661</v>
       </c>
       <c r="C105" s="21" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="D105" s="89" t="s">
         <v>30</v>
@@ -10892,7 +10892,7 @@
         <v>0.74513888888888891</v>
       </c>
       <c r="C106" s="21" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="D106" s="89" t="s">
         <v>84</v>
@@ -10909,7 +10909,7 @@
         <v>0.74722222222222223</v>
       </c>
       <c r="C107" s="21" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="D107" s="89" t="s">
         <v>151</v>
@@ -10920,13 +10920,13 @@
     </row>
     <row r="108" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A108" s="169" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B108" s="170">
         <v>0.75208333333333333</v>
       </c>
       <c r="C108" s="22" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D108" s="88"/>
       <c r="E108" s="106"/>
@@ -10937,7 +10937,7 @@
         <v>0.77638888888888891</v>
       </c>
       <c r="C109" s="22" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D109" s="88"/>
       <c r="E109" s="106"/>
@@ -10950,7 +10950,7 @@
         <v>0.81944444444444453</v>
       </c>
       <c r="C110" s="21" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="D110" s="89" t="s">
         <v>27</v>
@@ -10967,7 +10967,7 @@
         <v>0.84791666666666676</v>
       </c>
       <c r="C111" s="21" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="D111" s="89" t="s">
         <v>210</v>
@@ -10978,20 +10978,20 @@
     </row>
     <row r="112" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A112" s="169" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B112" s="170">
         <v>0.87708333333333333</v>
       </c>
       <c r="C112" s="22" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D112" s="171"/>
       <c r="E112" s="25"/>
     </row>
     <row r="113" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A113" s="173" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="B113" s="174"/>
       <c r="C113" s="175"/>
@@ -11006,13 +11006,13 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C114" s="76" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="D114" s="101" t="s">
         <v>336</v>
       </c>
       <c r="E114" s="75" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -11023,13 +11023,13 @@
         <v>0.34236111111111112</v>
       </c>
       <c r="C115" s="47" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="D115" s="87" t="s">
         <v>94</v>
       </c>
       <c r="E115" s="108" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -11040,13 +11040,13 @@
         <v>0.37708333333333338</v>
       </c>
       <c r="C116" s="47" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="D116" s="77" t="s">
         <v>112</v>
       </c>
       <c r="E116" s="111" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -11057,7 +11057,7 @@
         <v>0.37916666666666665</v>
       </c>
       <c r="C117" s="47" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="D117" s="77" t="s">
         <v>9</v>
@@ -11074,7 +11074,7 @@
         <v>0.38125000000000003</v>
       </c>
       <c r="C118" s="21" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="D118" s="87" t="s">
         <v>252</v>
@@ -11091,7 +11091,7 @@
         <v>0.3972222222222222</v>
       </c>
       <c r="C119" s="21" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="D119" s="89" t="s">
         <v>309</v>
@@ -11108,7 +11108,7 @@
         <v>0.4069444444444445</v>
       </c>
       <c r="C120" s="21" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="D120" s="89" t="s">
         <v>199</v>
@@ -11119,13 +11119,13 @@
     </row>
     <row r="121" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A121" s="169" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B121" s="170">
         <v>0.41180555555555554</v>
       </c>
       <c r="C121" s="22" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D121" s="171"/>
       <c r="E121" s="25"/>
@@ -11138,13 +11138,13 @@
         <v>0.46249999999999997</v>
       </c>
       <c r="C122" s="47" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="D122" s="87" t="s">
         <v>183</v>
       </c>
       <c r="E122" s="108" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -11155,7 +11155,7 @@
         <v>0.47638888888888892</v>
       </c>
       <c r="C123" s="21" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="D123" s="87" t="s">
         <v>135</v>
@@ -11172,7 +11172,7 @@
         <v>0.51111111111111118</v>
       </c>
       <c r="C124" s="47" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="D124" s="77" t="s">
         <v>321</v>
@@ -11183,13 +11183,13 @@
     </row>
     <row r="125" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A125" s="169" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B125" s="170">
         <v>0.51388888888888895</v>
       </c>
       <c r="C125" s="22" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D125" s="88"/>
       <c r="E125" s="106"/>
@@ -11200,7 +11200,7 @@
         <v>0.53819444444444442</v>
       </c>
       <c r="C126" s="22" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D126" s="171"/>
       <c r="E126" s="25"/>
@@ -11213,7 +11213,7 @@
         <v>0.55069444444444449</v>
       </c>
       <c r="C127" s="21" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D127" s="89" t="s">
         <v>137</v>
@@ -11230,7 +11230,7 @@
         <v>0.57847222222222217</v>
       </c>
       <c r="C128" s="21" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="D128" s="89" t="s">
         <v>60</v>
@@ -11247,7 +11247,7 @@
         <v>0.57986111111111105</v>
       </c>
       <c r="C129" s="47" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="D129" s="87" t="s">
         <v>175</v>
@@ -11264,7 +11264,7 @@
         <v>0.58194444444444449</v>
       </c>
       <c r="C130" s="47" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="D130" s="87" t="s">
         <v>59</v>
@@ -11281,7 +11281,7 @@
         <v>0.62222222222222223</v>
       </c>
       <c r="C131" s="21" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D131" s="89" t="s">
         <v>255</v>
@@ -11292,26 +11292,26 @@
     </row>
     <row r="132" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A132" s="169" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B132" s="170">
         <v>0.63194444444444442</v>
       </c>
       <c r="C132" s="22" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D132" s="88"/>
       <c r="E132" s="106"/>
     </row>
     <row r="133" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A133" s="169" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B133" s="170">
         <v>0.66319444444444442</v>
       </c>
       <c r="C133" s="22" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D133" s="88"/>
       <c r="E133" s="106"/>

--- a/ESD2026.xlsx
+++ b/ESD2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17640" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17640"/>
   </bookViews>
   <sheets>
     <sheet name="Evolve April 15 - 19" sheetId="1" r:id="rId1"/>
@@ -342,9 +342,6 @@
     <t>Advanced Mini Hip Hop Solo</t>
   </si>
   <si>
-    <t>Lose Control</t>
-  </si>
-  <si>
     <t>Stella Knowler</t>
   </si>
   <si>
@@ -1833,6 +1830,9 @@
   </si>
   <si>
     <t>Eloise Baker, Annabella Beeroo, Ava Jagusch, Madison Jones, Stella Knowler, Quincy Knowler, Melody Lefebvre, Keira McCurdy, Aurora O'Connor, Claire Stretch, Maria Sushko, Philippa Tam, Emmy Thomson, Ellery Watts, Brixton Wright</t>
+  </si>
+  <si>
+    <t>Loose Control</t>
   </si>
 </sst>
 </file>
@@ -3255,7 +3255,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>6</v>
@@ -3391,7 +3391,7 @@
     </row>
     <row r="12" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A12" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B12" s="28">
         <v>0.61805555555555558</v>
@@ -4090,27 +4090,27 @@
         <v>102</v>
       </c>
       <c r="D54" s="21" t="s">
+        <v>596</v>
+      </c>
+      <c r="E54" s="21" t="s">
         <v>103</v>
-      </c>
-      <c r="E54" s="21" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="62" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B55" s="20">
         <v>0.71180555555555547</v>
       </c>
       <c r="C55" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="D55" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="D55" s="21" t="s">
+      <c r="E55" s="21" t="s">
         <v>107</v>
-      </c>
-      <c r="E55" s="21" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4121,13 +4121,13 @@
         <v>0.71319444444444446</v>
       </c>
       <c r="C56" s="21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D56" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="E56" s="21" t="s">
         <v>109</v>
-      </c>
-      <c r="E56" s="21" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4138,13 +4138,13 @@
         <v>0.72222222222222221</v>
       </c>
       <c r="C57" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="D57" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="D57" s="21" t="s">
+      <c r="E57" s="21" t="s">
         <v>112</v>
-      </c>
-      <c r="E57" s="21" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4155,13 +4155,13 @@
         <v>0.72430555555555554</v>
       </c>
       <c r="C58" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="D58" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="D58" s="21" t="s">
+      <c r="E58" s="21" t="s">
         <v>115</v>
-      </c>
-      <c r="E58" s="21" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4172,30 +4172,30 @@
         <v>0.72638888888888886</v>
       </c>
       <c r="C59" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="D59" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="D59" s="21" t="s">
+      <c r="E59" s="21" t="s">
         <v>118</v>
-      </c>
-      <c r="E59" s="21" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A60" s="62" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B60" s="20">
         <v>0.75208333333333333</v>
       </c>
       <c r="C60" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="D60" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="D60" s="21" t="s">
-        <v>122</v>
-      </c>
       <c r="E60" s="21" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4206,13 +4206,13 @@
         <v>0.75416666666666676</v>
       </c>
       <c r="C61" s="21" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D61" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="E61" s="21" t="s">
         <v>123</v>
-      </c>
-      <c r="E61" s="21" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4223,13 +4223,13 @@
         <v>0.75763888888888886</v>
       </c>
       <c r="C62" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="D62" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="D62" s="21" t="s">
+      <c r="E62" s="21" t="s">
         <v>126</v>
-      </c>
-      <c r="E62" s="21" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4257,13 +4257,13 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="C64" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="D64" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="D64" s="21" t="s">
+      <c r="E64" s="21" t="s">
         <v>129</v>
-      </c>
-      <c r="E64" s="21" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4274,10 +4274,10 @@
         <v>0.86319444444444438</v>
       </c>
       <c r="C65" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="D65" s="21" t="s">
         <v>131</v>
-      </c>
-      <c r="D65" s="21" t="s">
-        <v>132</v>
       </c>
       <c r="E65" s="21" t="s">
         <v>53</v>
@@ -4302,7 +4302,7 @@
     </row>
     <row r="67" spans="1:5" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A67" s="15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B67" s="16"/>
       <c r="C67" s="34"/>
@@ -4321,13 +4321,13 @@
         <v>0.45694444444444443</v>
       </c>
       <c r="C68" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="D68" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="D68" s="21" t="s">
-        <v>135</v>
-      </c>
       <c r="E68" s="21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4338,10 +4338,10 @@
         <v>0.47083333333333338</v>
       </c>
       <c r="C69" s="47" t="s">
+        <v>135</v>
+      </c>
+      <c r="D69" s="21" t="s">
         <v>136</v>
-      </c>
-      <c r="D69" s="21" t="s">
-        <v>137</v>
       </c>
       <c r="E69" s="21" t="s">
         <v>98</v>
@@ -4355,13 +4355,13 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="C70" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="D70" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="D70" s="21" t="s">
+      <c r="E70" s="21" t="s">
         <v>139</v>
-      </c>
-      <c r="E70" s="21" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4372,13 +4372,13 @@
         <v>0.48125000000000001</v>
       </c>
       <c r="C71" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="D71" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="D71" s="21" t="s">
+      <c r="E71" s="21" t="s">
         <v>142</v>
-      </c>
-      <c r="E71" s="21" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4406,13 +4406,13 @@
         <v>0.52777777777777779</v>
       </c>
       <c r="C73" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="D73" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="D73" s="21" t="s">
+      <c r="E73" s="21" t="s">
         <v>145</v>
-      </c>
-      <c r="E73" s="21" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4423,13 +4423,13 @@
         <v>0.5395833333333333</v>
       </c>
       <c r="C74" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="D74" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="D74" s="21" t="s">
+      <c r="E74" s="21" t="s">
         <v>148</v>
-      </c>
-      <c r="E74" s="21" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4440,13 +4440,13 @@
         <v>0.55138888888888882</v>
       </c>
       <c r="C75" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="D75" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="D75" s="21" t="s">
+      <c r="E75" s="21" t="s">
         <v>151</v>
-      </c>
-      <c r="E75" s="21" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4457,13 +4457,13 @@
         <v>0.56111111111111112</v>
       </c>
       <c r="C76" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="D76" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="D76" s="21" t="s">
+      <c r="E76" s="21" t="s">
         <v>154</v>
-      </c>
-      <c r="E76" s="21" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4474,13 +4474,13 @@
         <v>0.58472222222222225</v>
       </c>
       <c r="C77" s="47" t="s">
+        <v>155</v>
+      </c>
+      <c r="D77" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="D77" s="21" t="s">
+      <c r="E77" s="21" t="s">
         <v>157</v>
-      </c>
-      <c r="E77" s="21" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4491,13 +4491,13 @@
         <v>0.59236111111111112</v>
       </c>
       <c r="C78" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="D78" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="D78" s="21" t="s">
+      <c r="E78" s="21" t="s">
         <v>160</v>
-      </c>
-      <c r="E78" s="21" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4508,13 +4508,13 @@
         <v>0.60972222222222217</v>
       </c>
       <c r="C79" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="D79" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="D79" s="21" t="s">
+      <c r="E79" s="21" t="s">
         <v>163</v>
-      </c>
-      <c r="E79" s="21" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4525,13 +4525,13 @@
         <v>0.6118055555555556</v>
       </c>
       <c r="C80" s="21" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D80" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="E80" s="21" t="s">
         <v>165</v>
-      </c>
-      <c r="E80" s="21" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
@@ -4564,7 +4564,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" s="58" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B83" s="43"/>
       <c r="C83" s="44"/>
@@ -4577,7 +4577,7 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" s="58" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B84" s="43"/>
       <c r="C84" s="44"/>
@@ -4590,7 +4590,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" s="58" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B85" s="43"/>
       <c r="C85" s="44"/>
@@ -4603,7 +4603,7 @@
     </row>
     <row r="86" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A86" s="59" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B86" s="38"/>
       <c r="C86" s="39"/>
@@ -4622,13 +4622,13 @@
         <v>0.71111111111111114</v>
       </c>
       <c r="C87" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="D87" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="D87" s="21" t="s">
-        <v>172</v>
-      </c>
       <c r="E87" s="21" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4639,10 +4639,10 @@
         <v>0.74791666666666667</v>
       </c>
       <c r="C88" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="D88" s="21" t="s">
         <v>173</v>
-      </c>
-      <c r="D88" s="21" t="s">
-        <v>174</v>
       </c>
       <c r="E88" s="21" t="s">
         <v>28</v>
@@ -4659,10 +4659,10 @@
         <v>58</v>
       </c>
       <c r="D89" s="21" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E89" s="21" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4690,10 +4690,10 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="C91" s="21" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D91" s="21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E91" s="21" t="s">
         <v>55</v>
@@ -4707,10 +4707,10 @@
         <v>0.83958333333333324</v>
       </c>
       <c r="C92" s="26" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D92" s="21" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E92" s="21" t="s">
         <v>57</v>
@@ -4746,7 +4746,7 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" s="58" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B95" s="43"/>
       <c r="C95" s="44"/>
@@ -4759,7 +4759,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" s="58" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B96" s="43"/>
       <c r="C96" s="44"/>
@@ -4772,7 +4772,7 @@
     </row>
     <row r="97" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A97" s="64" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B97" s="65"/>
       <c r="C97" s="66"/>
@@ -4785,7 +4785,7 @@
     </row>
     <row r="98" spans="1:5" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A98" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B98" s="16"/>
       <c r="C98" s="34"/>
@@ -4804,13 +4804,13 @@
         <v>0.375</v>
       </c>
       <c r="C99" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="D99" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="D99" s="21" t="s">
+      <c r="E99" s="21" t="s">
         <v>183</v>
-      </c>
-      <c r="E99" s="21" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4821,30 +4821,30 @@
         <v>0.37847222222222227</v>
       </c>
       <c r="C100" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D100" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="D100" s="21" t="s">
+      <c r="E100" s="21" t="s">
         <v>186</v>
-      </c>
-      <c r="E100" s="21" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A101" s="69" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B101" s="20">
         <v>0.40138888888888885</v>
       </c>
       <c r="C101" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="D101" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="D101" s="21" t="s">
+      <c r="E101" s="21" t="s">
         <v>190</v>
-      </c>
-      <c r="E101" s="21" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4855,13 +4855,13 @@
         <v>0.40347222222222223</v>
       </c>
       <c r="C102" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="D102" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="D102" s="21" t="s">
+      <c r="E102" s="21" t="s">
         <v>193</v>
-      </c>
-      <c r="E102" s="21" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4872,13 +4872,13 @@
         <v>0.41319444444444442</v>
       </c>
       <c r="C103" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="D103" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="D103" s="21" t="s">
+      <c r="E103" s="21" t="s">
         <v>196</v>
-      </c>
-      <c r="E103" s="21" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4889,13 +4889,13 @@
         <v>0.42777777777777781</v>
       </c>
       <c r="C104" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="D104" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="D104" s="21" t="s">
+      <c r="E104" s="21" t="s">
         <v>199</v>
-      </c>
-      <c r="E104" s="21" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4906,13 +4906,13 @@
         <v>0.44444444444444442</v>
       </c>
       <c r="C105" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="D105" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="D105" s="21" t="s">
+      <c r="E105" s="21" t="s">
         <v>202</v>
-      </c>
-      <c r="E105" s="21" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4923,13 +4923,13 @@
         <v>0.4465277777777778</v>
       </c>
       <c r="C106" s="47" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D106" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="E106" s="21" t="s">
         <v>204</v>
-      </c>
-      <c r="E106" s="21" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4940,13 +4940,13 @@
         <v>0.47222222222222227</v>
       </c>
       <c r="C107" s="21" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D107" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="E107" s="21" t="s">
         <v>206</v>
-      </c>
-      <c r="E107" s="21" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
@@ -4968,7 +4968,7 @@
     </row>
     <row r="109" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A109" s="59" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B109" s="38"/>
       <c r="C109" s="39"/>
@@ -4987,13 +4987,13 @@
         <v>0.52638888888888891</v>
       </c>
       <c r="C110" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="D110" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="D110" s="21" t="s">
+      <c r="E110" s="21" t="s">
         <v>210</v>
-      </c>
-      <c r="E110" s="21" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
@@ -5018,7 +5018,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" s="58" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B113" s="43"/>
       <c r="C113" s="44"/>
@@ -5027,7 +5027,7 @@
     </row>
     <row r="114" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A114" s="59" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B114" s="38"/>
       <c r="C114" s="39"/>
@@ -5055,7 +5055,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -5064,10 +5064,10 @@
     </row>
     <row r="2" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="78" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C2" s="79"/>
       <c r="D2" s="80"/>
@@ -5075,7 +5075,7 @@
     </row>
     <row r="3" spans="1:5" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="81" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>4</v>
@@ -5084,7 +5084,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E3" s="82" t="s">
         <v>6</v>
@@ -5092,7 +5092,7 @@
     </row>
     <row r="4" spans="1:5" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="83" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B4" s="84"/>
       <c r="C4" s="84"/>
@@ -5107,13 +5107,13 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="C5" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="D5" s="77" t="s">
+        <v>192</v>
+      </c>
+      <c r="E5" s="72" t="s">
         <v>219</v>
-      </c>
-      <c r="D5" s="77" t="s">
-        <v>193</v>
-      </c>
-      <c r="E5" s="72" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -5124,13 +5124,13 @@
         <v>0.42083333333333334</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D6" s="77" t="s">
+        <v>189</v>
+      </c>
+      <c r="E6" s="72" t="s">
         <v>190</v>
-      </c>
-      <c r="E6" s="72" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -5141,7 +5141,7 @@
         <v>0.42499999999999999</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D7" s="77" t="s">
         <v>44</v>
@@ -5158,7 +5158,7 @@
         <v>0.4291666666666667</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D8" s="77" t="s">
         <v>17</v>
@@ -5175,10 +5175,10 @@
         <v>0.43541666666666662</v>
       </c>
       <c r="C9" s="26" t="s">
+        <v>222</v>
+      </c>
+      <c r="D9" s="87" t="s">
         <v>223</v>
-      </c>
-      <c r="D9" s="87" t="s">
-        <v>224</v>
       </c>
       <c r="E9" s="72" t="s">
         <v>37</v>
@@ -5186,13 +5186,13 @@
     </row>
     <row r="10" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B10" s="23">
         <v>0.4375</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D10" s="88"/>
       <c r="E10" s="25"/>
@@ -5205,10 +5205,10 @@
         <v>0.49305555555555558</v>
       </c>
       <c r="C11" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="D11" s="77" t="s">
         <v>226</v>
-      </c>
-      <c r="D11" s="77" t="s">
-        <v>227</v>
       </c>
       <c r="E11" s="72" t="s">
         <v>35</v>
@@ -5222,24 +5222,24 @@
         <v>0.50416666666666665</v>
       </c>
       <c r="C12" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="D12" s="77" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" s="72" t="s">
         <v>228</v>
-      </c>
-      <c r="D12" s="77" t="s">
-        <v>109</v>
-      </c>
-      <c r="E12" s="72" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B13" s="23">
         <v>0.50694444444444442</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D13" s="88"/>
       <c r="E13" s="25"/>
@@ -5252,7 +5252,7 @@
         <v>0.53125</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D14" s="87" t="s">
         <v>25</v>
@@ -5269,7 +5269,7 @@
         <v>0.54861111111111105</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D15" s="77" t="s">
         <v>12</v>
@@ -5280,13 +5280,13 @@
     </row>
     <row r="16" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B16" s="23">
         <v>0.55555555555555558</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D16" s="88"/>
       <c r="E16" s="25"/>
@@ -5299,13 +5299,13 @@
         <v>0.55902777777777779</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D17" s="77" t="s">
+        <v>162</v>
+      </c>
+      <c r="E17" s="72" t="s">
         <v>163</v>
-      </c>
-      <c r="E17" s="72" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -5316,13 +5316,13 @@
         <v>0.56041666666666667</v>
       </c>
       <c r="C18" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="D18" s="77" t="s">
         <v>232</v>
       </c>
-      <c r="D18" s="77" t="s">
-        <v>233</v>
-      </c>
       <c r="E18" s="72" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -5333,7 +5333,7 @@
         <v>0.5625</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D19" s="77" t="s">
         <v>47</v>
@@ -5350,13 +5350,13 @@
         <v>0.56458333333333333</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D20" s="77" t="s">
+        <v>106</v>
+      </c>
+      <c r="E20" s="72" t="s">
         <v>107</v>
-      </c>
-      <c r="E20" s="72" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -5367,7 +5367,7 @@
         <v>0.56666666666666665</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D21" s="77" t="s">
         <v>97</v>
@@ -5384,7 +5384,7 @@
         <v>0.5708333333333333</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D22" s="77" t="s">
         <v>30</v>
@@ -5401,7 +5401,7 @@
         <v>0.57291666666666663</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D23" s="77" t="s">
         <v>56</v>
@@ -5418,10 +5418,10 @@
         <v>0.57500000000000007</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D24" s="89" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E24" s="72" t="s">
         <v>28</v>
@@ -5435,7 +5435,7 @@
         <v>0.57638888888888895</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D25" s="77" t="s">
         <v>54</v>
@@ -5452,10 +5452,10 @@
         <v>0.57777777777777783</v>
       </c>
       <c r="C26" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="D26" s="77" t="s">
         <v>240</v>
-      </c>
-      <c r="D26" s="77" t="s">
-        <v>241</v>
       </c>
       <c r="E26" s="72" t="s">
         <v>53</v>
@@ -5469,24 +5469,24 @@
         <v>0.57916666666666672</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D27" s="77" t="s">
+        <v>128</v>
+      </c>
+      <c r="E27" s="72" t="s">
         <v>129</v>
-      </c>
-      <c r="E27" s="72" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B28" s="23">
         <v>0.59027777777777779</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D28" s="88"/>
       <c r="E28" s="25"/>
@@ -5499,24 +5499,24 @@
         <v>0.59375</v>
       </c>
       <c r="C29" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="D29" s="77" t="s">
         <v>243</v>
       </c>
-      <c r="D29" s="77" t="s">
+      <c r="E29" s="72" t="s">
         <v>244</v>
-      </c>
-      <c r="E29" s="72" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B30" s="23">
         <v>0.61458333333333337</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D30" s="88"/>
       <c r="E30" s="25"/>
@@ -5529,13 +5529,13 @@
         <v>0.73611111111111116</v>
       </c>
       <c r="C31" s="47" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D31" s="90" t="s">
+        <v>182</v>
+      </c>
+      <c r="E31" s="72" t="s">
         <v>183</v>
-      </c>
-      <c r="E31" s="72" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -5546,13 +5546,13 @@
         <v>0.73749999999999993</v>
       </c>
       <c r="C32" s="47" t="s">
+        <v>246</v>
+      </c>
+      <c r="D32" s="90" t="s">
+        <v>185</v>
+      </c>
+      <c r="E32" s="72" t="s">
         <v>247</v>
-      </c>
-      <c r="D32" s="90" t="s">
-        <v>186</v>
-      </c>
-      <c r="E32" s="72" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -5563,24 +5563,24 @@
         <v>0.73958333333333337</v>
       </c>
       <c r="C33" s="47" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D33" s="90" t="s">
         <v>78</v>
       </c>
       <c r="E33" s="72" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B34" s="23">
         <v>0.75555555555555554</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D34" s="88"/>
       <c r="E34" s="25"/>
@@ -5593,13 +5593,13 @@
         <v>0.76041666666666663</v>
       </c>
       <c r="C35" s="47" t="s">
+        <v>250</v>
+      </c>
+      <c r="D35" s="90" t="s">
         <v>251</v>
       </c>
-      <c r="D35" s="90" t="s">
+      <c r="E35" s="72" t="s">
         <v>252</v>
-      </c>
-      <c r="E35" s="72" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -5610,24 +5610,24 @@
         <v>0.77430555555555547</v>
       </c>
       <c r="C36" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="D36" s="90" t="s">
         <v>254</v>
       </c>
-      <c r="D36" s="90" t="s">
-        <v>255</v>
-      </c>
       <c r="E36" s="72" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B37" s="23">
         <v>0.77916666666666667</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D37" s="88"/>
       <c r="E37" s="25"/>
@@ -5640,24 +5640,24 @@
         <v>0.78472222222222221</v>
       </c>
       <c r="C38" s="47" t="s">
+        <v>255</v>
+      </c>
+      <c r="D38" s="90" t="s">
         <v>256</v>
       </c>
-      <c r="D38" s="90" t="s">
+      <c r="E38" s="72" t="s">
         <v>257</v>
-      </c>
-      <c r="E38" s="72" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B39" s="23">
         <v>0.80763888888888891</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D39" s="88"/>
       <c r="E39" s="25"/>
@@ -5670,7 +5670,7 @@
         <v>0.88888888888888884</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D40" s="90" t="s">
         <v>60</v>
@@ -5687,7 +5687,7 @@
         <v>0.89027777777777783</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D41" s="90" t="s">
         <v>59</v>
@@ -5704,31 +5704,31 @@
         <v>0.89166666666666661</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D42" s="90" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E42" s="72" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B43" s="23">
         <v>0.89930555555555547</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D43" s="88"/>
       <c r="E43" s="25"/>
     </row>
     <row r="44" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="91" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B44" s="92"/>
       <c r="C44" s="92"/>
@@ -5743,10 +5743,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C45" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="D45" s="94" t="s">
         <v>262</v>
-      </c>
-      <c r="D45" s="94" t="s">
-        <v>263</v>
       </c>
       <c r="E45" s="72" t="s">
         <v>43</v>
@@ -5760,7 +5760,7 @@
         <v>0.34027777777777773</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D46" s="94" t="s">
         <v>40</v>
@@ -5771,13 +5771,13 @@
     </row>
     <row r="47" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B47" s="23">
         <v>0.36041666666666666</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D47" s="88"/>
       <c r="E47" s="25"/>
@@ -5790,7 +5790,7 @@
         <v>0.46875</v>
       </c>
       <c r="C48" s="26" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D48" s="94" t="s">
         <v>94</v>
@@ -5807,13 +5807,13 @@
         <v>0.47083333333333338</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D49" s="94" t="s">
+        <v>156</v>
+      </c>
+      <c r="E49" s="72" t="s">
         <v>157</v>
-      </c>
-      <c r="E49" s="72" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -5824,13 +5824,13 @@
         <v>0.47361111111111115</v>
       </c>
       <c r="C50" s="26" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D50" s="94" t="s">
+        <v>141</v>
+      </c>
+      <c r="E50" s="72" t="s">
         <v>142</v>
-      </c>
-      <c r="E50" s="72" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -5841,24 +5841,24 @@
         <v>0.4826388888888889</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D51" s="94" t="s">
+        <v>209</v>
+      </c>
+      <c r="E51" s="72" t="s">
         <v>210</v>
-      </c>
-      <c r="E51" s="72" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B52" s="23">
         <v>0.48958333333333331</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D52" s="88"/>
       <c r="E52" s="25"/>
@@ -5871,7 +5871,7 @@
         <v>0.5</v>
       </c>
       <c r="C53" s="26" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D53" s="94" t="s">
         <v>66</v>
@@ -5882,13 +5882,13 @@
     </row>
     <row r="54" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A54" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B54" s="23">
         <v>0.52152777777777781</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D54" s="88"/>
       <c r="E54" s="25"/>
@@ -5901,13 +5901,13 @@
         <v>0.63194444444444442</v>
       </c>
       <c r="C55" s="26" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D55" s="94" t="s">
+        <v>159</v>
+      </c>
+      <c r="E55" s="72" t="s">
         <v>160</v>
-      </c>
-      <c r="E55" s="72" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -5918,13 +5918,13 @@
         <v>0.63541666666666663</v>
       </c>
       <c r="C56" s="26" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D56" s="94" t="s">
+        <v>153</v>
+      </c>
+      <c r="E56" s="72" t="s">
         <v>154</v>
-      </c>
-      <c r="E56" s="72" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -5935,7 +5935,7 @@
         <v>0.63680555555555551</v>
       </c>
       <c r="C57" s="26" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D57" s="94" t="s">
         <v>50</v>
@@ -5952,24 +5952,24 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="C58" s="26" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D58" s="94" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E58" s="72" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A59" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B59" s="23">
         <v>0.65277777777777779</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D59" s="88"/>
       <c r="E59" s="25"/>
@@ -5982,31 +5982,31 @@
         <v>0.88541666666666663</v>
       </c>
       <c r="C60" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="D60" s="94" t="s">
         <v>274</v>
       </c>
-      <c r="D60" s="94" t="s">
+      <c r="E60" s="72" t="s">
         <v>275</v>
-      </c>
-      <c r="E60" s="72" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A61" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B61" s="23">
         <v>0.89513888888888893</v>
       </c>
       <c r="C61" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D61" s="88"/>
       <c r="E61" s="25"/>
     </row>
     <row r="62" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A62" s="91" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B62" s="92"/>
       <c r="C62" s="73"/>
@@ -6021,10 +6021,10 @@
         <v>0.39930555555555558</v>
       </c>
       <c r="C63" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="D63" s="94" t="s">
         <v>278</v>
-      </c>
-      <c r="D63" s="94" t="s">
-        <v>279</v>
       </c>
       <c r="E63" s="72" t="s">
         <v>53</v>
@@ -6038,10 +6038,10 @@
         <v>0.40069444444444446</v>
       </c>
       <c r="C64" s="26" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D64" s="94" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E64" s="72" t="s">
         <v>55</v>
@@ -6049,13 +6049,13 @@
     </row>
     <row r="65" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A65" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B65" s="23">
         <v>0.4236111111111111</v>
       </c>
       <c r="C65" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D65" s="88"/>
       <c r="E65" s="25"/>
@@ -6068,13 +6068,13 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="C66" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D66" s="94" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E66" s="72" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -6085,13 +6085,13 @@
         <v>0.4284722222222222</v>
       </c>
       <c r="C67" s="26" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D67" s="94" t="s">
+        <v>144</v>
+      </c>
+      <c r="E67" s="72" t="s">
         <v>145</v>
-      </c>
-      <c r="E67" s="72" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -6102,10 +6102,10 @@
         <v>0.43194444444444446</v>
       </c>
       <c r="C68" s="26" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D68" s="94" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E68" s="72" t="s">
         <v>98</v>
@@ -6119,10 +6119,10 @@
         <v>0.4375</v>
       </c>
       <c r="C69" s="26" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D69" s="94" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E69" s="72" t="s">
         <v>57</v>
@@ -6130,13 +6130,13 @@
     </row>
     <row r="70" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A70" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B70" s="23">
         <v>0.44791666666666669</v>
       </c>
       <c r="C70" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D70" s="88"/>
       <c r="E70" s="25"/>
@@ -6149,7 +6149,7 @@
         <v>0.52777777777777779</v>
       </c>
       <c r="C71" s="26" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D71" s="87" t="s">
         <v>9</v>
@@ -6166,24 +6166,24 @@
         <v>0.52916666666666667</v>
       </c>
       <c r="C72" s="26" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D72" s="87" t="s">
+        <v>111</v>
+      </c>
+      <c r="E72" s="72" t="s">
         <v>112</v>
-      </c>
-      <c r="E72" s="72" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A73" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B73" s="23">
         <v>0.55555555555555558</v>
       </c>
       <c r="C73" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D73" s="88"/>
       <c r="E73" s="25"/>
@@ -6196,7 +6196,7 @@
         <v>0.5625</v>
       </c>
       <c r="C74" s="26" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D74" s="94" t="s">
         <v>81</v>
@@ -6207,13 +6207,13 @@
     </row>
     <row r="75" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B75" s="23">
         <v>0.57986111111111105</v>
       </c>
       <c r="C75" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D75" s="88"/>
       <c r="E75" s="25"/>
@@ -6226,7 +6226,7 @@
         <v>0.58680555555555558</v>
       </c>
       <c r="C76" s="26" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D76" s="94" t="s">
         <v>72</v>
@@ -6237,13 +6237,13 @@
     </row>
     <row r="77" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B77" s="23">
         <v>0.6069444444444444</v>
       </c>
       <c r="C77" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D77" s="88"/>
       <c r="E77" s="25"/>
@@ -6256,13 +6256,13 @@
         <v>0.61111111111111105</v>
       </c>
       <c r="C78" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="D78" s="94" t="s">
         <v>287</v>
       </c>
-      <c r="D78" s="94" t="s">
-        <v>288</v>
-      </c>
       <c r="E78" s="72" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -6273,13 +6273,13 @@
         <v>0.61319444444444449</v>
       </c>
       <c r="C79" s="26" t="s">
+        <v>288</v>
+      </c>
+      <c r="D79" s="94" t="s">
+        <v>150</v>
+      </c>
+      <c r="E79" s="72" t="s">
         <v>289</v>
-      </c>
-      <c r="D79" s="94" t="s">
-        <v>151</v>
-      </c>
-      <c r="E79" s="72" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -6290,13 +6290,13 @@
         <v>0.61736111111111114</v>
       </c>
       <c r="C80" s="26" t="s">
+        <v>290</v>
+      </c>
+      <c r="D80" s="94" t="s">
         <v>291</v>
       </c>
-      <c r="D80" s="94" t="s">
-        <v>292</v>
-      </c>
       <c r="E80" s="72" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -6307,24 +6307,24 @@
         <v>0.62847222222222221</v>
       </c>
       <c r="C81" s="26" t="s">
+        <v>292</v>
+      </c>
+      <c r="D81" s="94" t="s">
         <v>293</v>
       </c>
-      <c r="D81" s="94" t="s">
-        <v>294</v>
-      </c>
       <c r="E81" s="72" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B82" s="23">
         <v>0.63194444444444442</v>
       </c>
       <c r="C82" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D82" s="88"/>
       <c r="E82" s="25"/>
@@ -6337,24 +6337,24 @@
         <v>0.63888888888888895</v>
       </c>
       <c r="C83" s="26" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D83" s="94" t="s">
+        <v>201</v>
+      </c>
+      <c r="E83" s="72" t="s">
         <v>202</v>
-      </c>
-      <c r="E83" s="72" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A84" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B84" s="23">
         <v>0.65625</v>
       </c>
       <c r="C84" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D84" s="88"/>
       <c r="E84" s="25"/>
@@ -6367,24 +6367,24 @@
         <v>0.66319444444444442</v>
       </c>
       <c r="C85" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="D85" s="94" t="s">
         <v>296</v>
       </c>
-      <c r="D85" s="94" t="s">
-        <v>297</v>
-      </c>
       <c r="E85" s="72" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A86" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B86" s="23">
         <v>0.68819444444444444</v>
       </c>
       <c r="C86" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D86" s="88"/>
       <c r="E86" s="25"/>
@@ -6397,13 +6397,13 @@
         <v>0.69444444444444453</v>
       </c>
       <c r="C87" s="26" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D87" s="94" t="s">
+        <v>596</v>
+      </c>
+      <c r="E87" s="72" t="s">
         <v>103</v>
-      </c>
-      <c r="E87" s="72" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -6414,7 +6414,7 @@
         <v>0.69861111111111107</v>
       </c>
       <c r="C88" s="26" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D88" s="94" t="s">
         <v>100</v>
@@ -6425,13 +6425,13 @@
     </row>
     <row r="89" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A89" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B89" s="23">
         <v>0.71180555555555547</v>
       </c>
       <c r="C89" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D89" s="88"/>
       <c r="E89" s="25"/>
@@ -6444,13 +6444,13 @@
         <v>0.74305555555555547</v>
       </c>
       <c r="C90" s="26" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D90" s="94" t="s">
+        <v>195</v>
+      </c>
+      <c r="E90" s="72" t="s">
         <v>196</v>
-      </c>
-      <c r="E90" s="72" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -6461,10 +6461,10 @@
         <v>0.74513888888888891</v>
       </c>
       <c r="C91" s="26" t="s">
+        <v>299</v>
+      </c>
+      <c r="D91" s="94" t="s">
         <v>300</v>
-      </c>
-      <c r="D91" s="94" t="s">
-        <v>301</v>
       </c>
       <c r="E91" s="72" t="s">
         <v>64</v>
@@ -6478,7 +6478,7 @@
         <v>0.74722222222222223</v>
       </c>
       <c r="C92" s="26" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D92" s="94" t="s">
         <v>22</v>
@@ -6489,13 +6489,13 @@
     </row>
     <row r="93" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A93" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B93" s="23">
         <v>0.75694444444444453</v>
       </c>
       <c r="C93" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D93" s="88"/>
       <c r="E93" s="25"/>
@@ -6508,7 +6508,7 @@
         <v>0.76388888888888884</v>
       </c>
       <c r="C94" s="26" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D94" s="94" t="s">
         <v>20</v>
@@ -6525,24 +6525,24 @@
         <v>0.77222222222222225</v>
       </c>
       <c r="C95" s="26" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D95" s="94" t="s">
+        <v>125</v>
+      </c>
+      <c r="E95" s="72" t="s">
         <v>126</v>
-      </c>
-      <c r="E95" s="72" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A96" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B96" s="23">
         <v>0.78263888888888899</v>
       </c>
       <c r="C96" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D96" s="88"/>
       <c r="E96" s="25"/>
@@ -6555,24 +6555,24 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="C97" s="26" t="s">
+        <v>304</v>
+      </c>
+      <c r="D97" s="94" t="s">
         <v>305</v>
       </c>
-      <c r="D97" s="94" t="s">
+      <c r="E97" s="72" t="s">
         <v>306</v>
-      </c>
-      <c r="E97" s="72" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A98" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B98" s="23">
         <v>0.79861111111111116</v>
       </c>
       <c r="C98" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D98" s="88"/>
       <c r="E98" s="25"/>
@@ -6585,13 +6585,13 @@
         <v>0.80555555555555547</v>
       </c>
       <c r="C99" s="47" t="s">
+        <v>307</v>
+      </c>
+      <c r="D99" s="94" t="s">
         <v>308</v>
       </c>
-      <c r="D99" s="94" t="s">
+      <c r="E99" s="72" t="s">
         <v>309</v>
-      </c>
-      <c r="E99" s="72" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6602,24 +6602,24 @@
         <v>0.80972222222222223</v>
       </c>
       <c r="C100" s="26" t="s">
+        <v>310</v>
+      </c>
+      <c r="D100" s="94" t="s">
         <v>311</v>
       </c>
-      <c r="D100" s="94" t="s">
+      <c r="E100" s="72" t="s">
         <v>312</v>
-      </c>
-      <c r="E100" s="72" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A101" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B101" s="23">
         <v>0.82708333333333339</v>
       </c>
       <c r="C101" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D101" s="88"/>
       <c r="E101" s="25"/>
@@ -6632,13 +6632,13 @@
         <v>0.86458333333333337</v>
       </c>
       <c r="C102" s="74" t="s">
+        <v>313</v>
+      </c>
+      <c r="D102" s="99" t="s">
         <v>314</v>
       </c>
-      <c r="D102" s="99" t="s">
+      <c r="E102" s="75" t="s">
         <v>315</v>
-      </c>
-      <c r="E102" s="75" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6649,24 +6649,24 @@
         <v>0.875</v>
       </c>
       <c r="C103" s="26" t="s">
+        <v>316</v>
+      </c>
+      <c r="D103" s="94" t="s">
         <v>317</v>
       </c>
-      <c r="D103" s="94" t="s">
+      <c r="E103" s="72" t="s">
         <v>318</v>
-      </c>
-      <c r="E103" s="72" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A104" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B104" s="23">
         <v>0.88124999999999998</v>
       </c>
       <c r="C104" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D104" s="88"/>
       <c r="E104" s="25"/>
@@ -6679,31 +6679,31 @@
         <v>0.88888888888888884</v>
       </c>
       <c r="C105" s="26" t="s">
+        <v>319</v>
+      </c>
+      <c r="D105" s="94" t="s">
         <v>320</v>
       </c>
-      <c r="D105" s="94" t="s">
+      <c r="E105" s="72" t="s">
         <v>321</v>
-      </c>
-      <c r="E105" s="72" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A106" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B106" s="23">
         <v>0.90347222222222223</v>
       </c>
       <c r="C106" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D106" s="88"/>
       <c r="E106" s="25"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A107" s="91" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B107" s="92"/>
       <c r="C107" s="73"/>
@@ -6718,24 +6718,24 @@
         <v>0.3576388888888889</v>
       </c>
       <c r="C108" s="26" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D108" s="94" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E108" s="72" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A109" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B109" s="23">
         <v>0.37986111111111115</v>
       </c>
       <c r="C109" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D109" s="88"/>
       <c r="E109" s="25"/>
@@ -6748,13 +6748,13 @@
         <v>0.3888888888888889</v>
       </c>
       <c r="C110" s="26" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D110" s="94" t="s">
+        <v>198</v>
+      </c>
+      <c r="E110" s="72" t="s">
         <v>199</v>
-      </c>
-      <c r="E110" s="72" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -6765,10 +6765,10 @@
         <v>0.39097222222222222</v>
       </c>
       <c r="C111" s="26" t="s">
+        <v>325</v>
+      </c>
+      <c r="D111" s="94" t="s">
         <v>326</v>
-      </c>
-      <c r="D111" s="94" t="s">
-        <v>327</v>
       </c>
       <c r="E111" s="72" t="s">
         <v>88</v>
@@ -6782,7 +6782,7 @@
         <v>0.40625</v>
       </c>
       <c r="C112" s="26" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D112" s="94" t="s">
         <v>69</v>
@@ -6793,13 +6793,13 @@
     </row>
     <row r="113" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A113" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B113" s="23">
         <v>0.40763888888888888</v>
       </c>
       <c r="C113" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D113" s="88"/>
       <c r="E113" s="25"/>
@@ -6812,24 +6812,24 @@
         <v>0.4201388888888889</v>
       </c>
       <c r="C114" s="26" t="s">
+        <v>328</v>
+      </c>
+      <c r="D114" s="94" t="s">
         <v>329</v>
       </c>
-      <c r="D114" s="94" t="s">
+      <c r="E114" s="72" t="s">
         <v>330</v>
-      </c>
-      <c r="E114" s="72" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A115" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B115" s="23">
         <v>0.43402777777777773</v>
       </c>
       <c r="C115" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D115" s="88"/>
       <c r="E115" s="25"/>
@@ -6842,13 +6842,13 @@
         <v>0.44097222222222227</v>
       </c>
       <c r="C116" s="76" t="s">
+        <v>331</v>
+      </c>
+      <c r="D116" s="100" t="s">
         <v>332</v>
       </c>
-      <c r="D116" s="100" t="s">
+      <c r="E116" s="75" t="s">
         <v>333</v>
-      </c>
-      <c r="E116" s="75" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6859,13 +6859,13 @@
         <v>0.44305555555555554</v>
       </c>
       <c r="C117" s="76" t="s">
+        <v>334</v>
+      </c>
+      <c r="D117" s="100" t="s">
         <v>335</v>
       </c>
-      <c r="D117" s="100" t="s">
+      <c r="E117" s="75" t="s">
         <v>336</v>
-      </c>
-      <c r="E117" s="75" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
@@ -6876,24 +6876,24 @@
         <v>0.44513888888888892</v>
       </c>
       <c r="C118" s="76" t="s">
+        <v>337</v>
+      </c>
+      <c r="D118" s="99" t="s">
         <v>338</v>
       </c>
-      <c r="D118" s="99" t="s">
+      <c r="E118" s="75" t="s">
         <v>339</v>
-      </c>
-      <c r="E118" s="75" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A119" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B119" s="23">
         <v>0.45555555555555555</v>
       </c>
       <c r="C119" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D119" s="88"/>
       <c r="E119" s="25"/>
@@ -6906,13 +6906,13 @@
         <v>0.51736111111111105</v>
       </c>
       <c r="C120" s="76" t="s">
+        <v>340</v>
+      </c>
+      <c r="D120" s="100" t="s">
         <v>341</v>
       </c>
-      <c r="D120" s="100" t="s">
+      <c r="E120" s="75" t="s">
         <v>342</v>
-      </c>
-      <c r="E120" s="75" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6923,13 +6923,13 @@
         <v>0.52361111111111114</v>
       </c>
       <c r="C121" s="76" t="s">
+        <v>343</v>
+      </c>
+      <c r="D121" s="100" t="s">
         <v>344</v>
       </c>
-      <c r="D121" s="100" t="s">
+      <c r="E121" s="75" t="s">
         <v>345</v>
-      </c>
-      <c r="E121" s="75" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
@@ -6940,24 +6940,24 @@
         <v>0.52777777777777779</v>
       </c>
       <c r="C122" s="76" t="s">
+        <v>346</v>
+      </c>
+      <c r="D122" s="100" t="s">
         <v>347</v>
       </c>
-      <c r="D122" s="100" t="s">
-        <v>348</v>
-      </c>
       <c r="E122" s="75" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A123" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B123" s="23">
         <v>0.53055555555555556</v>
       </c>
       <c r="C123" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D123" s="88"/>
       <c r="E123" s="25"/>
@@ -6970,24 +6970,24 @@
         <v>0.53819444444444442</v>
       </c>
       <c r="C124" s="76" t="s">
+        <v>348</v>
+      </c>
+      <c r="D124" s="99" t="s">
         <v>349</v>
       </c>
-      <c r="D124" s="99" t="s">
+      <c r="E124" s="75" t="s">
         <v>350</v>
-      </c>
-      <c r="E124" s="75" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A125" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B125" s="23">
         <v>0.54513888888888895</v>
       </c>
       <c r="C125" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D125" s="88"/>
       <c r="E125" s="25"/>
@@ -7000,24 +7000,24 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="C126" s="47" t="s">
+        <v>351</v>
+      </c>
+      <c r="D126" s="94" t="s">
         <v>352</v>
       </c>
-      <c r="D126" s="94" t="s">
-        <v>353</v>
-      </c>
       <c r="E126" s="72" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A127" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B127" s="23">
         <v>0.56319444444444444</v>
       </c>
       <c r="C127" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D127" s="88"/>
       <c r="E127" s="25"/>
@@ -7030,13 +7030,13 @@
         <v>0.60069444444444442</v>
       </c>
       <c r="C128" s="76" t="s">
+        <v>353</v>
+      </c>
+      <c r="D128" s="100" t="s">
         <v>354</v>
       </c>
-      <c r="D128" s="100" t="s">
-        <v>355</v>
-      </c>
       <c r="E128" s="75" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
@@ -7047,24 +7047,24 @@
         <v>0.60763888888888895</v>
       </c>
       <c r="C129" s="76" t="s">
+        <v>355</v>
+      </c>
+      <c r="D129" s="99" t="s">
         <v>356</v>
       </c>
-      <c r="D129" s="99" t="s">
+      <c r="E129" s="75" t="s">
         <v>357</v>
-      </c>
-      <c r="E129" s="75" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A130" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B130" s="23">
         <v>0.61805555555555558</v>
       </c>
       <c r="C130" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D130" s="88"/>
       <c r="E130" s="25"/>
@@ -7077,13 +7077,13 @@
         <v>0.70138888888888884</v>
       </c>
       <c r="C131" s="76" t="s">
+        <v>358</v>
+      </c>
+      <c r="D131" s="100" t="s">
         <v>359</v>
       </c>
-      <c r="D131" s="100" t="s">
+      <c r="E131" s="75" t="s">
         <v>360</v>
-      </c>
-      <c r="E131" s="75" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
@@ -7094,24 +7094,24 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="C132" s="76" t="s">
+        <v>361</v>
+      </c>
+      <c r="D132" s="100" t="s">
         <v>362</v>
       </c>
-      <c r="D132" s="100" t="s">
+      <c r="E132" s="75" t="s">
         <v>363</v>
-      </c>
-      <c r="E132" s="75" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A133" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B133" s="23">
         <v>0.72013888888888899</v>
       </c>
       <c r="C133" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D133" s="88"/>
       <c r="E133" s="25"/>
@@ -7124,24 +7124,24 @@
         <v>0.76736111111111116</v>
       </c>
       <c r="C134" s="47" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D134" s="94" t="s">
+        <v>205</v>
+      </c>
+      <c r="E134" s="72" t="s">
         <v>206</v>
-      </c>
-      <c r="E134" s="72" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A135" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B135" s="23">
         <v>0.78125</v>
       </c>
       <c r="C135" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D135" s="88"/>
       <c r="E135" s="25"/>
@@ -7154,24 +7154,24 @@
         <v>0.78819444444444453</v>
       </c>
       <c r="C136" s="47" t="s">
+        <v>365</v>
+      </c>
+      <c r="D136" s="94" t="s">
         <v>366</v>
       </c>
-      <c r="D136" s="94" t="s">
+      <c r="E136" s="72" t="s">
         <v>367</v>
-      </c>
-      <c r="E136" s="72" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A137" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B137" s="23">
         <v>0.80902777777777779</v>
       </c>
       <c r="C137" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D137" s="88"/>
       <c r="E137" s="25"/>
@@ -7184,13 +7184,13 @@
         <v>0.81597222222222221</v>
       </c>
       <c r="C138" s="76" t="s">
+        <v>368</v>
+      </c>
+      <c r="D138" s="100" t="s">
         <v>369</v>
       </c>
-      <c r="D138" s="100" t="s">
-        <v>370</v>
-      </c>
       <c r="E138" s="75" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
@@ -7201,24 +7201,24 @@
         <v>0.82638888888888884</v>
       </c>
       <c r="C139" s="76" t="s">
+        <v>370</v>
+      </c>
+      <c r="D139" s="99" t="s">
         <v>371</v>
       </c>
-      <c r="D139" s="99" t="s">
+      <c r="E139" s="75" t="s">
         <v>372</v>
-      </c>
-      <c r="E139" s="75" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A140" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B140" s="23">
         <v>0.84375</v>
       </c>
       <c r="C140" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D140" s="88"/>
       <c r="E140" s="25"/>
@@ -7231,24 +7231,24 @@
         <v>0.85069444444444453</v>
       </c>
       <c r="C141" s="76" t="s">
+        <v>373</v>
+      </c>
+      <c r="D141" s="99" t="s">
         <v>374</v>
       </c>
-      <c r="D141" s="99" t="s">
+      <c r="E141" s="75" t="s">
         <v>375</v>
-      </c>
-      <c r="E141" s="75" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A142" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B142" s="23">
         <v>0.875</v>
       </c>
       <c r="C142" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D142" s="88"/>
       <c r="E142" s="25"/>
@@ -7261,7 +7261,7 @@
         <v>0.88194444444444453</v>
       </c>
       <c r="C143" s="47" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D143" s="94" t="s">
         <v>84</v>
@@ -7272,13 +7272,13 @@
     </row>
     <row r="144" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A144" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B144" s="23">
         <v>0.90277777777777779</v>
       </c>
       <c r="C144" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D144" s="88"/>
       <c r="E144" s="25"/>
@@ -7291,7 +7291,7 @@
         <v>0.90972222222222221</v>
       </c>
       <c r="C145" s="47" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D145" s="94" t="s">
         <v>27</v>
@@ -7302,20 +7302,20 @@
     </row>
     <row r="146" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A146" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B146" s="23">
         <v>0.93194444444444446</v>
       </c>
       <c r="C146" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D146" s="88"/>
       <c r="E146" s="25"/>
     </row>
     <row r="147" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A147" s="91" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B147" s="92"/>
       <c r="C147" s="73"/>
@@ -7330,24 +7330,24 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="C148" s="76" t="s">
+        <v>379</v>
+      </c>
+      <c r="D148" s="101" t="s">
         <v>380</v>
       </c>
-      <c r="D148" s="101" t="s">
-        <v>381</v>
-      </c>
       <c r="E148" s="75" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A149" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B149" s="23">
         <v>0.46875</v>
       </c>
       <c r="C149" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D149" s="88"/>
       <c r="E149" s="25"/>
@@ -7360,24 +7360,24 @@
         <v>0.61111111111111105</v>
       </c>
       <c r="C150" s="76" t="s">
+        <v>381</v>
+      </c>
+      <c r="D150" s="101" t="s">
         <v>382</v>
       </c>
-      <c r="D150" s="101" t="s">
-        <v>383</v>
-      </c>
       <c r="E150" s="75" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A151" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B151" s="23">
         <v>0.63194444444444442</v>
       </c>
       <c r="C151" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D151" s="88"/>
       <c r="E151" s="25"/>
@@ -7390,7 +7390,7 @@
         <v>0.63888888888888895</v>
       </c>
       <c r="C152" s="47" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D152" s="89" t="s">
         <v>75</v>
@@ -7401,13 +7401,13 @@
     </row>
     <row r="153" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A153" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B153" s="23">
         <v>0.66666666666666663</v>
       </c>
       <c r="C153" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D153" s="88"/>
       <c r="E153" s="25"/>
@@ -7420,48 +7420,48 @@
         <v>0.69444444444444453</v>
       </c>
       <c r="C154" s="47" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D154" s="89" t="s">
+        <v>114</v>
+      </c>
+      <c r="E154" s="72" t="s">
         <v>115</v>
-      </c>
-      <c r="E154" s="72" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A155" s="48" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B155" s="49">
         <v>0.70277777777777783</v>
       </c>
       <c r="C155" s="48" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D155" s="102"/>
       <c r="E155" s="51"/>
     </row>
     <row r="156" spans="1:5" ht="64.5" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A156" s="103" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B156" s="104">
         <v>0.70833333333333337</v>
       </c>
       <c r="C156" s="105" t="s">
+        <v>355</v>
+      </c>
+      <c r="D156" s="105" t="s">
         <v>356</v>
       </c>
-      <c r="D156" s="105" t="s">
-        <v>357</v>
-      </c>
       <c r="E156" s="75" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A157" s="22" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B157" s="106"/>
       <c r="C157" s="22"/>
@@ -7488,7 +7488,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="122" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B1" s="107"/>
       <c r="C1" s="5"/>
@@ -7497,10 +7497,10 @@
     </row>
     <row r="2" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="B2" s="78" t="s">
         <v>390</v>
-      </c>
-      <c r="B2" s="78" t="s">
-        <v>391</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
@@ -7517,7 +7517,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>6</v>
@@ -7525,7 +7525,7 @@
     </row>
     <row r="4" spans="1:5" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="124" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B4" s="84"/>
       <c r="C4" s="84"/>
@@ -7540,13 +7540,13 @@
         <v>0.49027777777777781</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D5" s="89" t="s">
+        <v>125</v>
+      </c>
+      <c r="E5" s="108" t="s">
         <v>126</v>
-      </c>
-      <c r="E5" s="108" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -7557,7 +7557,7 @@
         <v>0.49444444444444446</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D6" s="125" t="s">
         <v>20</v>
@@ -7574,13 +7574,13 @@
         <v>0.50763888888888886</v>
       </c>
       <c r="C7" s="74" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D7" s="128" t="s">
+        <v>141</v>
+      </c>
+      <c r="E7" s="109" t="s">
         <v>142</v>
-      </c>
-      <c r="E7" s="109" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -7591,13 +7591,13 @@
         <v>0.62291666666666667</v>
       </c>
       <c r="C8" s="21" t="s">
+        <v>395</v>
+      </c>
+      <c r="D8" s="125" t="s">
         <v>396</v>
       </c>
-      <c r="D8" s="125" t="s">
-        <v>397</v>
-      </c>
       <c r="E8" s="108" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -7608,13 +7608,13 @@
         <v>0.625</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D9" s="125" t="s">
+        <v>153</v>
+      </c>
+      <c r="E9" s="111" t="s">
         <v>154</v>
-      </c>
-      <c r="E9" s="111" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -7625,13 +7625,13 @@
         <v>0.62847222222222221</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D10" s="125" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E10" s="108" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -7642,7 +7642,7 @@
         <v>0.64444444444444449</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D11" s="131" t="s">
         <v>50</v>
@@ -7659,7 +7659,7 @@
         <v>0.67361111111111116</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D12" s="77" t="s">
         <v>100</v>
@@ -7676,13 +7676,13 @@
         <v>0.76527777777777783</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D13" s="132" t="s">
+        <v>128</v>
+      </c>
+      <c r="E13" s="111" t="s">
         <v>129</v>
-      </c>
-      <c r="E13" s="111" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
@@ -7693,13 +7693,13 @@
         <v>0.78680555555555554</v>
       </c>
       <c r="C14" s="109" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D14" s="135" t="s">
+        <v>314</v>
+      </c>
+      <c r="E14" s="75" t="s">
         <v>315</v>
-      </c>
-      <c r="E14" s="75" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7710,13 +7710,13 @@
         <v>0.7895833333333333</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D15" s="89" t="s">
+        <v>317</v>
+      </c>
+      <c r="E15" s="72" t="s">
         <v>318</v>
-      </c>
-      <c r="E15" s="72" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -7727,7 +7727,7 @@
         <v>0.8354166666666667</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D16" s="125" t="s">
         <v>60</v>
@@ -7744,13 +7744,13 @@
         <v>0.84166666666666667</v>
       </c>
       <c r="C17" s="47" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D17" s="131" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E17" s="111" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -7761,7 +7761,7 @@
         <v>0.84305555555555556</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D18" s="131" t="s">
         <v>59</v>
@@ -7778,18 +7778,18 @@
         <v>0.85833333333333339</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D19" s="77" t="s">
+        <v>320</v>
+      </c>
+      <c r="E19" s="72" t="s">
         <v>321</v>
-      </c>
-      <c r="E19" s="72" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="140" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B20" s="92"/>
       <c r="C20" s="92"/>
@@ -7804,13 +7804,13 @@
         <v>0.3888888888888889</v>
       </c>
       <c r="C21" s="76" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D21" s="141" t="s">
+        <v>338</v>
+      </c>
+      <c r="E21" s="75" t="s">
         <v>339</v>
-      </c>
-      <c r="E21" s="75" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="64.5" thickBot="1" x14ac:dyDescent="0.2">
@@ -7821,13 +7821,13 @@
         <v>0.39097222222222222</v>
       </c>
       <c r="C22" s="109" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D22" s="100" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E22" s="75" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.25">
@@ -7838,13 +7838,13 @@
         <v>0.3923611111111111</v>
       </c>
       <c r="C23" s="109" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D23" s="135" t="s">
+        <v>344</v>
+      </c>
+      <c r="E23" s="75" t="s">
         <v>345</v>
-      </c>
-      <c r="E23" s="75" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
@@ -7855,47 +7855,47 @@
         <v>0.40277777777777773</v>
       </c>
       <c r="C24" s="109" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D24" s="135" t="s">
+        <v>341</v>
+      </c>
+      <c r="E24" s="75" t="s">
         <v>342</v>
-      </c>
-      <c r="E24" s="75" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="144" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B25" s="20">
         <v>0.4069444444444445</v>
       </c>
       <c r="C25" s="47" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D25" s="131" t="s">
         <v>94</v>
       </c>
       <c r="E25" s="108" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="144" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B26" s="20">
         <v>0.40972222222222227</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D26" s="89" t="s">
+        <v>156</v>
+      </c>
+      <c r="E26" s="108" t="s">
         <v>157</v>
-      </c>
-      <c r="E26" s="108" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="12.75" x14ac:dyDescent="0.15">
@@ -7906,18 +7906,18 @@
         <v>0.41805555555555557</v>
       </c>
       <c r="C27" s="109" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D27" s="125" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E27" s="109" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A28" s="146" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B28" s="129"/>
       <c r="C28" s="110"/>
@@ -7932,18 +7932,18 @@
         <v>0.4201388888888889</v>
       </c>
       <c r="C29" s="76" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D29" s="141" t="s">
+        <v>356</v>
+      </c>
+      <c r="E29" s="75" t="s">
         <v>357</v>
-      </c>
-      <c r="E29" s="75" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="147" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B30" s="142"/>
       <c r="C30" s="112"/>
@@ -7958,7 +7958,7 @@
         <v>0.4680555555555555</v>
       </c>
       <c r="C31" s="109" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D31" s="125" t="s">
         <v>27</v>
@@ -7969,7 +7969,7 @@
     </row>
     <row r="32" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A32" s="146" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B32" s="129"/>
       <c r="C32" s="110"/>
@@ -7984,18 +7984,18 @@
         <v>0.47361111111111115</v>
       </c>
       <c r="C33" s="76" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D33" s="141" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E33" s="75" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="147" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B34" s="149"/>
       <c r="C34" s="112"/>
@@ -8010,13 +8010,13 @@
         <v>0.55069444444444449</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D35" s="89" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E35" s="72" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8027,10 +8027,10 @@
         <v>0.56180555555555556</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D36" s="125" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E36" s="108" t="s">
         <v>98</v>
@@ -8038,19 +8038,19 @@
     </row>
     <row r="37" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="144" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B37" s="139">
         <v>0.58333333333333337</v>
       </c>
       <c r="C37" s="47" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D37" s="125" t="s">
+        <v>209</v>
+      </c>
+      <c r="E37" s="108" t="s">
         <v>210</v>
-      </c>
-      <c r="E37" s="108" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8061,13 +8061,13 @@
         <v>0.60486111111111118</v>
       </c>
       <c r="C38" s="47" t="s">
+        <v>427</v>
+      </c>
+      <c r="D38" s="131" t="s">
+        <v>182</v>
+      </c>
+      <c r="E38" s="108" t="s">
         <v>428</v>
-      </c>
-      <c r="D38" s="131" t="s">
-        <v>183</v>
-      </c>
-      <c r="E38" s="108" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8078,13 +8078,13 @@
         <v>0.6069444444444444</v>
       </c>
       <c r="C39" s="47" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D39" s="125" t="s">
+        <v>185</v>
+      </c>
+      <c r="E39" s="108" t="s">
         <v>186</v>
-      </c>
-      <c r="E39" s="108" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8095,7 +8095,7 @@
         <v>0.61041666666666672</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D40" s="125" t="s">
         <v>78</v>
@@ -8112,30 +8112,30 @@
         <v>0.62152777777777779</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D41" s="125" t="s">
+        <v>192</v>
+      </c>
+      <c r="E41" s="108" t="s">
         <v>193</v>
-      </c>
-      <c r="E41" s="108" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="144" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B42" s="139">
         <v>0.62569444444444444</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D42" s="125" t="s">
+        <v>189</v>
+      </c>
+      <c r="E42" s="111" t="s">
         <v>190</v>
-      </c>
-      <c r="E42" s="111" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8146,7 +8146,7 @@
         <v>0.62708333333333333</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D43" s="125" t="s">
         <v>44</v>
@@ -8163,7 +8163,7 @@
         <v>0.62916666666666665</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D44" s="132" t="s">
         <v>17</v>
@@ -8180,13 +8180,13 @@
         <v>0.64027777777777783</v>
       </c>
       <c r="C45" s="109" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D45" s="135" t="s">
+        <v>332</v>
+      </c>
+      <c r="E45" s="75" t="s">
         <v>333</v>
-      </c>
-      <c r="E45" s="75" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.25">
@@ -8197,13 +8197,13 @@
         <v>0.64652777777777781</v>
       </c>
       <c r="C46" s="109" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D46" s="101" t="s">
+        <v>335</v>
+      </c>
+      <c r="E46" s="72" t="s">
         <v>336</v>
-      </c>
-      <c r="E46" s="72" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8214,10 +8214,10 @@
         <v>0.65347222222222223</v>
       </c>
       <c r="C47" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="D47" s="131" t="s">
         <v>440</v>
-      </c>
-      <c r="D47" s="131" t="s">
-        <v>441</v>
       </c>
       <c r="E47" s="111" t="s">
         <v>37</v>
@@ -8231,10 +8231,10 @@
         <v>0.65555555555555556</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D48" s="131" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E48" s="111" t="s">
         <v>35</v>
@@ -8248,13 +8248,13 @@
         <v>0.70208333333333339</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D49" s="125" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E49" s="111" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
@@ -8265,30 +8265,30 @@
         <v>0.77500000000000002</v>
       </c>
       <c r="C50" s="76" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D50" s="141" t="s">
+        <v>374</v>
+      </c>
+      <c r="E50" s="75" t="s">
         <v>375</v>
-      </c>
-      <c r="E50" s="75" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="144" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B51" s="139">
         <v>0.79513888888888884</v>
       </c>
       <c r="C51" s="47" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D51" s="125" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E51" s="111" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8299,10 +8299,10 @@
         <v>0.84375</v>
       </c>
       <c r="C52" s="47" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D52" s="132" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E52" s="111" t="s">
         <v>57</v>
@@ -8316,10 +8316,10 @@
         <v>0.85625000000000007</v>
       </c>
       <c r="C53" s="47" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D53" s="125" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E53" s="111" t="s">
         <v>53</v>
@@ -8333,10 +8333,10 @@
         <v>0.85763888888888884</v>
       </c>
       <c r="C54" s="47" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D54" s="125" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E54" s="111" t="s">
         <v>55</v>
@@ -8344,7 +8344,7 @@
     </row>
     <row r="55" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="140" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B55" s="92"/>
       <c r="C55" s="34"/>
@@ -8359,13 +8359,13 @@
         <v>0.37916666666666665</v>
       </c>
       <c r="C56" s="115" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D56" s="135" t="s">
+        <v>359</v>
+      </c>
+      <c r="E56" s="75" t="s">
         <v>360</v>
-      </c>
-      <c r="E56" s="75" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
@@ -8376,13 +8376,13 @@
         <v>0.38958333333333334</v>
       </c>
       <c r="C57" s="115" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D57" s="141" t="s">
+        <v>362</v>
+      </c>
+      <c r="E57" s="75" t="s">
         <v>363</v>
-      </c>
-      <c r="E57" s="75" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8393,13 +8393,13 @@
         <v>0.41250000000000003</v>
       </c>
       <c r="C58" s="114" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D58" s="125" t="s">
+        <v>201</v>
+      </c>
+      <c r="E58" s="111" t="s">
         <v>202</v>
-      </c>
-      <c r="E58" s="111" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8410,13 +8410,13 @@
         <v>0.4145833333333333</v>
       </c>
       <c r="C59" s="115" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D59" s="158" t="s">
+        <v>195</v>
+      </c>
+      <c r="E59" s="74" t="s">
         <v>196</v>
-      </c>
-      <c r="E59" s="74" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8427,10 +8427,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="C60" s="115" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D60" s="125" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E60" s="116" t="s">
         <v>64</v>
@@ -8444,7 +8444,7 @@
         <v>0.41875000000000001</v>
       </c>
       <c r="C61" s="115" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D61" s="125" t="s">
         <v>22</v>
@@ -8461,13 +8461,13 @@
         <v>0.42083333333333334</v>
       </c>
       <c r="C62" s="114" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D62" s="77" t="s">
+        <v>596</v>
+      </c>
+      <c r="E62" s="111" t="s">
         <v>103</v>
-      </c>
-      <c r="E62" s="111" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -8478,13 +8478,13 @@
         <v>0.42499999999999999</v>
       </c>
       <c r="C63" s="115" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D63" s="141" t="s">
+        <v>308</v>
+      </c>
+      <c r="E63" s="116" t="s">
         <v>309</v>
-      </c>
-      <c r="E63" s="116" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.25">
@@ -8495,13 +8495,13 @@
         <v>0.43611111111111112</v>
       </c>
       <c r="C64" s="115" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D64" s="135" t="s">
+        <v>311</v>
+      </c>
+      <c r="E64" s="116" t="s">
         <v>312</v>
-      </c>
-      <c r="E64" s="116" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="51" x14ac:dyDescent="0.2">
@@ -8512,24 +8512,24 @@
         <v>0.4381944444444445</v>
       </c>
       <c r="C65" s="117" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D65" s="141" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E65" s="75" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A66" s="157" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B66" s="139">
         <v>0.47569444444444442</v>
       </c>
       <c r="C66" s="119" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D66" s="125" t="s">
         <v>81</v>
@@ -8546,7 +8546,7 @@
         <v>0.4777777777777778</v>
       </c>
       <c r="C67" s="117" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D67" s="131" t="s">
         <v>72</v>
@@ -8557,7 +8557,7 @@
     </row>
     <row r="68" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A68" s="157" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B68" s="150"/>
       <c r="C68" s="118"/>
@@ -8572,7 +8572,7 @@
         <v>0.48749999999999999</v>
       </c>
       <c r="C69" s="119" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D69" s="125" t="s">
         <v>84</v>
@@ -8589,13 +8589,13 @@
         <v>0.49374999999999997</v>
       </c>
       <c r="C70" s="117" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D70" s="141" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E70" s="75" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
@@ -8606,13 +8606,13 @@
         <v>0.52708333333333335</v>
       </c>
       <c r="C71" s="117" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D71" s="141" t="s">
+        <v>256</v>
+      </c>
+      <c r="E71" s="116" t="s">
         <v>257</v>
-      </c>
-      <c r="E71" s="116" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8623,13 +8623,13 @@
         <v>0.60138888888888886</v>
       </c>
       <c r="C72" s="119" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D72" s="89" t="s">
+        <v>366</v>
+      </c>
+      <c r="E72" s="72" t="s">
         <v>367</v>
-      </c>
-      <c r="E72" s="72" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -8640,13 +8640,13 @@
         <v>0.64166666666666672</v>
       </c>
       <c r="C73" s="119" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D73" s="87" t="s">
+        <v>251</v>
+      </c>
+      <c r="E73" s="72" t="s">
         <v>252</v>
-      </c>
-      <c r="E73" s="72" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8657,13 +8657,13 @@
         <v>0.6791666666666667</v>
       </c>
       <c r="C74" s="119" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D74" s="131" t="s">
+        <v>114</v>
+      </c>
+      <c r="E74" s="108" t="s">
         <v>115</v>
-      </c>
-      <c r="E74" s="108" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8674,7 +8674,7 @@
         <v>0.68888888888888899</v>
       </c>
       <c r="C75" s="119" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D75" s="132" t="s">
         <v>69</v>
@@ -8691,13 +8691,13 @@
         <v>0.79513888888888884</v>
       </c>
       <c r="C76" s="120" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D76" s="125" t="s">
+        <v>198</v>
+      </c>
+      <c r="E76" s="108" t="s">
         <v>199</v>
-      </c>
-      <c r="E76" s="108" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8708,13 +8708,13 @@
         <v>0.80486111111111114</v>
       </c>
       <c r="C77" s="119" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D77" s="125" t="s">
+        <v>205</v>
+      </c>
+      <c r="E77" s="108" t="s">
         <v>206</v>
-      </c>
-      <c r="E77" s="108" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8725,7 +8725,7 @@
         <v>0.80694444444444446</v>
       </c>
       <c r="C78" s="119" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D78" s="125" t="s">
         <v>75</v>
@@ -8742,18 +8742,18 @@
         <v>0.86249999999999993</v>
       </c>
       <c r="C79" s="117" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D79" s="141" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E79" s="75" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A80" s="140" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B80" s="92"/>
       <c r="C80" s="34"/>
@@ -8768,7 +8768,7 @@
         <v>0.3840277777777778</v>
       </c>
       <c r="C81" s="21" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D81" s="132" t="s">
         <v>40</v>
@@ -8785,10 +8785,10 @@
         <v>0.38611111111111113</v>
       </c>
       <c r="C82" s="21" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D82" s="131" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E82" s="72" t="s">
         <v>43</v>
@@ -8802,13 +8802,13 @@
         <v>0.41111111111111115</v>
       </c>
       <c r="C83" s="21" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D83" s="132" t="s">
+        <v>243</v>
+      </c>
+      <c r="E83" s="72" t="s">
         <v>244</v>
-      </c>
-      <c r="E83" s="72" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8819,10 +8819,10 @@
         <v>0.42499999999999999</v>
       </c>
       <c r="C84" s="26" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D84" s="125" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E84" s="72" t="s">
         <v>88</v>
@@ -8836,7 +8836,7 @@
         <v>0.4284722222222222</v>
       </c>
       <c r="C85" s="21" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D85" s="125" t="s">
         <v>66</v>
@@ -8853,13 +8853,13 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="C86" s="21" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D86" s="125" t="s">
+        <v>108</v>
+      </c>
+      <c r="E86" s="108" t="s">
         <v>109</v>
-      </c>
-      <c r="E86" s="108" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8870,13 +8870,13 @@
         <v>0.4597222222222222</v>
       </c>
       <c r="C87" s="21" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D87" s="125" t="s">
+        <v>106</v>
+      </c>
+      <c r="E87" s="111" t="s">
         <v>107</v>
-      </c>
-      <c r="E87" s="111" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
@@ -8887,7 +8887,7 @@
         <v>0.46111111111111108</v>
       </c>
       <c r="C88" s="21" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D88" s="125" t="s">
         <v>47</v>
@@ -8904,13 +8904,13 @@
         <v>0.46319444444444446</v>
       </c>
       <c r="C89" s="21" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D89" s="131" t="s">
+        <v>162</v>
+      </c>
+      <c r="E89" s="108" t="s">
         <v>163</v>
-      </c>
-      <c r="E89" s="108" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8921,13 +8921,13 @@
         <v>0.46527777777777773</v>
       </c>
       <c r="C90" s="21" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D90" s="131" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E90" s="111" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="12.75" x14ac:dyDescent="0.15">
@@ -8938,13 +8938,13 @@
         <v>0.47222222222222227</v>
       </c>
       <c r="C91" s="109" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D91" s="99" t="s">
+        <v>150</v>
+      </c>
+      <c r="E91" s="116" t="s">
         <v>151</v>
-      </c>
-      <c r="E91" s="116" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8955,13 +8955,13 @@
         <v>0.47569444444444442</v>
       </c>
       <c r="C92" s="21" t="s">
+        <v>478</v>
+      </c>
+      <c r="D92" s="132" t="s">
+        <v>111</v>
+      </c>
+      <c r="E92" s="111" t="s">
         <v>479</v>
-      </c>
-      <c r="D92" s="132" t="s">
-        <v>112</v>
-      </c>
-      <c r="E92" s="111" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8972,13 +8972,13 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="C93" s="74" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D93" s="125" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E93" s="109" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -8989,7 +8989,7 @@
         <v>0.48333333333333334</v>
       </c>
       <c r="C94" s="109" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D94" s="135" t="s">
         <v>9</v>
@@ -9006,13 +9006,13 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="C95" s="74" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D95" s="131" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E95" s="109" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -9023,7 +9023,7 @@
         <v>0.49305555555555558</v>
       </c>
       <c r="C96" s="21" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D96" s="125" t="s">
         <v>97</v>
@@ -9040,7 +9040,7 @@
         <v>0.49652777777777773</v>
       </c>
       <c r="C97" s="26" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D97" s="125" t="s">
         <v>30</v>
@@ -9057,13 +9057,13 @@
         <v>0.5</v>
       </c>
       <c r="C98" s="21" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D98" s="125" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E98" s="111" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -9074,13 +9074,13 @@
         <v>0.50208333333333333</v>
       </c>
       <c r="C99" s="26" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D99" s="125" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E99" s="108" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -9091,13 +9091,13 @@
         <v>0.50624999999999998</v>
       </c>
       <c r="C100" s="21" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D100" s="125" t="s">
+        <v>144</v>
+      </c>
+      <c r="E100" s="111" t="s">
         <v>145</v>
-      </c>
-      <c r="E100" s="111" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -9108,10 +9108,10 @@
         <v>0.51736111111111105</v>
       </c>
       <c r="C101" s="26" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D101" s="125" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E101" s="108" t="s">
         <v>28</v>
@@ -9125,7 +9125,7 @@
         <v>0.51944444444444449</v>
       </c>
       <c r="C102" s="21" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D102" s="131" t="s">
         <v>25</v>
@@ -9142,10 +9142,10 @@
         <v>0.52361111111111114</v>
       </c>
       <c r="C103" s="26" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D103" s="125" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E103" s="108" t="s">
         <v>53</v>
@@ -9159,7 +9159,7 @@
         <v>0.58888888888888891</v>
       </c>
       <c r="C104" s="26" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D104" s="132" t="s">
         <v>56</v>
@@ -9176,7 +9176,7 @@
         <v>0.59166666666666667</v>
       </c>
       <c r="C105" s="47" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D105" s="125" t="s">
         <v>12</v>
@@ -9193,7 +9193,7 @@
         <v>0.59375</v>
       </c>
       <c r="C106" s="26" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D106" s="131" t="s">
         <v>54</v>
@@ -9204,7 +9204,7 @@
     </row>
     <row r="107" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A107" s="162" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B107" s="21"/>
       <c r="C107" s="21"/>
@@ -9231,10 +9231,10 @@
   <sheetData>
     <row r="1" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="176" t="s">
+        <v>494</v>
+      </c>
+      <c r="B1" s="177" t="s">
         <v>495</v>
-      </c>
-      <c r="B1" s="177" t="s">
-        <v>496</v>
       </c>
       <c r="C1" s="164"/>
       <c r="D1" s="135"/>
@@ -9242,7 +9242,7 @@
     </row>
     <row r="2" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="178" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B2" s="179"/>
       <c r="C2" s="165"/>
@@ -9260,7 +9260,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="184" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>6</v>
@@ -9268,7 +9268,7 @@
     </row>
     <row r="4" spans="1:5" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A4" s="185" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B4" s="186"/>
       <c r="C4" s="186"/>
@@ -9283,13 +9283,13 @@
         <v>0.34583333333333338</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D5" s="89" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E5" s="108" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
@@ -9300,13 +9300,13 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D6" s="89" t="s">
+        <v>156</v>
+      </c>
+      <c r="E6" s="108" t="s">
         <v>157</v>
-      </c>
-      <c r="E6" s="108" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
@@ -9317,13 +9317,13 @@
         <v>0.35902777777777778</v>
       </c>
       <c r="C7" s="76" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D7" s="135" t="s">
+        <v>341</v>
+      </c>
+      <c r="E7" s="75" t="s">
         <v>342</v>
-      </c>
-      <c r="E7" s="75" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -9341,7 +9341,7 @@
         <v>0.37847222222222227</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D9" s="89" t="s">
         <v>44</v>
@@ -9358,13 +9358,13 @@
         <v>0.38055555555555554</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D10" s="89" t="s">
+        <v>189</v>
+      </c>
+      <c r="E10" s="72" t="s">
         <v>190</v>
-      </c>
-      <c r="E10" s="72" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -9375,13 +9375,13 @@
         <v>0.40625</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D11" s="89" t="s">
+        <v>305</v>
+      </c>
+      <c r="E11" s="72" t="s">
         <v>306</v>
-      </c>
-      <c r="E11" s="72" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="38.25" x14ac:dyDescent="0.15">
@@ -9392,24 +9392,24 @@
         <v>0.4145833333333333</v>
       </c>
       <c r="C12" s="109" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D12" s="141" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E12" s="75" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="169" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B13" s="170">
         <v>0.41736111111111113</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D13" s="88"/>
       <c r="E13" s="166"/>
@@ -9422,41 +9422,41 @@
         <v>0.44722222222222219</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D14" s="89" t="s">
+        <v>108</v>
+      </c>
+      <c r="E14" s="111" t="s">
         <v>109</v>
-      </c>
-      <c r="E14" s="111" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="160" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B15" s="167">
         <v>0.44930555555555557</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D15" s="89" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15" s="111" t="s">
         <v>107</v>
-      </c>
-      <c r="E15" s="111" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="160" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B16" s="167">
         <v>0.4513888888888889</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D16" s="89" t="s">
         <v>47</v>
@@ -9473,13 +9473,13 @@
         <v>0.47083333333333338</v>
       </c>
       <c r="C17" s="47" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D17" s="77" t="s">
+        <v>243</v>
+      </c>
+      <c r="E17" s="111" t="s">
         <v>244</v>
-      </c>
-      <c r="E17" s="111" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
@@ -9490,7 +9490,7 @@
         <v>0.48541666666666666</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D18" s="89" t="s">
         <v>75</v>
@@ -9507,13 +9507,13 @@
         <v>0.48749999999999999</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D19" s="89" t="s">
+        <v>205</v>
+      </c>
+      <c r="E19" s="108" t="s">
         <v>206</v>
-      </c>
-      <c r="E19" s="108" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="25.5" x14ac:dyDescent="0.15">
@@ -9524,13 +9524,13 @@
         <v>0.50694444444444442</v>
       </c>
       <c r="C20" s="109" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D20" s="141" t="s">
+        <v>362</v>
+      </c>
+      <c r="E20" s="75" t="s">
         <v>363</v>
-      </c>
-      <c r="E20" s="75" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -9541,7 +9541,7 @@
         <v>0.5180555555555556</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D21" s="89" t="s">
         <v>100</v>
@@ -9552,13 +9552,13 @@
     </row>
     <row r="22" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="169" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B22" s="170">
         <v>0.52569444444444446</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D22" s="171"/>
       <c r="E22" s="25"/>
@@ -9569,7 +9569,7 @@
         <v>0.54999999999999993</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D23" s="88"/>
       <c r="E23" s="166"/>
@@ -9582,10 +9582,10 @@
         <v>0.5854166666666667</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D24" s="89" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E24" s="111" t="s">
         <v>88</v>
@@ -9599,7 +9599,7 @@
         <v>0.60833333333333328</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D25" s="89" t="s">
         <v>22</v>
@@ -9616,13 +9616,13 @@
         <v>0.61041666666666672</v>
       </c>
       <c r="C26" s="47" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D26" s="94" t="s">
+        <v>195</v>
+      </c>
+      <c r="E26" s="111" t="s">
         <v>196</v>
-      </c>
-      <c r="E26" s="111" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -9633,10 +9633,10 @@
         <v>0.62430555555555556</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D27" s="89" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E27" s="111" t="s">
         <v>28</v>
@@ -9644,13 +9644,13 @@
     </row>
     <row r="28" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="169" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B28" s="170">
         <v>0.65763888888888888</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D28" s="171"/>
       <c r="E28" s="166"/>
@@ -9663,10 +9663,10 @@
         <v>0.6875</v>
       </c>
       <c r="C29" s="47" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D29" s="87" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E29" s="121" t="s">
         <v>35</v>
@@ -9680,10 +9680,10 @@
         <v>0.69166666666666676</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D30" s="87" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E30" s="121" t="s">
         <v>37</v>
@@ -9697,13 +9697,13 @@
         <v>0.69374999999999998</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D31" s="87" t="s">
+        <v>162</v>
+      </c>
+      <c r="E31" s="121" t="s">
         <v>163</v>
-      </c>
-      <c r="E31" s="121" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -9714,13 +9714,13 @@
         <v>0.6958333333333333</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D32" s="87" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E32" s="108" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -9731,7 +9731,7 @@
         <v>0.71111111111111114</v>
       </c>
       <c r="C33" s="47" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D33" s="87" t="s">
         <v>72</v>
@@ -9748,7 +9748,7 @@
         <v>0.74791666666666667</v>
       </c>
       <c r="C34" s="47" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D34" s="87" t="s">
         <v>50</v>
@@ -9759,13 +9759,13 @@
     </row>
     <row r="35" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="169" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B35" s="170">
         <v>0.76874999999999993</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D35" s="88"/>
       <c r="E35" s="166"/>
@@ -9776,7 +9776,7 @@
         <v>0.79305555555555562</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D36" s="171"/>
       <c r="E36" s="25"/>
@@ -9789,31 +9789,31 @@
         <v>0.8222222222222223</v>
       </c>
       <c r="C37" s="109" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D37" s="141" t="s">
+        <v>374</v>
+      </c>
+      <c r="E37" s="75" t="s">
         <v>375</v>
-      </c>
-      <c r="E37" s="75" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="169" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B38" s="170">
         <v>0.88611111111111107</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D38" s="171"/>
       <c r="E38" s="25"/>
     </row>
     <row r="39" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="173" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B39" s="174"/>
       <c r="C39" s="175"/>
@@ -9828,7 +9828,7 @@
         <v>0.34166666666666662</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D40" s="89" t="s">
         <v>78</v>
@@ -9845,13 +9845,13 @@
         <v>0.35000000000000003</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D41" s="89" t="s">
+        <v>366</v>
+      </c>
+      <c r="E41" s="72" t="s">
         <v>367</v>
-      </c>
-      <c r="E41" s="72" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -9862,7 +9862,7 @@
         <v>0.36458333333333331</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D42" s="89" t="s">
         <v>66</v>
@@ -9879,13 +9879,13 @@
         <v>0.36874999999999997</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D43" s="89" t="s">
+        <v>153</v>
+      </c>
+      <c r="E43" s="111" t="s">
         <v>154</v>
-      </c>
-      <c r="E43" s="111" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
@@ -9896,24 +9896,24 @@
         <v>0.38194444444444442</v>
       </c>
       <c r="C44" s="76" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D44" s="135" t="s">
+        <v>344</v>
+      </c>
+      <c r="E44" s="75" t="s">
         <v>345</v>
-      </c>
-      <c r="E44" s="75" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="169" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B45" s="170">
         <v>0.41597222222222219</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D45" s="88"/>
       <c r="E45" s="166"/>
@@ -9926,13 +9926,13 @@
         <v>0.44027777777777777</v>
       </c>
       <c r="C46" s="76" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D46" s="135" t="s">
+        <v>314</v>
+      </c>
+      <c r="E46" s="75" t="s">
         <v>315</v>
-      </c>
-      <c r="E46" s="75" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -9943,13 +9943,13 @@
         <v>0.4604166666666667</v>
       </c>
       <c r="C47" s="47" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D47" s="89" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E47" s="108" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
@@ -9960,13 +9960,13 @@
         <v>0.47083333333333338</v>
       </c>
       <c r="C48" s="76" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D48" s="141" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E48" s="75" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -9977,7 +9977,7 @@
         <v>0.47361111111111115</v>
       </c>
       <c r="C49" s="47" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D49" s="77" t="s">
         <v>40</v>
@@ -9994,10 +9994,10 @@
         <v>0.4777777777777778</v>
       </c>
       <c r="C50" s="47" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D50" s="87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E50" s="72" t="s">
         <v>43</v>
@@ -10011,13 +10011,13 @@
         <v>0.49236111111111108</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D51" s="87" t="s">
+        <v>114</v>
+      </c>
+      <c r="E51" s="108" t="s">
         <v>115</v>
-      </c>
-      <c r="E51" s="108" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -10028,7 +10028,7 @@
         <v>0.50486111111111109</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D52" s="87" t="s">
         <v>54</v>
@@ -10045,7 +10045,7 @@
         <v>0.50694444444444442</v>
       </c>
       <c r="C53" s="47" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D53" s="87" t="s">
         <v>25</v>
@@ -10062,13 +10062,13 @@
         <v>0.52013888888888882</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D54" s="89" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E54" s="108" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="51" x14ac:dyDescent="0.15">
@@ -10079,24 +10079,24 @@
         <v>0.52222222222222225</v>
       </c>
       <c r="C55" s="109" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D55" s="141" t="s">
+        <v>356</v>
+      </c>
+      <c r="E55" s="75" t="s">
         <v>357</v>
-      </c>
-      <c r="E55" s="75" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A56" s="169" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B56" s="170">
         <v>0.52500000000000002</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D56" s="88"/>
       <c r="E56" s="106"/>
@@ -10107,7 +10107,7 @@
         <v>0.5493055555555556</v>
       </c>
       <c r="C57" s="22" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D57" s="171"/>
       <c r="E57" s="25"/>
@@ -10120,13 +10120,13 @@
         <v>0.57013888888888886</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D58" s="89" t="s">
+        <v>256</v>
+      </c>
+      <c r="E58" s="72" t="s">
         <v>257</v>
-      </c>
-      <c r="E58" s="72" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -10137,7 +10137,7 @@
         <v>0.57291666666666663</v>
       </c>
       <c r="C59" s="47" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D59" s="77" t="s">
         <v>69</v>
@@ -10154,13 +10154,13 @@
         <v>0.60138888888888886</v>
       </c>
       <c r="C60" s="109" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D60" s="141" t="s">
+        <v>141</v>
+      </c>
+      <c r="E60" s="109" t="s">
         <v>142</v>
-      </c>
-      <c r="E60" s="109" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -10171,13 +10171,13 @@
         <v>0.61388888888888882</v>
       </c>
       <c r="C61" s="47" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D61" s="77" t="s">
+        <v>311</v>
+      </c>
+      <c r="E61" s="72" t="s">
         <v>312</v>
-      </c>
-      <c r="E61" s="72" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
@@ -10188,7 +10188,7 @@
         <v>0.61875000000000002</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D62" s="89" t="s">
         <v>12</v>
@@ -10205,7 +10205,7 @@
         <v>0.65069444444444446</v>
       </c>
       <c r="C63" s="47" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D63" s="89" t="s">
         <v>20</v>
@@ -10216,13 +10216,13 @@
     </row>
     <row r="64" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A64" s="169" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B64" s="170">
         <v>0.65833333333333333</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D64" s="88"/>
       <c r="E64" s="106"/>
@@ -10235,13 +10235,13 @@
         <v>0.69166666666666676</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D65" s="89" t="s">
+        <v>596</v>
+      </c>
+      <c r="E65" s="108" t="s">
         <v>103</v>
-      </c>
-      <c r="E65" s="108" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
@@ -10252,13 +10252,13 @@
         <v>0.69930555555555562</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D66" s="89" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E66" s="108" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
@@ -10269,13 +10269,13 @@
         <v>0.70347222222222217</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D67" s="89" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E67" s="108" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
@@ -10286,13 +10286,13 @@
         <v>0.70486111111111116</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D68" s="89" t="s">
+        <v>144</v>
+      </c>
+      <c r="E68" s="108" t="s">
         <v>145</v>
-      </c>
-      <c r="E68" s="108" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
@@ -10303,7 +10303,7 @@
         <v>0.72083333333333333</v>
       </c>
       <c r="C69" s="21" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D69" s="89" t="s">
         <v>97</v>
@@ -10314,13 +10314,13 @@
     </row>
     <row r="70" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A70" s="169" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B70" s="170">
         <v>0.76527777777777783</v>
       </c>
       <c r="C70" s="22" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D70" s="88"/>
       <c r="E70" s="106"/>
@@ -10331,7 +10331,7 @@
         <v>0.7895833333333333</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D71" s="88"/>
       <c r="E71" s="106"/>
@@ -10344,13 +10344,13 @@
         <v>0.84444444444444444</v>
       </c>
       <c r="C72" s="109" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D72" s="141" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E72" s="75" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="25.5" x14ac:dyDescent="0.15">
@@ -10361,31 +10361,31 @@
         <v>0.88263888888888886</v>
       </c>
       <c r="C73" s="109" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D73" s="141" t="s">
+        <v>371</v>
+      </c>
+      <c r="E73" s="75" t="s">
         <v>372</v>
-      </c>
-      <c r="E73" s="75" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A74" s="169" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B74" s="170">
         <v>0.88541666666666663</v>
       </c>
       <c r="C74" s="22" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D74" s="171"/>
       <c r="E74" s="25"/>
     </row>
     <row r="75" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A75" s="173" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B75" s="174"/>
       <c r="C75" s="175"/>
@@ -10400,7 +10400,7 @@
         <v>0.34583333333333338</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D76" s="89" t="s">
         <v>81</v>
@@ -10417,13 +10417,13 @@
         <v>0.34791666666666665</v>
       </c>
       <c r="C77" s="21" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D77" s="89" t="s">
+        <v>185</v>
+      </c>
+      <c r="E77" s="108" t="s">
         <v>186</v>
-      </c>
-      <c r="E77" s="108" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
@@ -10434,10 +10434,10 @@
         <v>0.36041666666666666</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D78" s="89" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E78" s="72" t="s">
         <v>64</v>
@@ -10451,13 +10451,13 @@
         <v>0.36249999999999999</v>
       </c>
       <c r="C79" s="21" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D79" s="89" t="s">
+        <v>125</v>
+      </c>
+      <c r="E79" s="108" t="s">
         <v>126</v>
-      </c>
-      <c r="E79" s="108" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -10468,13 +10468,13 @@
         <v>0.37847222222222227</v>
       </c>
       <c r="C80" s="47" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D80" s="77" t="s">
+        <v>128</v>
+      </c>
+      <c r="E80" s="111" t="s">
         <v>129</v>
-      </c>
-      <c r="E80" s="111" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
@@ -10485,13 +10485,13 @@
         <v>0.38958333333333334</v>
       </c>
       <c r="C81" s="21" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D81" s="89" t="s">
+        <v>329</v>
+      </c>
+      <c r="E81" s="72" t="s">
         <v>330</v>
-      </c>
-      <c r="E81" s="72" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="25.5" x14ac:dyDescent="0.15">
@@ -10502,24 +10502,24 @@
         <v>0.39513888888888887</v>
       </c>
       <c r="C82" s="109" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D82" s="141" t="s">
+        <v>338</v>
+      </c>
+      <c r="E82" s="75" t="s">
         <v>339</v>
-      </c>
-      <c r="E82" s="75" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A83" s="169" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B83" s="170">
         <v>0.41319444444444442</v>
       </c>
       <c r="C83" s="22" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D83" s="171"/>
       <c r="E83" s="25"/>
@@ -10532,13 +10532,13 @@
         <v>0.4916666666666667</v>
       </c>
       <c r="C84" s="21" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D84" s="89" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E84" s="108" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
@@ -10549,13 +10549,13 @@
         <v>0.99375000000000002</v>
       </c>
       <c r="C85" s="109" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D85" s="141" t="s">
+        <v>349</v>
+      </c>
+      <c r="E85" s="75" t="s">
         <v>350</v>
-      </c>
-      <c r="E85" s="75" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
@@ -10566,24 +10566,24 @@
         <v>0.50694444444444442</v>
       </c>
       <c r="C86" s="109" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D86" s="135" t="s">
+        <v>332</v>
+      </c>
+      <c r="E86" s="75" t="s">
         <v>333</v>
-      </c>
-      <c r="E86" s="75" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A87" s="169" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B87" s="170">
         <v>0.51736111111111105</v>
       </c>
       <c r="C87" s="22" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D87" s="88"/>
       <c r="E87" s="106"/>
@@ -10594,7 +10594,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C88" s="22" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D88" s="171"/>
       <c r="E88" s="25"/>
@@ -10607,7 +10607,7 @@
         <v>0.56666666666666665</v>
       </c>
       <c r="C89" s="47" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D89" s="77" t="s">
         <v>56</v>
@@ -10624,10 +10624,10 @@
         <v>0.56874999999999998</v>
       </c>
       <c r="C90" s="21" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D90" s="89" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E90" s="108" t="s">
         <v>53</v>
@@ -10641,13 +10641,13 @@
         <v>0.57291666666666663</v>
       </c>
       <c r="C91" s="21" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D91" s="89" t="s">
+        <v>192</v>
+      </c>
+      <c r="E91" s="108" t="s">
         <v>193</v>
-      </c>
-      <c r="E91" s="108" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -10658,7 +10658,7 @@
         <v>0.57500000000000007</v>
       </c>
       <c r="C92" s="47" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D92" s="77" t="s">
         <v>17</v>
@@ -10675,13 +10675,13 @@
         <v>0.5805555555555556</v>
       </c>
       <c r="C93" s="21" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D93" s="89" t="s">
+        <v>317</v>
+      </c>
+      <c r="E93" s="72" t="s">
         <v>318</v>
-      </c>
-      <c r="E93" s="72" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -10692,10 +10692,10 @@
         <v>0.58750000000000002</v>
       </c>
       <c r="C94" s="47" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D94" s="77" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E94" s="111" t="s">
         <v>57</v>
@@ -10709,13 +10709,13 @@
         <v>0.6</v>
       </c>
       <c r="C95" s="109" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D95" s="141" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E95" s="75" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="38.25" x14ac:dyDescent="0.15">
@@ -10726,24 +10726,24 @@
         <v>0.63680555555555551</v>
       </c>
       <c r="C96" s="109" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D96" s="141" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E96" s="75" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A97" s="169" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B97" s="170">
         <v>0.63750000000000007</v>
       </c>
       <c r="C97" s="22" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D97" s="171"/>
       <c r="E97" s="25"/>
@@ -10756,13 +10756,13 @@
         <v>0.67152777777777783</v>
       </c>
       <c r="C98" s="21" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D98" s="89" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E98" s="108" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
@@ -10773,13 +10773,13 @@
         <v>0.6777777777777777</v>
       </c>
       <c r="C99" s="76" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D99" s="135" t="s">
+        <v>359</v>
+      </c>
+      <c r="E99" s="75" t="s">
         <v>360</v>
-      </c>
-      <c r="E99" s="75" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
@@ -10790,13 +10790,13 @@
         <v>0.69374999999999998</v>
       </c>
       <c r="C100" s="21" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D100" s="89" t="s">
+        <v>274</v>
+      </c>
+      <c r="E100" s="72" t="s">
         <v>275</v>
-      </c>
-      <c r="E100" s="72" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
@@ -10807,10 +10807,10 @@
         <v>0.7055555555555556</v>
       </c>
       <c r="C101" s="21" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D101" s="89" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E101" s="108" t="s">
         <v>53</v>
@@ -10824,10 +10824,10 @@
         <v>0.70763888888888893</v>
       </c>
       <c r="C102" s="21" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D102" s="89" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E102" s="108" t="s">
         <v>55</v>
@@ -10841,13 +10841,13 @@
         <v>0.72361111111111109</v>
       </c>
       <c r="C103" s="21" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D103" s="89" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E103" s="108" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
@@ -10858,13 +10858,13 @@
         <v>0.72569444444444453</v>
       </c>
       <c r="C104" s="21" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D104" s="89" t="s">
+        <v>201</v>
+      </c>
+      <c r="E104" s="108" t="s">
         <v>202</v>
-      </c>
-      <c r="E104" s="108" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
@@ -10875,7 +10875,7 @@
         <v>0.73541666666666661</v>
       </c>
       <c r="C105" s="21" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D105" s="89" t="s">
         <v>30</v>
@@ -10892,7 +10892,7 @@
         <v>0.74513888888888891</v>
       </c>
       <c r="C106" s="21" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D106" s="89" t="s">
         <v>84</v>
@@ -10909,24 +10909,24 @@
         <v>0.74722222222222223</v>
       </c>
       <c r="C107" s="21" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D107" s="89" t="s">
+        <v>150</v>
+      </c>
+      <c r="E107" s="108" t="s">
         <v>151</v>
-      </c>
-      <c r="E107" s="108" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A108" s="169" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B108" s="170">
         <v>0.75208333333333333</v>
       </c>
       <c r="C108" s="22" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D108" s="88"/>
       <c r="E108" s="106"/>
@@ -10937,7 +10937,7 @@
         <v>0.77638888888888891</v>
       </c>
       <c r="C109" s="22" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D109" s="88"/>
       <c r="E109" s="106"/>
@@ -10950,7 +10950,7 @@
         <v>0.81944444444444453</v>
       </c>
       <c r="C110" s="21" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D110" s="89" t="s">
         <v>27</v>
@@ -10967,31 +10967,31 @@
         <v>0.84791666666666676</v>
       </c>
       <c r="C111" s="21" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D111" s="89" t="s">
+        <v>209</v>
+      </c>
+      <c r="E111" s="108" t="s">
         <v>210</v>
-      </c>
-      <c r="E111" s="108" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A112" s="169" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B112" s="170">
         <v>0.87708333333333333</v>
       </c>
       <c r="C112" s="22" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D112" s="171"/>
       <c r="E112" s="25"/>
     </row>
     <row r="113" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A113" s="173" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B113" s="174"/>
       <c r="C113" s="175"/>
@@ -11006,13 +11006,13 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C114" s="76" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D114" s="101" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E114" s="75" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -11023,13 +11023,13 @@
         <v>0.34236111111111112</v>
       </c>
       <c r="C115" s="47" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D115" s="87" t="s">
         <v>94</v>
       </c>
       <c r="E115" s="108" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -11040,13 +11040,13 @@
         <v>0.37708333333333338</v>
       </c>
       <c r="C116" s="47" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D116" s="77" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E116" s="111" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -11057,7 +11057,7 @@
         <v>0.37916666666666665</v>
       </c>
       <c r="C117" s="47" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D117" s="77" t="s">
         <v>9</v>
@@ -11074,13 +11074,13 @@
         <v>0.38125000000000003</v>
       </c>
       <c r="C118" s="21" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D118" s="87" t="s">
+        <v>251</v>
+      </c>
+      <c r="E118" s="72" t="s">
         <v>252</v>
-      </c>
-      <c r="E118" s="72" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
@@ -11091,13 +11091,13 @@
         <v>0.3972222222222222</v>
       </c>
       <c r="C119" s="21" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D119" s="89" t="s">
+        <v>308</v>
+      </c>
+      <c r="E119" s="72" t="s">
         <v>309</v>
-      </c>
-      <c r="E119" s="72" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
@@ -11108,24 +11108,24 @@
         <v>0.4069444444444445</v>
       </c>
       <c r="C120" s="21" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D120" s="89" t="s">
+        <v>198</v>
+      </c>
+      <c r="E120" s="108" t="s">
         <v>199</v>
-      </c>
-      <c r="E120" s="108" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A121" s="169" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B121" s="170">
         <v>0.41180555555555554</v>
       </c>
       <c r="C121" s="22" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D121" s="171"/>
       <c r="E121" s="25"/>
@@ -11138,13 +11138,13 @@
         <v>0.46249999999999997</v>
       </c>
       <c r="C122" s="47" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D122" s="87" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E122" s="108" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -11155,13 +11155,13 @@
         <v>0.47638888888888892</v>
       </c>
       <c r="C123" s="21" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D123" s="87" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E123" s="108" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -11172,24 +11172,24 @@
         <v>0.51111111111111118</v>
       </c>
       <c r="C124" s="47" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D124" s="77" t="s">
+        <v>320</v>
+      </c>
+      <c r="E124" s="72" t="s">
         <v>321</v>
-      </c>
-      <c r="E124" s="72" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A125" s="169" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B125" s="170">
         <v>0.51388888888888895</v>
       </c>
       <c r="C125" s="22" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D125" s="88"/>
       <c r="E125" s="106"/>
@@ -11200,7 +11200,7 @@
         <v>0.53819444444444442</v>
       </c>
       <c r="C126" s="22" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D126" s="171"/>
       <c r="E126" s="25"/>
@@ -11213,10 +11213,10 @@
         <v>0.55069444444444449</v>
       </c>
       <c r="C127" s="21" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D127" s="89" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E127" s="108" t="s">
         <v>98</v>
@@ -11230,7 +11230,7 @@
         <v>0.57847222222222217</v>
       </c>
       <c r="C128" s="21" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D128" s="89" t="s">
         <v>60</v>
@@ -11247,13 +11247,13 @@
         <v>0.57986111111111105</v>
       </c>
       <c r="C129" s="47" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D129" s="87" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E129" s="108" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -11264,7 +11264,7 @@
         <v>0.58194444444444449</v>
       </c>
       <c r="C130" s="47" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D130" s="87" t="s">
         <v>59</v>
@@ -11281,37 +11281,37 @@
         <v>0.62222222222222223</v>
       </c>
       <c r="C131" s="21" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D131" s="89" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E131" s="72" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A132" s="169" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B132" s="170">
         <v>0.63194444444444442</v>
       </c>
       <c r="C132" s="22" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D132" s="88"/>
       <c r="E132" s="106"/>
     </row>
     <row r="133" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A133" s="169" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B133" s="170">
         <v>0.66319444444444442</v>
       </c>
       <c r="C133" s="22" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D133" s="88"/>
       <c r="E133" s="106"/>

--- a/ESD2026.xlsx
+++ b/ESD2026.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1427" uniqueCount="597">
   <si>
     <t>Evolve</t>
   </si>
@@ -3213,7 +3213,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E114"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr defaultColWidth="86.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="55.140625" style="2" customWidth="1"/>
@@ -3221,10 +3221,11 @@
     <col min="3" max="3" width="45.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="45.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="86.42578125" style="2"/>
+    <col min="6" max="6" width="15.5703125" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="86.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3233,7 +3234,7 @@
       <c r="D1" s="5"/>
       <c r="E1" s="6"/>
     </row>
-    <row r="2" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -3244,7 +3245,7 @@
       <c r="D2" s="7"/>
       <c r="E2" s="9"/>
     </row>
-    <row r="3" spans="1:5" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
@@ -3260,8 +3261,11 @@
       <c r="E3" s="14" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F3" s="14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>7</v>
       </c>
@@ -3269,8 +3273,9 @@
       <c r="C4" s="17"/>
       <c r="D4" s="17"/>
       <c r="E4" s="18"/>
-    </row>
-    <row r="5" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F4" s="18"/>
+    </row>
+    <row r="5" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="19">
         <v>0.39583333333333331</v>
       </c>
@@ -3286,8 +3291,11 @@
       <c r="E5" s="21" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F5" s="21">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>0.40972222222222227</v>
       </c>
@@ -3303,8 +3311,11 @@
       <c r="E6" s="21" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F6" s="21">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
         <v>14</v>
       </c>
@@ -3320,8 +3331,9 @@
       <c r="E7" s="25" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F7" s="25"/>
+    </row>
+    <row r="8" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>0.4861111111111111</v>
       </c>
@@ -3337,8 +3349,11 @@
       <c r="E8" s="21" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F8" s="21">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19">
         <v>0.50347222222222221</v>
       </c>
@@ -3354,8 +3369,11 @@
       <c r="E9" s="21" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F9" s="21">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>0.51041666666666663</v>
       </c>
@@ -3371,8 +3389,11 @@
       <c r="E10" s="21" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F10" s="21">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19">
         <v>0.53472222222222221</v>
       </c>
@@ -3388,8 +3409,11 @@
       <c r="E11" s="21" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="F11" s="21">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A12" s="27" t="s">
         <v>213</v>
       </c>
@@ -3405,8 +3429,9 @@
       <c r="E12" s="31" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F12" s="31"/>
+    </row>
+    <row r="13" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
         <v>14</v>
       </c>
@@ -3422,8 +3447,9 @@
       <c r="E13" s="25" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F13" s="25"/>
+    </row>
+    <row r="14" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>0.71875</v>
       </c>
@@ -3439,8 +3465,11 @@
       <c r="E14" s="21" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F14" s="21">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
         <v>14</v>
       </c>
@@ -3456,8 +3485,9 @@
       <c r="E15" s="25" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F15" s="25"/>
+    </row>
+    <row r="16" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>0.76041666666666663</v>
       </c>
@@ -3473,8 +3503,11 @@
       <c r="E16" s="21" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F16" s="21">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
         <v>14</v>
       </c>
@@ -3490,8 +3523,9 @@
       <c r="E17" s="25" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F17" s="25"/>
+    </row>
+    <row r="18" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="32" t="s">
         <v>32</v>
       </c>
@@ -3503,8 +3537,9 @@
       <c r="E18" s="36" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F18" s="36"/>
+    </row>
+    <row r="19" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="19">
         <v>0.35069444444444442</v>
       </c>
@@ -3520,8 +3555,11 @@
       <c r="E19" s="21" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F19" s="21">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>0.35069444444444442</v>
       </c>
@@ -3537,8 +3575,11 @@
       <c r="E20" s="21" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F20" s="21">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="37" t="s">
         <v>38</v>
       </c>
@@ -3554,8 +3595,9 @@
       <c r="E21" s="31" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F21" s="31"/>
+    </row>
+    <row r="22" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>0.48958333333333331</v>
       </c>
@@ -3571,8 +3613,11 @@
       <c r="E22" s="21" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F22" s="21">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="19">
         <v>0.48958333333333331</v>
       </c>
@@ -3588,8 +3633,11 @@
       <c r="E23" s="21" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F23" s="21">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>0.50694444444444442</v>
       </c>
@@ -3605,8 +3653,11 @@
       <c r="E24" s="21" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F24" s="21">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="19">
         <v>0.53472222222222221</v>
       </c>
@@ -3622,8 +3673,11 @@
       <c r="E25" s="21" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F25" s="21">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="42" t="s">
         <v>14</v>
       </c>
@@ -3639,8 +3693,9 @@
       <c r="E26" s="31" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F26" s="31"/>
+    </row>
+    <row r="27" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="19">
         <v>0.61111111111111105</v>
       </c>
@@ -3656,8 +3711,11 @@
       <c r="E27" s="21" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F27" s="21">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>0.67708333333333337</v>
       </c>
@@ -3673,8 +3731,11 @@
       <c r="E28" s="21" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F28" s="21">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="19">
         <v>0.67708333333333337</v>
       </c>
@@ -3690,8 +3751,11 @@
       <c r="E29" s="21" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F29" s="21">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>0.67708333333333337</v>
       </c>
@@ -3707,8 +3771,11 @@
       <c r="E30" s="21" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F30" s="21">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
         <v>14</v>
       </c>
@@ -3724,8 +3791,9 @@
       <c r="E31" s="25" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F31" s="25"/>
+    </row>
+    <row r="32" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>0.76041666666666663</v>
       </c>
@@ -3741,8 +3809,11 @@
       <c r="E32" s="21" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F32" s="21">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19">
         <v>0.76041666666666663</v>
       </c>
@@ -3758,8 +3829,11 @@
       <c r="E33" s="21" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F33" s="21">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="48" t="s">
         <v>14</v>
       </c>
@@ -3775,8 +3849,9 @@
       <c r="E34" s="51" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F34" s="51"/>
+    </row>
+    <row r="35" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
         <v>61</v>
       </c>
@@ -3788,8 +3863,9 @@
       <c r="E35" s="36" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F35" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>0.33333333333333331</v>
       </c>
@@ -3805,8 +3881,11 @@
       <c r="E36" s="21" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F36" s="21">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="19">
         <v>0.36458333333333331</v>
       </c>
@@ -3822,8 +3901,11 @@
       <c r="E37" s="21" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F37" s="21">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>0.38194444444444442</v>
       </c>
@@ -3839,8 +3921,11 @@
       <c r="E38" s="21" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F38" s="21">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="22" t="s">
         <v>14</v>
       </c>
@@ -3856,8 +3941,9 @@
       <c r="E39" s="25" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F39" s="25"/>
+    </row>
+    <row r="40" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>0.46875</v>
       </c>
@@ -3873,8 +3959,11 @@
       <c r="E40" s="21" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F40" s="21">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="19">
         <v>0.51041666666666663</v>
       </c>
@@ -3890,8 +3979,11 @@
       <c r="E41" s="21" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F41" s="21">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>0.51736111111111105</v>
       </c>
@@ -3907,8 +3999,11 @@
       <c r="E42" s="21" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F42" s="21">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="19">
         <v>0.54166666666666663</v>
       </c>
@@ -3924,8 +4019,11 @@
       <c r="E43" s="21" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F43" s="21">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>0.55555555555555558</v>
       </c>
@@ -3941,8 +4039,11 @@
       <c r="E44" s="21" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F44" s="21">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="19">
         <v>0.55902777777777779</v>
       </c>
@@ -3958,8 +4059,11 @@
       <c r="E45" s="21" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F45" s="21">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="52" t="s">
         <v>14</v>
       </c>
@@ -3975,8 +4079,9 @@
       <c r="E46" s="31" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F46" s="31"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="58" t="s">
         <v>89</v>
       </c>
@@ -3988,8 +4093,9 @@
       <c r="E47" s="46" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F47" s="46"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="58" t="s">
         <v>90</v>
       </c>
@@ -4001,8 +4107,9 @@
       <c r="E48" s="46" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F48" s="46"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="58" t="s">
         <v>91</v>
       </c>
@@ -4014,8 +4121,9 @@
       <c r="E49" s="46" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F49" s="46"/>
+    </row>
+    <row r="50" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="59" t="s">
         <v>92</v>
       </c>
@@ -4027,8 +4135,9 @@
       <c r="E50" s="41" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F50" s="41"/>
+    </row>
+    <row r="51" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="19">
         <v>0.61805555555555558</v>
       </c>
@@ -4044,8 +4153,11 @@
       <c r="E51" s="21" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F51" s="21">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
         <v>0.61805555555555558</v>
       </c>
@@ -4061,8 +4173,11 @@
       <c r="E52" s="21" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F52" s="21">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="19">
         <v>0.64930555555555558</v>
       </c>
@@ -4078,8 +4193,11 @@
       <c r="E53" s="21" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F53" s="21">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
         <v>0.64930555555555558</v>
       </c>
@@ -4095,8 +4213,11 @@
       <c r="E54" s="21" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F54" s="21">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="62" t="s">
         <v>104</v>
       </c>
@@ -4112,8 +4233,11 @@
       <c r="E55" s="21" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F55" s="21">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
         <v>0.65972222222222221</v>
       </c>
@@ -4129,8 +4253,11 @@
       <c r="E56" s="21" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F56" s="21">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A57" s="19">
         <v>0.66666666666666663</v>
       </c>
@@ -4146,8 +4273,11 @@
       <c r="E57" s="21" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F57" s="21">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A58" s="19">
         <v>0.66666666666666663</v>
       </c>
@@ -4163,8 +4293,11 @@
       <c r="E58" s="21" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F58" s="21">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A59" s="19">
         <v>0.66666666666666663</v>
       </c>
@@ -4180,8 +4313,11 @@
       <c r="E59" s="21" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F59" s="21">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A60" s="62" t="s">
         <v>119</v>
       </c>
@@ -4197,8 +4333,11 @@
       <c r="E60" s="21" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F60" s="21">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A61" s="19">
         <v>0.69791666666666663</v>
       </c>
@@ -4214,8 +4353,11 @@
       <c r="E61" s="21" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F61" s="21">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A62" s="19">
         <v>0.69791666666666663</v>
       </c>
@@ -4231,8 +4373,11 @@
       <c r="E62" s="21" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F62" s="21">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A63" s="22" t="s">
         <v>14</v>
       </c>
@@ -4248,8 +4393,9 @@
       <c r="E63" s="25" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F63" s="25"/>
+    </row>
+    <row r="64" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A64" s="63">
         <v>0.78125</v>
       </c>
@@ -4265,8 +4411,11 @@
       <c r="E64" s="21" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F64" s="21">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A65" s="63">
         <v>0.80902777777777779</v>
       </c>
@@ -4282,8 +4431,11 @@
       <c r="E65" s="21" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F65" s="21">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A66" s="48" t="s">
         <v>14</v>
       </c>
@@ -4299,8 +4451,9 @@
       <c r="E66" s="51" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F66" s="51"/>
+    </row>
+    <row r="67" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A67" s="15" t="s">
         <v>132</v>
       </c>
@@ -4312,8 +4465,9 @@
       <c r="E67" s="36" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F67" s="36"/>
+    </row>
+    <row r="68" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A68" s="19">
         <v>0.40625</v>
       </c>
@@ -4329,8 +4483,11 @@
       <c r="E68" s="21" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F68" s="21">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A69" s="19">
         <v>0.41666666666666669</v>
       </c>
@@ -4346,8 +4503,11 @@
       <c r="E69" s="21" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F69" s="21">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A70" s="19">
         <v>0.42708333333333331</v>
       </c>
@@ -4363,8 +4523,11 @@
       <c r="E70" s="21" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F70" s="21">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A71" s="19">
         <v>0.42708333333333331</v>
       </c>
@@ -4380,8 +4543,11 @@
       <c r="E71" s="21" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F71" s="21">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A72" s="22" t="s">
         <v>14</v>
       </c>
@@ -4397,8 +4563,9 @@
       <c r="E72" s="25" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F72" s="25"/>
+    </row>
+    <row r="73" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A73" s="19">
         <v>0.47222222222222227</v>
       </c>
@@ -4414,8 +4581,11 @@
       <c r="E73" s="21" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F73" s="21">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A74" s="19">
         <v>0.4861111111111111</v>
       </c>
@@ -4431,8 +4601,11 @@
       <c r="E74" s="21" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F74" s="21">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A75" s="19">
         <v>0.5</v>
       </c>
@@ -4448,8 +4621,11 @@
       <c r="E75" s="21" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F75" s="21">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A76" s="19">
         <v>0.50694444444444442</v>
       </c>
@@ -4465,8 +4641,11 @@
       <c r="E76" s="21" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F76" s="21">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A77" s="19">
         <v>0.53125</v>
       </c>
@@ -4482,8 +4661,11 @@
       <c r="E77" s="21" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F77" s="21">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A78" s="19">
         <v>0.54166666666666663</v>
       </c>
@@ -4499,8 +4681,11 @@
       <c r="E78" s="21" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F78" s="21">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A79" s="19">
         <v>0.55902777777777779</v>
       </c>
@@ -4516,8 +4701,11 @@
       <c r="E79" s="21" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F79" s="21">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A80" s="19">
         <v>0.55902777777777779</v>
       </c>
@@ -4533,8 +4721,11 @@
       <c r="E80" s="21" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F80" s="21">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="52" t="s">
         <v>14</v>
       </c>
@@ -4550,8 +4741,9 @@
       <c r="E81" s="31" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F81" s="31"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" s="55"/>
       <c r="B82" s="43"/>
       <c r="C82" s="44"/>
@@ -4561,8 +4753,9 @@
       <c r="E82" s="46" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F82" s="46"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="58" t="s">
         <v>166</v>
       </c>
@@ -4574,8 +4767,9 @@
       <c r="E83" s="46" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F83" s="46"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="58" t="s">
         <v>167</v>
       </c>
@@ -4587,8 +4781,9 @@
       <c r="E84" s="46" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F84" s="46"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="58" t="s">
         <v>168</v>
       </c>
@@ -4600,8 +4795,9 @@
       <c r="E85" s="46" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F85" s="46"/>
+    </row>
+    <row r="86" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A86" s="59" t="s">
         <v>169</v>
       </c>
@@ -4613,8 +4809,9 @@
       <c r="E86" s="41" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F86" s="41"/>
+    </row>
+    <row r="87" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A87" s="19">
         <v>0.65625</v>
       </c>
@@ -4630,8 +4827,11 @@
       <c r="E87" s="21" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F87" s="21">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A88" s="19">
         <v>0.69444444444444453</v>
       </c>
@@ -4647,8 +4847,11 @@
       <c r="E88" s="21" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F88" s="21">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A89" s="19">
         <v>0.70833333333333337</v>
       </c>
@@ -4664,8 +4867,11 @@
       <c r="E89" s="21" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F89" s="21">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A90" s="22" t="s">
         <v>14</v>
       </c>
@@ -4681,8 +4887,9 @@
       <c r="E90" s="25" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F90" s="25"/>
+    </row>
+    <row r="91" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A91" s="19">
         <v>0.75</v>
       </c>
@@ -4698,8 +4905,11 @@
       <c r="E91" s="21" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F91" s="21">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A92" s="19">
         <v>0.78472222222222221</v>
       </c>
@@ -4715,8 +4925,11 @@
       <c r="E92" s="21" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F92" s="21">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" s="52" t="s">
         <v>14</v>
       </c>
@@ -4732,8 +4945,9 @@
       <c r="E93" s="31" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F93" s="31"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" s="55"/>
       <c r="B94" s="43"/>
       <c r="C94" s="44"/>
@@ -4743,8 +4957,9 @@
       <c r="E94" s="46" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F94" s="46"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="58" t="s">
         <v>177</v>
       </c>
@@ -4756,8 +4971,9 @@
       <c r="E95" s="46" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F95" s="46"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="58" t="s">
         <v>178</v>
       </c>
@@ -4769,8 +4985,9 @@
       <c r="E96" s="46" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F96" s="46"/>
+    </row>
+    <row r="97" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A97" s="64" t="s">
         <v>179</v>
       </c>
@@ -4782,8 +4999,9 @@
       <c r="E97" s="68" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F97" s="68"/>
+    </row>
+    <row r="98" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A98" s="15" t="s">
         <v>180</v>
       </c>
@@ -4795,8 +5013,9 @@
       <c r="E98" s="36" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F98" s="36"/>
+    </row>
+    <row r="99" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A99" s="19">
         <v>0.33333333333333331</v>
       </c>
@@ -4812,8 +5031,11 @@
       <c r="E99" s="21" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F99" s="21">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A100" s="19">
         <v>0.33333333333333331</v>
       </c>
@@ -4829,8 +5051,11 @@
       <c r="E100" s="21" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F100" s="21">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A101" s="69" t="s">
         <v>187</v>
       </c>
@@ -4846,8 +5071,11 @@
       <c r="E101" s="21" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F101" s="21">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A102" s="19">
         <v>0.35069444444444442</v>
       </c>
@@ -4863,8 +5091,11 @@
       <c r="E102" s="21" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F102" s="21">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A103" s="19">
         <v>0.3611111111111111</v>
       </c>
@@ -4880,8 +5111,11 @@
       <c r="E103" s="21" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F103" s="21">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A104" s="19">
         <v>0.375</v>
       </c>
@@ -4897,8 +5131,11 @@
       <c r="E104" s="21" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="105" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F104" s="21">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A105" s="19">
         <v>0.3923611111111111</v>
       </c>
@@ -4914,8 +5151,11 @@
       <c r="E105" s="21" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F105" s="21">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A106" s="19">
         <v>0.3923611111111111</v>
       </c>
@@ -4931,8 +5171,11 @@
       <c r="E106" s="21" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="107" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F106" s="21">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A107" s="19">
         <v>0.41666666666666669</v>
       </c>
@@ -4948,8 +5191,11 @@
       <c r="E107" s="21" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F107" s="21">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="52" t="s">
         <v>14</v>
       </c>
@@ -4965,8 +5211,9 @@
       <c r="E108" s="31" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="109" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F108" s="31"/>
+    </row>
+    <row r="109" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A109" s="59" t="s">
         <v>207</v>
       </c>
@@ -4978,8 +5225,9 @@
       <c r="E109" s="41" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="110" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F109" s="41"/>
+    </row>
+    <row r="110" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A110" s="19">
         <v>0.47222222222222227</v>
       </c>
@@ -4995,8 +5243,11 @@
       <c r="E110" s="21" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F110" s="21">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="52" t="s">
         <v>14</v>
       </c>
@@ -5008,15 +5259,17 @@
       </c>
       <c r="D111" s="30"/>
       <c r="E111" s="31"/>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F111" s="31"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="55"/>
       <c r="B112" s="43"/>
       <c r="C112" s="44"/>
       <c r="D112" s="45"/>
       <c r="E112" s="46"/>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F112" s="46"/>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="58" t="s">
         <v>211</v>
       </c>
@@ -5024,8 +5277,9 @@
       <c r="C113" s="44"/>
       <c r="D113" s="45"/>
       <c r="E113" s="46"/>
-    </row>
-    <row r="114" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F113" s="46"/>
+    </row>
+    <row r="114" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A114" s="59" t="s">
         <v>212</v>
       </c>
@@ -5033,6 +5287,7 @@
       <c r="C114" s="39"/>
       <c r="D114" s="40"/>
       <c r="E114" s="41"/>
+      <c r="F114" s="41"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5042,7 +5297,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E157"/>
+  <dimension ref="A1:F157"/>
   <sheetFormatPr defaultColWidth="71" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="68" style="1" bestFit="1" customWidth="1"/>
@@ -5053,7 +5308,7 @@
     <col min="6" max="16384" width="71" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>214</v>
       </c>
@@ -5062,7 +5317,7 @@
       <c r="D1" s="77"/>
       <c r="E1" s="70"/>
     </row>
-    <row r="2" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="78" t="s">
         <v>215</v>
       </c>
@@ -5073,7 +5328,7 @@
       <c r="D2" s="80"/>
       <c r="E2" s="71"/>
     </row>
-    <row r="3" spans="1:5" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="81" t="s">
         <v>216</v>
       </c>
@@ -5089,8 +5344,11 @@
       <c r="E3" s="82" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F3" s="14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="83" t="s">
         <v>217</v>
       </c>
@@ -5099,7 +5357,7 @@
       <c r="D4" s="84"/>
       <c r="E4" s="85"/>
     </row>
-    <row r="5" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="19">
         <v>0.36458333333333331</v>
       </c>
@@ -5116,7 +5374,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>0.36458333333333331</v>
       </c>
@@ -5133,7 +5391,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="19">
         <v>0.36458333333333331</v>
       </c>
@@ -5150,7 +5408,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>0.375</v>
       </c>
@@ -5167,7 +5425,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19">
         <v>0.38541666666666669</v>
       </c>
@@ -5184,7 +5442,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>224</v>
       </c>
@@ -5197,7 +5455,7 @@
       <c r="D10" s="88"/>
       <c r="E10" s="25"/>
     </row>
-    <row r="11" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19">
         <v>0.4375</v>
       </c>
@@ -5214,7 +5472,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>0.44791666666666669</v>
       </c>
@@ -5231,7 +5489,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
         <v>224</v>
       </c>
@@ -5244,7 +5502,7 @@
       <c r="D13" s="88"/>
       <c r="E13" s="25"/>
     </row>
-    <row r="14" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>0.47916666666666669</v>
       </c>
@@ -5261,7 +5519,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="19">
         <v>0.47916666666666669</v>
       </c>
@@ -5278,7 +5536,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
         <v>224</v>
       </c>
@@ -7475,7 +7733,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E107"/>
+  <dimension ref="A1:F107"/>
   <sheetFormatPr defaultColWidth="55.140625" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="54.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -7486,7 +7744,7 @@
     <col min="6" max="16384" width="55.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="122" t="s">
         <v>388</v>
       </c>
@@ -7495,7 +7753,7 @@
       <c r="D1" s="6"/>
       <c r="E1" s="5"/>
     </row>
-    <row r="2" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>389</v>
       </c>
@@ -7506,7 +7764,7 @@
       <c r="D2" s="7"/>
       <c r="E2" s="9"/>
     </row>
-    <row r="3" spans="1:5" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="123" t="s">
         <v>3</v>
       </c>
@@ -7522,8 +7780,11 @@
       <c r="E3" s="14" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F3" s="14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="124" t="s">
         <v>391</v>
       </c>
@@ -7532,7 +7793,7 @@
       <c r="D4" s="84"/>
       <c r="E4" s="85"/>
     </row>
-    <row r="5" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="19">
         <v>0.42708333333333331</v>
       </c>
@@ -7549,7 +7810,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>0.44097222222222227</v>
       </c>
@@ -7566,7 +7827,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="126">
         <v>0.42708333333333331</v>
       </c>
@@ -7583,7 +7844,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>0.56944444444444442</v>
       </c>
@@ -7600,7 +7861,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19">
         <v>0.56944444444444442</v>
       </c>
@@ -7617,7 +7878,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>0.57291666666666663</v>
       </c>
@@ -7634,7 +7895,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19">
         <v>0.59027777777777779</v>
       </c>
@@ -7651,7 +7912,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>0.61805555555555558</v>
       </c>
@@ -7668,7 +7929,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="19">
         <v>0.70833333333333337</v>
       </c>
@@ -7685,7 +7946,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A14" s="133">
         <v>0.72222222222222221</v>
       </c>
@@ -7702,7 +7963,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="26.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="138">
         <v>0.72222222222222221</v>
       </c>
@@ -7719,7 +7980,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="138">
         <v>0.78125</v>
       </c>
@@ -9219,7 +9480,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E133"/>
+  <dimension ref="A1:F133"/>
   <sheetFormatPr defaultColWidth="82" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="75.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -9229,7 +9490,7 @@
     <col min="5" max="16384" width="82" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="176" t="s">
         <v>494</v>
       </c>
@@ -9240,7 +9501,7 @@
       <c r="D1" s="135"/>
       <c r="E1" s="164"/>
     </row>
-    <row r="2" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="178" t="s">
         <v>496</v>
       </c>
@@ -9249,7 +9510,7 @@
       <c r="D2" s="180"/>
       <c r="E2" s="165"/>
     </row>
-    <row r="3" spans="1:5" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="181" t="s">
         <v>3</v>
       </c>
@@ -9265,8 +9526,11 @@
       <c r="E3" s="14" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="F3" s="14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A4" s="185" t="s">
         <v>497</v>
       </c>
@@ -9275,7 +9539,7 @@
       <c r="D4" s="186"/>
       <c r="E4" s="187"/>
     </row>
-    <row r="5" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="138">
         <v>0.29166666666666669</v>
       </c>
@@ -9292,7 +9556,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" s="138">
         <v>0.30208333333333331</v>
       </c>
@@ -9309,7 +9573,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="168">
         <v>0.29166666666666669</v>
       </c>
@@ -9326,14 +9590,14 @@
         <v>342</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="188"/>
       <c r="B8" s="136"/>
       <c r="C8" s="113"/>
       <c r="D8" s="137"/>
       <c r="E8" s="72"/>
     </row>
-    <row r="9" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="138">
         <v>0.32291666666666669</v>
       </c>
@@ -9350,7 +9614,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A10" s="138">
         <v>0.32291666666666669</v>
       </c>
@@ -9367,7 +9631,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="26.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A11" s="138">
         <v>0.34375</v>
       </c>
@@ -9384,7 +9648,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="38.25" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:6" ht="38.25" x14ac:dyDescent="0.15">
       <c r="A12" s="168">
         <v>0.35416666666666669</v>
       </c>
@@ -9401,7 +9665,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="169" t="s">
         <v>504</v>
       </c>
@@ -9414,7 +9678,7 @@
       <c r="D13" s="88"/>
       <c r="E13" s="166"/>
     </row>
-    <row r="14" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="138">
         <v>0.38541666666666669</v>
       </c>
@@ -9431,7 +9695,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="160" t="s">
         <v>506</v>
       </c>
@@ -9448,7 +9712,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="160" t="s">
         <v>506</v>
       </c>

--- a/ESD2026.xlsx
+++ b/ESD2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17640"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17640" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Evolve April 15 - 19" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Abstract May 21 - 24'!$A$3:$E$133</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Danceworks May 7 - 10'!$A$3:$E$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Danceworks May 7 - 10'!$A$3:$E$109</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1427" uniqueCount="597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="598">
   <si>
     <t>Evolve</t>
   </si>
@@ -1833,6 +1833,9 @@
   </si>
   <si>
     <t>Loose Control</t>
+  </si>
+  <si>
+    <t>Tier 4 Inter 2 Small Group 13yrs Jazz</t>
   </si>
 </sst>
 </file>
@@ -2371,7 +2374,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="189">
+  <cellXfs count="194">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2932,6 +2935,21 @@
     </xf>
     <xf numFmtId="18" fontId="6" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="6" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7733,14 +7751,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F107"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr defaultColWidth="55.140625" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="54.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="55" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="84.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="55.140625" style="1"/>
   </cols>
   <sheetData>
@@ -8518,72 +8536,72 @@
         <v>204</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A50" s="153">
+    <row r="50" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="189">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="B50" s="190">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="C50" s="191" t="s">
+        <v>597</v>
+      </c>
+      <c r="D50" s="192" t="s">
+        <v>371</v>
+      </c>
+      <c r="E50" s="193" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A51" s="153">
         <v>0.71527777777777779</v>
       </c>
-      <c r="B50" s="148">
+      <c r="B51" s="148">
         <v>0.77500000000000002</v>
       </c>
-      <c r="C50" s="76" t="s">
+      <c r="C51" s="76" t="s">
         <v>443</v>
       </c>
-      <c r="D50" s="141" t="s">
+      <c r="D51" s="141" t="s">
         <v>374</v>
       </c>
-      <c r="E50" s="75" t="s">
+      <c r="E51" s="75" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="144" t="s">
+    <row r="52" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="144" t="s">
         <v>444</v>
       </c>
-      <c r="B51" s="139">
+      <c r="B52" s="139">
         <v>0.79513888888888884</v>
       </c>
-      <c r="C51" s="47" t="s">
+      <c r="C52" s="47" t="s">
         <v>445</v>
       </c>
-      <c r="D51" s="125" t="s">
+      <c r="D52" s="125" t="s">
         <v>171</v>
       </c>
-      <c r="E51" s="111" t="s">
+      <c r="E52" s="111" t="s">
         <v>129</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="19">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="B52" s="139">
-        <v>0.84375</v>
-      </c>
-      <c r="C52" s="47" t="s">
-        <v>404</v>
-      </c>
-      <c r="D52" s="132" t="s">
-        <v>176</v>
-      </c>
-      <c r="E52" s="111" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="19">
-        <v>0.80208333333333337</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="B53" s="139">
-        <v>0.85625000000000007</v>
+        <v>0.84375</v>
       </c>
       <c r="C53" s="47" t="s">
-        <v>405</v>
-      </c>
-      <c r="D53" s="125" t="s">
-        <v>278</v>
+        <v>404</v>
+      </c>
+      <c r="D53" s="132" t="s">
+        <v>176</v>
       </c>
       <c r="E53" s="111" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8591,93 +8609,93 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="B54" s="139">
-        <v>0.85763888888888884</v>
+        <v>0.85625000000000007</v>
       </c>
       <c r="C54" s="47" t="s">
         <v>405</v>
       </c>
       <c r="D54" s="125" t="s">
+        <v>278</v>
+      </c>
+      <c r="E54" s="111" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="19">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="B55" s="139">
+        <v>0.85763888888888884</v>
+      </c>
+      <c r="C55" s="47" t="s">
+        <v>405</v>
+      </c>
+      <c r="D55" s="125" t="s">
         <v>175</v>
       </c>
-      <c r="E54" s="111" t="s">
+      <c r="E55" s="111" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="140" t="s">
+    <row r="56" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="140" t="s">
         <v>446</v>
       </c>
-      <c r="B55" s="92"/>
-      <c r="C55" s="34"/>
-      <c r="D55" s="154"/>
-      <c r="E55" s="155"/>
-    </row>
-    <row r="56" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="156">
+      <c r="B56" s="92"/>
+      <c r="C56" s="34"/>
+      <c r="D56" s="154"/>
+      <c r="E56" s="155"/>
+    </row>
+    <row r="57" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="156">
         <v>0.33333333333333331</v>
       </c>
-      <c r="B56" s="127">
+      <c r="B57" s="127">
         <v>0.37916666666666665</v>
       </c>
-      <c r="C56" s="115" t="s">
+      <c r="C57" s="115" t="s">
         <v>447</v>
       </c>
-      <c r="D56" s="135" t="s">
+      <c r="D57" s="135" t="s">
         <v>359</v>
       </c>
-      <c r="E56" s="75" t="s">
+      <c r="E57" s="75" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A57" s="145">
+    <row r="58" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A58" s="145">
         <v>0.33333333333333331</v>
       </c>
-      <c r="B57" s="134">
+      <c r="B58" s="134">
         <v>0.38958333333333334</v>
       </c>
-      <c r="C57" s="115" t="s">
+      <c r="C58" s="115" t="s">
         <v>448</v>
       </c>
-      <c r="D57" s="141" t="s">
+      <c r="D58" s="141" t="s">
         <v>362</v>
       </c>
-      <c r="E57" s="75" t="s">
+      <c r="E58" s="75" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="19">
+    <row r="59" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="19">
         <v>0.3611111111111111</v>
       </c>
-      <c r="B58" s="20">
+      <c r="B59" s="20">
         <v>0.41250000000000003</v>
       </c>
-      <c r="C58" s="114" t="s">
+      <c r="C59" s="114" t="s">
         <v>449</v>
       </c>
-      <c r="D58" s="125" t="s">
+      <c r="D59" s="125" t="s">
         <v>201</v>
       </c>
-      <c r="E58" s="111" t="s">
+      <c r="E59" s="111" t="s">
         <v>202</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="156">
-        <v>0.3611111111111111</v>
-      </c>
-      <c r="B59" s="127">
-        <v>0.4145833333333333</v>
-      </c>
-      <c r="C59" s="115" t="s">
-        <v>450</v>
-      </c>
-      <c r="D59" s="158" t="s">
-        <v>195</v>
-      </c>
-      <c r="E59" s="74" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8685,246 +8703,246 @@
         <v>0.3611111111111111</v>
       </c>
       <c r="B60" s="127">
-        <v>0.41666666666666669</v>
+        <v>0.4145833333333333</v>
       </c>
       <c r="C60" s="115" t="s">
         <v>450</v>
       </c>
-      <c r="D60" s="125" t="s">
-        <v>300</v>
-      </c>
-      <c r="E60" s="116" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="D60" s="158" t="s">
+        <v>195</v>
+      </c>
+      <c r="E60" s="74" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A61" s="156">
         <v>0.3611111111111111</v>
       </c>
       <c r="B61" s="127">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C61" s="115" t="s">
+        <v>450</v>
+      </c>
+      <c r="D61" s="125" t="s">
+        <v>300</v>
+      </c>
+      <c r="E61" s="116" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A62" s="156">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="B62" s="127">
         <v>0.41875000000000001</v>
       </c>
-      <c r="C61" s="115" t="s">
+      <c r="C62" s="115" t="s">
         <v>451</v>
       </c>
-      <c r="D61" s="125" t="s">
+      <c r="D62" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="E61" s="74" t="s">
+      <c r="E62" s="74" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="19">
+    <row r="63" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="19">
         <v>0.3611111111111111</v>
       </c>
-      <c r="B62" s="20">
+      <c r="B63" s="20">
         <v>0.42083333333333334</v>
       </c>
-      <c r="C62" s="114" t="s">
+      <c r="C63" s="114" t="s">
         <v>452</v>
       </c>
-      <c r="D62" s="77" t="s">
+      <c r="D63" s="77" t="s">
         <v>596</v>
       </c>
-      <c r="E62" s="111" t="s">
+      <c r="E63" s="111" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="156">
+    <row r="64" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="156">
         <v>0.36805555555555558</v>
       </c>
-      <c r="B63" s="127">
+      <c r="B64" s="127">
         <v>0.42499999999999999</v>
       </c>
-      <c r="C63" s="115" t="s">
+      <c r="C64" s="115" t="s">
         <v>453</v>
       </c>
-      <c r="D63" s="141" t="s">
+      <c r="D64" s="141" t="s">
         <v>308</v>
       </c>
-      <c r="E63" s="116" t="s">
+      <c r="E64" s="116" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="156">
+    <row r="65" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="156">
         <v>0.375</v>
       </c>
-      <c r="B64" s="127">
+      <c r="B65" s="127">
         <v>0.43611111111111112</v>
       </c>
-      <c r="C64" s="115" t="s">
+      <c r="C65" s="115" t="s">
         <v>454</v>
       </c>
-      <c r="D64" s="135" t="s">
+      <c r="D65" s="135" t="s">
         <v>311</v>
       </c>
-      <c r="E64" s="116" t="s">
+      <c r="E65" s="116" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A65" s="133">
+    <row r="66" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="A66" s="133">
         <v>0.375</v>
       </c>
-      <c r="B65" s="159">
+      <c r="B66" s="159">
         <v>0.4381944444444445</v>
       </c>
-      <c r="C65" s="117" t="s">
+      <c r="C66" s="117" t="s">
         <v>455</v>
       </c>
-      <c r="D65" s="141" t="s">
+      <c r="D66" s="141" t="s">
         <v>369</v>
       </c>
-      <c r="E65" s="75" t="s">
+      <c r="E66" s="75" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="157" t="s">
+    <row r="67" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="157" t="s">
         <v>456</v>
       </c>
-      <c r="B66" s="139">
+      <c r="B67" s="139">
         <v>0.47569444444444442</v>
       </c>
-      <c r="C66" s="119" t="s">
+      <c r="C67" s="119" t="s">
         <v>457</v>
       </c>
-      <c r="D66" s="125" t="s">
+      <c r="D67" s="125" t="s">
         <v>81</v>
       </c>
-      <c r="E66" s="108" t="s">
+      <c r="E67" s="108" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A67" s="156">
+    <row r="68" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A68" s="156">
         <v>0.4236111111111111</v>
       </c>
-      <c r="B67" s="148">
+      <c r="B68" s="148">
         <v>0.4777777777777778</v>
       </c>
-      <c r="C67" s="117" t="s">
+      <c r="C68" s="117" t="s">
         <v>458</v>
       </c>
-      <c r="D67" s="131" t="s">
+      <c r="D68" s="131" t="s">
         <v>72</v>
       </c>
-      <c r="E67" s="76" t="s">
+      <c r="E68" s="76" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="157" t="s">
+    <row r="69" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="157" t="s">
         <v>459</v>
       </c>
-      <c r="B68" s="150"/>
-      <c r="C68" s="118"/>
-      <c r="D68" s="152"/>
-      <c r="E68" s="113"/>
-    </row>
-    <row r="69" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="19">
+      <c r="B69" s="150"/>
+      <c r="C69" s="118"/>
+      <c r="D69" s="152"/>
+      <c r="E69" s="113"/>
+    </row>
+    <row r="70" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="19">
         <v>0.43402777777777773</v>
       </c>
-      <c r="B69" s="139">
+      <c r="B70" s="139">
         <v>0.48749999999999999</v>
       </c>
-      <c r="C69" s="119" t="s">
+      <c r="C70" s="119" t="s">
         <v>460</v>
       </c>
-      <c r="D69" s="125" t="s">
+      <c r="D70" s="125" t="s">
         <v>84</v>
       </c>
-      <c r="E69" s="108" t="s">
+      <c r="E70" s="108" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="145">
+    <row r="71" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="145">
         <v>0.4375</v>
       </c>
-      <c r="B70" s="159">
+      <c r="B71" s="159">
         <v>0.49374999999999997</v>
       </c>
-      <c r="C70" s="117" t="s">
+      <c r="C71" s="117" t="s">
         <v>461</v>
       </c>
-      <c r="D70" s="141" t="s">
+      <c r="D71" s="141" t="s">
         <v>382</v>
       </c>
-      <c r="E70" s="75" t="s">
+      <c r="E71" s="75" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="145">
+    <row r="72" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A72" s="145">
         <v>0.4826388888888889</v>
       </c>
-      <c r="B71" s="159">
+      <c r="B72" s="159">
         <v>0.52708333333333335</v>
       </c>
-      <c r="C71" s="117" t="s">
+      <c r="C72" s="117" t="s">
         <v>462</v>
       </c>
-      <c r="D71" s="141" t="s">
+      <c r="D72" s="141" t="s">
         <v>256</v>
       </c>
-      <c r="E71" s="116" t="s">
+      <c r="E72" s="116" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="138">
+    <row r="73" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="138">
         <v>0.54166666666666663</v>
       </c>
-      <c r="B72" s="139">
+      <c r="B73" s="139">
         <v>0.60138888888888886</v>
       </c>
-      <c r="C72" s="119" t="s">
+      <c r="C73" s="119" t="s">
         <v>463</v>
       </c>
-      <c r="D72" s="89" t="s">
+      <c r="D73" s="89" t="s">
         <v>366</v>
       </c>
-      <c r="E72" s="72" t="s">
+      <c r="E73" s="72" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="138">
+    <row r="74" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="138">
         <v>0.58333333333333337</v>
       </c>
-      <c r="B73" s="139">
+      <c r="B74" s="139">
         <v>0.64166666666666672</v>
       </c>
-      <c r="C73" s="119" t="s">
+      <c r="C74" s="119" t="s">
         <v>464</v>
       </c>
-      <c r="D73" s="87" t="s">
+      <c r="D74" s="87" t="s">
         <v>251</v>
       </c>
-      <c r="E73" s="72" t="s">
+      <c r="E74" s="72" t="s">
         <v>252</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="138">
-        <v>0.625</v>
-      </c>
-      <c r="B74" s="139">
-        <v>0.6791666666666667</v>
-      </c>
-      <c r="C74" s="119" t="s">
-        <v>465</v>
-      </c>
-      <c r="D74" s="131" t="s">
-        <v>114</v>
-      </c>
-      <c r="E74" s="108" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8932,50 +8950,50 @@
         <v>0.625</v>
       </c>
       <c r="B75" s="139">
+        <v>0.6791666666666667</v>
+      </c>
+      <c r="C75" s="119" t="s">
+        <v>465</v>
+      </c>
+      <c r="D75" s="131" t="s">
+        <v>114</v>
+      </c>
+      <c r="E75" s="108" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="138">
+        <v>0.625</v>
+      </c>
+      <c r="B76" s="139">
         <v>0.68888888888888899</v>
       </c>
-      <c r="C75" s="119" t="s">
+      <c r="C76" s="119" t="s">
         <v>466</v>
       </c>
-      <c r="D75" s="132" t="s">
+      <c r="D76" s="132" t="s">
         <v>69</v>
       </c>
-      <c r="E75" s="111" t="s">
+      <c r="E76" s="111" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="138">
+    <row r="77" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="138">
         <v>0.73958333333333337</v>
       </c>
-      <c r="B76" s="139">
+      <c r="B77" s="139">
         <v>0.79513888888888884</v>
       </c>
-      <c r="C76" s="120" t="s">
+      <c r="C77" s="120" t="s">
         <v>467</v>
       </c>
-      <c r="D76" s="125" t="s">
+      <c r="D77" s="125" t="s">
         <v>198</v>
       </c>
-      <c r="E76" s="108" t="s">
+      <c r="E77" s="108" t="s">
         <v>199</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="138">
-        <v>0.75</v>
-      </c>
-      <c r="B77" s="139">
-        <v>0.80486111111111114</v>
-      </c>
-      <c r="C77" s="119" t="s">
-        <v>468</v>
-      </c>
-      <c r="D77" s="125" t="s">
-        <v>205</v>
-      </c>
-      <c r="E77" s="108" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8983,195 +9001,195 @@
         <v>0.75</v>
       </c>
       <c r="B78" s="139">
-        <v>0.80694444444444446</v>
+        <v>0.80486111111111114</v>
       </c>
       <c r="C78" s="119" t="s">
         <v>468</v>
       </c>
       <c r="D78" s="125" t="s">
+        <v>205</v>
+      </c>
+      <c r="E78" s="108" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="138">
+        <v>0.75</v>
+      </c>
+      <c r="B79" s="139">
+        <v>0.80694444444444446</v>
+      </c>
+      <c r="C79" s="119" t="s">
+        <v>468</v>
+      </c>
+      <c r="D79" s="125" t="s">
         <v>75</v>
       </c>
-      <c r="E78" s="108" t="s">
+      <c r="E79" s="108" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="133">
+    <row r="80" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="133">
         <v>0.80208333333333337</v>
       </c>
-      <c r="B79" s="148">
+      <c r="B80" s="148">
         <v>0.86249999999999993</v>
       </c>
-      <c r="C79" s="117" t="s">
+      <c r="C80" s="117" t="s">
         <v>469</v>
       </c>
-      <c r="D79" s="141" t="s">
+      <c r="D80" s="141" t="s">
         <v>347</v>
       </c>
-      <c r="E79" s="75" t="s">
+      <c r="E80" s="75" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="140" t="s">
+    <row r="81" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="140" t="s">
         <v>470</v>
       </c>
-      <c r="B80" s="92"/>
-      <c r="C80" s="34"/>
-      <c r="D80" s="35"/>
-      <c r="E80" s="155"/>
-    </row>
-    <row r="81" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="138">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="B81" s="20">
-        <v>0.3840277777777778</v>
-      </c>
-      <c r="C81" s="21" t="s">
-        <v>471</v>
-      </c>
-      <c r="D81" s="132" t="s">
-        <v>40</v>
-      </c>
-      <c r="E81" s="108" t="s">
-        <v>41</v>
-      </c>
+      <c r="B81" s="92"/>
+      <c r="C81" s="34"/>
+      <c r="D81" s="35"/>
+      <c r="E81" s="155"/>
     </row>
     <row r="82" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A82" s="138">
         <v>0.33333333333333331</v>
       </c>
       <c r="B82" s="20">
-        <v>0.38611111111111113</v>
+        <v>0.3840277777777778</v>
       </c>
       <c r="C82" s="21" t="s">
         <v>471</v>
       </c>
-      <c r="D82" s="131" t="s">
-        <v>262</v>
-      </c>
-      <c r="E82" s="72" t="s">
-        <v>43</v>
+      <c r="D82" s="132" t="s">
+        <v>40</v>
+      </c>
+      <c r="E82" s="108" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A83" s="138">
-        <v>0.3576388888888889</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="B83" s="20">
-        <v>0.41111111111111115</v>
+        <v>0.38611111111111113</v>
       </c>
       <c r="C83" s="21" t="s">
-        <v>472</v>
-      </c>
-      <c r="D83" s="132" t="s">
-        <v>243</v>
+        <v>471</v>
+      </c>
+      <c r="D83" s="131" t="s">
+        <v>262</v>
       </c>
       <c r="E83" s="72" t="s">
-        <v>244</v>
+        <v>43</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A84" s="138">
-        <v>0.375</v>
+        <v>0.3576388888888889</v>
       </c>
       <c r="B84" s="20">
-        <v>0.42499999999999999</v>
-      </c>
-      <c r="C84" s="26" t="s">
-        <v>473</v>
-      </c>
-      <c r="D84" s="125" t="s">
-        <v>326</v>
+        <v>0.41111111111111115</v>
+      </c>
+      <c r="C84" s="21" t="s">
+        <v>472</v>
+      </c>
+      <c r="D84" s="132" t="s">
+        <v>243</v>
       </c>
       <c r="E84" s="72" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A85" s="138">
         <v>0.375</v>
       </c>
       <c r="B85" s="20">
-        <v>0.4284722222222222</v>
-      </c>
-      <c r="C85" s="21" t="s">
-        <v>474</v>
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="C85" s="26" t="s">
+        <v>473</v>
       </c>
       <c r="D85" s="125" t="s">
-        <v>66</v>
-      </c>
-      <c r="E85" s="108" t="s">
-        <v>67</v>
+        <v>326</v>
+      </c>
+      <c r="E85" s="72" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A86" s="138">
-        <v>0.40625</v>
+        <v>0.375</v>
       </c>
       <c r="B86" s="20">
-        <v>0.45833333333333331</v>
+        <v>0.4284722222222222</v>
       </c>
       <c r="C86" s="21" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D86" s="125" t="s">
-        <v>108</v>
+        <v>66</v>
       </c>
       <c r="E86" s="108" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A87" s="138">
         <v>0.40625</v>
       </c>
       <c r="B87" s="20">
-        <v>0.4597222222222222</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="C87" s="21" t="s">
         <v>475</v>
       </c>
       <c r="D87" s="125" t="s">
-        <v>106</v>
-      </c>
-      <c r="E87" s="111" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+      <c r="E87" s="108" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A88" s="138">
         <v>0.40625</v>
       </c>
       <c r="B88" s="20">
-        <v>0.46111111111111108</v>
+        <v>0.4597222222222222</v>
       </c>
       <c r="C88" s="21" t="s">
         <v>475</v>
       </c>
       <c r="D88" s="125" t="s">
-        <v>47</v>
-      </c>
-      <c r="E88" s="108" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="E88" s="111" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A89" s="138">
         <v>0.40625</v>
       </c>
       <c r="B89" s="20">
-        <v>0.46319444444444446</v>
+        <v>0.46111111111111108</v>
       </c>
       <c r="C89" s="21" t="s">
-        <v>476</v>
-      </c>
-      <c r="D89" s="131" t="s">
-        <v>162</v>
+        <v>475</v>
+      </c>
+      <c r="D89" s="125" t="s">
+        <v>47</v>
       </c>
       <c r="E89" s="108" t="s">
-        <v>163</v>
+        <v>48</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -9179,118 +9197,118 @@
         <v>0.40625</v>
       </c>
       <c r="B90" s="20">
-        <v>0.46527777777777773</v>
+        <v>0.46319444444444446</v>
       </c>
       <c r="C90" s="21" t="s">
         <v>476</v>
       </c>
       <c r="D90" s="131" t="s">
+        <v>162</v>
+      </c>
+      <c r="E90" s="108" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="138">
+        <v>0.40625</v>
+      </c>
+      <c r="B91" s="20">
+        <v>0.46527777777777773</v>
+      </c>
+      <c r="C91" s="21" t="s">
+        <v>476</v>
+      </c>
+      <c r="D91" s="131" t="s">
         <v>232</v>
       </c>
-      <c r="E90" s="111" t="s">
+      <c r="E91" s="111" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="12.75" x14ac:dyDescent="0.15">
-      <c r="A91" s="145">
+    <row r="92" spans="1:5" ht="12.75" x14ac:dyDescent="0.15">
+      <c r="A92" s="145">
         <v>0.4201388888888889</v>
       </c>
-      <c r="B91" s="127">
+      <c r="B92" s="127">
         <v>0.47222222222222227</v>
       </c>
-      <c r="C91" s="109" t="s">
+      <c r="C92" s="109" t="s">
         <v>477</v>
       </c>
-      <c r="D91" s="99" t="s">
+      <c r="D92" s="99" t="s">
         <v>150</v>
       </c>
-      <c r="E91" s="116" t="s">
+      <c r="E92" s="116" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="138">
+    <row r="93" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="138">
         <v>0.4236111111111111</v>
       </c>
-      <c r="B92" s="20">
+      <c r="B93" s="20">
         <v>0.47569444444444442</v>
       </c>
-      <c r="C92" s="21" t="s">
+      <c r="C93" s="21" t="s">
         <v>478</v>
       </c>
-      <c r="D92" s="132" t="s">
+      <c r="D93" s="132" t="s">
         <v>111</v>
       </c>
-      <c r="E92" s="111" t="s">
+      <c r="E93" s="111" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="145">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="B93" s="127">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="C93" s="74" t="s">
-        <v>480</v>
-      </c>
-      <c r="D93" s="125" t="s">
-        <v>287</v>
-      </c>
-      <c r="E93" s="109" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A94" s="145">
         <v>0.42708333333333331</v>
       </c>
       <c r="B94" s="127">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C94" s="74" t="s">
+        <v>480</v>
+      </c>
+      <c r="D94" s="125" t="s">
+        <v>287</v>
+      </c>
+      <c r="E94" s="109" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="145">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="B95" s="127">
         <v>0.48333333333333334</v>
       </c>
-      <c r="C94" s="109" t="s">
+      <c r="C95" s="109" t="s">
         <v>481</v>
       </c>
-      <c r="D94" s="135" t="s">
+      <c r="D95" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="E94" s="74" t="s">
+      <c r="E95" s="74" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A95" s="145">
+    <row r="96" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A96" s="145">
         <v>0.4375</v>
       </c>
-      <c r="B95" s="127">
+      <c r="B96" s="127">
         <v>0.48958333333333331</v>
       </c>
-      <c r="C95" s="74" t="s">
+      <c r="C96" s="74" t="s">
         <v>482</v>
       </c>
-      <c r="D95" s="131" t="s">
+      <c r="D96" s="131" t="s">
         <v>134</v>
       </c>
-      <c r="E95" s="109" t="s">
+      <c r="E96" s="109" t="s">
         <v>115</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="138">
-        <v>0.44097222222222227</v>
-      </c>
-      <c r="B96" s="20">
-        <v>0.49305555555555558</v>
-      </c>
-      <c r="C96" s="21" t="s">
-        <v>483</v>
-      </c>
-      <c r="D96" s="125" t="s">
-        <v>97</v>
-      </c>
-      <c r="E96" s="111" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -9298,33 +9316,33 @@
         <v>0.44097222222222227</v>
       </c>
       <c r="B97" s="20">
-        <v>0.49652777777777773</v>
-      </c>
-      <c r="C97" s="26" t="s">
-        <v>484</v>
+        <v>0.49305555555555558</v>
+      </c>
+      <c r="C97" s="21" t="s">
+        <v>483</v>
       </c>
       <c r="D97" s="125" t="s">
-        <v>30</v>
-      </c>
-      <c r="E97" s="108" t="s">
-        <v>31</v>
+        <v>97</v>
+      </c>
+      <c r="E97" s="111" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A98" s="138">
-        <v>0.44444444444444442</v>
+        <v>0.44097222222222227</v>
       </c>
       <c r="B98" s="20">
-        <v>0.5</v>
-      </c>
-      <c r="C98" s="21" t="s">
-        <v>485</v>
+        <v>0.49652777777777773</v>
+      </c>
+      <c r="C98" s="26" t="s">
+        <v>484</v>
       </c>
       <c r="D98" s="125" t="s">
-        <v>352</v>
-      </c>
-      <c r="E98" s="111" t="s">
-        <v>123</v>
+        <v>30</v>
+      </c>
+      <c r="E98" s="108" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -9332,16 +9350,16 @@
         <v>0.44444444444444442</v>
       </c>
       <c r="B99" s="20">
-        <v>0.50208333333333333</v>
-      </c>
-      <c r="C99" s="26" t="s">
-        <v>486</v>
+        <v>0.5</v>
+      </c>
+      <c r="C99" s="21" t="s">
+        <v>485</v>
       </c>
       <c r="D99" s="125" t="s">
-        <v>121</v>
-      </c>
-      <c r="E99" s="108" t="s">
-        <v>109</v>
+        <v>352</v>
+      </c>
+      <c r="E99" s="111" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -9349,33 +9367,33 @@
         <v>0.44444444444444442</v>
       </c>
       <c r="B100" s="20">
-        <v>0.50624999999999998</v>
-      </c>
-      <c r="C100" s="21" t="s">
-        <v>487</v>
+        <v>0.50208333333333333</v>
+      </c>
+      <c r="C100" s="26" t="s">
+        <v>486</v>
       </c>
       <c r="D100" s="125" t="s">
-        <v>144</v>
-      </c>
-      <c r="E100" s="111" t="s">
-        <v>145</v>
+        <v>121</v>
+      </c>
+      <c r="E100" s="108" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A101" s="138">
-        <v>0.45833333333333331</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="B101" s="20">
-        <v>0.51736111111111105</v>
-      </c>
-      <c r="C101" s="26" t="s">
-        <v>488</v>
+        <v>0.50624999999999998</v>
+      </c>
+      <c r="C101" s="21" t="s">
+        <v>487</v>
       </c>
       <c r="D101" s="125" t="s">
-        <v>173</v>
-      </c>
-      <c r="E101" s="108" t="s">
-        <v>28</v>
+        <v>144</v>
+      </c>
+      <c r="E101" s="111" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -9383,97 +9401,114 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="B102" s="20">
-        <v>0.51944444444444449</v>
-      </c>
-      <c r="C102" s="21" t="s">
-        <v>489</v>
-      </c>
-      <c r="D102" s="131" t="s">
-        <v>25</v>
+        <v>0.51736111111111105</v>
+      </c>
+      <c r="C102" s="26" t="s">
+        <v>488</v>
+      </c>
+      <c r="D102" s="125" t="s">
+        <v>173</v>
       </c>
       <c r="E102" s="108" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A103" s="138">
-        <v>0.46527777777777773</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="B103" s="20">
-        <v>0.52361111111111114</v>
-      </c>
-      <c r="C103" s="26" t="s">
-        <v>490</v>
-      </c>
-      <c r="D103" s="125" t="s">
-        <v>240</v>
+        <v>0.51944444444444449</v>
+      </c>
+      <c r="C103" s="21" t="s">
+        <v>489</v>
+      </c>
+      <c r="D103" s="131" t="s">
+        <v>25</v>
       </c>
       <c r="E103" s="108" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A104" s="138">
-        <v>0.53472222222222221</v>
-      </c>
-      <c r="B104" s="161">
-        <v>0.58888888888888891</v>
+        <v>0.46527777777777773</v>
+      </c>
+      <c r="B104" s="20">
+        <v>0.52361111111111114</v>
       </c>
       <c r="C104" s="26" t="s">
-        <v>491</v>
-      </c>
-      <c r="D104" s="132" t="s">
-        <v>56</v>
-      </c>
-      <c r="E104" s="121" t="s">
-        <v>57</v>
+        <v>490</v>
+      </c>
+      <c r="D104" s="125" t="s">
+        <v>240</v>
+      </c>
+      <c r="E104" s="108" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A105" s="138">
         <v>0.53472222222222221</v>
       </c>
-      <c r="B105" s="20">
-        <v>0.59166666666666667</v>
-      </c>
-      <c r="C105" s="47" t="s">
-        <v>492</v>
-      </c>
-      <c r="D105" s="125" t="s">
-        <v>12</v>
-      </c>
-      <c r="E105" s="111" t="s">
-        <v>13</v>
+      <c r="B105" s="161">
+        <v>0.58888888888888891</v>
+      </c>
+      <c r="C105" s="26" t="s">
+        <v>491</v>
+      </c>
+      <c r="D105" s="132" t="s">
+        <v>56</v>
+      </c>
+      <c r="E105" s="121" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A106" s="138">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="B106" s="20">
+        <v>0.59166666666666667</v>
+      </c>
+      <c r="C106" s="47" t="s">
+        <v>492</v>
+      </c>
+      <c r="D106" s="125" t="s">
+        <v>12</v>
+      </c>
+      <c r="E106" s="111" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="138">
         <v>0.53819444444444442</v>
       </c>
-      <c r="B106" s="20">
+      <c r="B107" s="20">
         <v>0.59375</v>
       </c>
-      <c r="C106" s="26" t="s">
+      <c r="C107" s="26" t="s">
         <v>490</v>
       </c>
-      <c r="D106" s="131" t="s">
+      <c r="D107" s="131" t="s">
         <v>54</v>
       </c>
-      <c r="E106" s="121" t="s">
+      <c r="E107" s="121" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="162" t="s">
+    <row r="108" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="162" t="s">
         <v>493</v>
       </c>
-      <c r="B107" s="21"/>
-      <c r="C107" s="21"/>
-      <c r="D107" s="21"/>
-      <c r="E107" s="108"/>
+      <c r="B108" s="21"/>
+      <c r="C108" s="21"/>
+      <c r="D108" s="21"/>
+      <c r="E108" s="108"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E108"/>
+  <autoFilter ref="A3:E109"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
